--- a/RCM- پیشرفت کار کارشناسان- تکسونامی تجهیزات گندله سازی.xlsx
+++ b/RCM- پیشرفت کار کارشناسان- تکسونامی تجهیزات گندله سازی.xlsx
@@ -8297,7 +8297,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AF596"/>
   <sheetFormatPr defaultColWidth="12.125" defaultRowHeight="15"/>
   <cols>
@@ -8411,7 +8410,7 @@
       </c>
       <c r="D2" s="56">
         <f>AVERAGEIF($B$8:$B$595,"vital",$M$8:$M$595)</f>
-        <v>0.79066666666666641</v>
+        <v>0.89059829059829065</v>
       </c>
       <c r="E2" s="62"/>
       <c r="F2" s="70" t="s">
@@ -8513,7 +8512,7 @@
       </c>
       <c r="D3" s="56">
         <f>AVERAGEIF($B$8:$B$595,"ESSENTIAL",$M$8:$M$595)</f>
-        <v>0.496702127659575</v>
+        <v>0.5407446808510642</v>
       </c>
       <c r="E3" s="62"/>
       <c r="F3" s="70" t="s">
@@ -8581,7 +8580,7 @@
       </c>
       <c r="D4" s="56">
         <f>AVERAGEIF($B$8:$B$595,"IMPORTANT",$M$8:$M$595)</f>
-        <v>0.36478048780487832</v>
+        <v>0.3967317073170733</v>
       </c>
       <c r="E4" s="62"/>
       <c r="F4" s="70" t="s">
@@ -8589,7 +8588,7 @@
       </c>
       <c r="G4" s="56">
         <f>SUMIF($A$8:$A$1048576,"100",$M$8:$M$1048576)/G2</f>
-        <v>0.75310447761194088</v>
+        <v>0.85504477611940299</v>
       </c>
       <c r="H4" s="56">
         <f>SUMIF($A$8:$A$1048576,"200",$M$8:$M$1048576)/H2</f>
@@ -8601,15 +8600,15 @@
       </c>
       <c r="J4" s="56">
         <f>SUMIF($A$8:$A$1048576,"500",$M$8:$M$1048576)/J2</f>
-        <v>0.53274418604651153</v>
+        <v>0.59767441860465109</v>
       </c>
       <c r="K4" s="56">
         <f>SUMIF($A$8:$A$1048576,"600",$M$8:$M$1048576)/K2</f>
-        <v>0.80693877551020421</v>
+        <v>0.90979591836734686</v>
       </c>
       <c r="L4" s="56">
         <f>SUMIF($A$8:$A$1048576,"700",$M$8:$M$1048576)/L2</f>
-        <v>0.83216216216216321</v>
+        <v>0.94405405405405407</v>
       </c>
       <c r="M4" s="56">
         <f>SUMIF($A$8:$A$1048576,"800",$M$8:$M$1048576)/M2</f>
@@ -8617,7 +8616,7 @@
       </c>
       <c r="N4" s="56">
         <f>SUMIF($A$8:$A$1048576,"900",$M$8:$M$1048576)/N2</f>
-        <v>0.51254901960784394</v>
+        <v>0.55254901960784364</v>
       </c>
       <c r="O4" s="56">
         <f>SUMIF($A$8:$A$1048576,"1000",$M$8:$M$1048576)/O2</f>
@@ -8665,13 +8664,13 @@
       </c>
       <c r="D5" s="56">
         <f>AVERAGEIF($B$8:$B$595,"NORMAL",$M$8:$M$595)</f>
-        <v>0.17320754716981124</v>
+        <v>0.19283018867924523</v>
       </c>
       <c r="E5" s="62"/>
       <c r="F5" s="63"/>
       <c r="G5" s="56">
         <f t="shared" ref="G5:P5" si="1">(G2+G3)*G4/($V$2+$V$3)</f>
-        <v>8.0455202186740779E-2</v>
+        <v>9.1345626518569936E-2</v>
       </c>
       <c r="H5" s="56">
         <f t="shared" si="1"/>
@@ -8683,15 +8682,15 @@
       </c>
       <c r="J5" s="56">
         <f t="shared" si="1"/>
-        <v>4.2588561384532174E-2</v>
+        <v>4.7779204975662508E-2</v>
       </c>
       <c r="K5" s="56">
         <f t="shared" si="1"/>
-        <v>7.858270052206931E-2</v>
+        <v>8.859931181775034E-2</v>
       </c>
       <c r="L5" s="56">
         <f t="shared" si="1"/>
-        <v>0.11853472658705232</v>
+        <v>0.13447281583909493</v>
       </c>
       <c r="M5" s="56">
         <f t="shared" si="1"/>
@@ -8699,7 +8698,7 @@
       </c>
       <c r="N5" s="56">
         <f t="shared" si="1"/>
-        <v>8.2693228454172499E-2</v>
+        <v>8.914671682626546E-2</v>
       </c>
       <c r="O5" s="56">
         <f t="shared" si="1"/>
@@ -8722,7 +8721,7 @@
       <c r="U5" s="56"/>
       <c r="V5" s="56">
         <f>SUBTOTAL(9,G5:U5)</f>
-        <v>0.45370641642573156</v>
+        <v>0.50219567326850767</v>
       </c>
     </row>
     <row r="6" spans="1:32" ht="15" customHeight="1">
@@ -8785,7 +8784,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="15.75" hidden="1">
+    <row r="8" spans="1:32" ht="15.75">
       <c r="A8" s="30">
         <v>100</v>
       </c>
@@ -8818,17 +8817,17 @@
         <v>1</v>
       </c>
       <c r="K8" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="28">
         <f t="shared" ref="M8:M71" si="2">SUMPRODUCT(H8:L8,$AA$2:$AE$2)</f>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" customFormat="1" ht="15.75">
       <c r="A9" s="2">
         <v>100</v>
       </c>
@@ -8860,18 +8859,22 @@
       <c r="J9" s="10">
         <v>1</v>
       </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
+      <c r="K9" s="28">
+        <v>1</v>
+      </c>
+      <c r="L9" s="28">
+        <v>1</v>
+      </c>
       <c r="M9" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N9" s="38"/>
       <c r="O9" s="38"/>
       <c r="P9" s="38"/>
       <c r="Q9" s="27"/>
     </row>
-    <row r="10" spans="1:32" customFormat="1" ht="15.75" hidden="1">
+    <row r="10" spans="1:32" customFormat="1" ht="15.75">
       <c r="A10" s="2">
         <v>100</v>
       </c>
@@ -8903,18 +8906,22 @@
       <c r="J10" s="10">
         <v>1</v>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
+      <c r="K10" s="28">
+        <v>1</v>
+      </c>
+      <c r="L10" s="28">
+        <v>1</v>
+      </c>
       <c r="M10" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N10" s="38"/>
       <c r="O10" s="38"/>
       <c r="P10" s="38"/>
       <c r="Q10" s="27"/>
     </row>
-    <row r="11" spans="1:32" ht="15.75" hidden="1">
+    <row r="11" spans="1:32" ht="15.75">
       <c r="A11" s="30">
         <v>100</v>
       </c>
@@ -8944,16 +8951,20 @@
         <v>1</v>
       </c>
       <c r="J11" s="28">
-        <v>0.9</v>
-      </c>
-      <c r="K11" s="28"/>
-      <c r="L11" s="28"/>
+        <v>1</v>
+      </c>
+      <c r="K11" s="28">
+        <v>1</v>
+      </c>
+      <c r="L11" s="28">
+        <v>1</v>
+      </c>
       <c r="M11" s="28">
         <f t="shared" si="2"/>
-        <v>0.85200000000000009</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" customFormat="1" ht="15.75">
       <c r="A12" s="2">
         <v>100</v>
       </c>
@@ -8985,18 +8996,22 @@
       <c r="J12" s="10">
         <v>1</v>
       </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
+      <c r="K12" s="28">
+        <v>1</v>
+      </c>
+      <c r="L12" s="28">
+        <v>1</v>
+      </c>
       <c r="M12" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N12" s="38"/>
       <c r="O12" s="38"/>
       <c r="P12" s="38"/>
       <c r="Q12" s="27"/>
     </row>
-    <row r="13" spans="1:32" customFormat="1" ht="15.75" hidden="1">
+    <row r="13" spans="1:32" customFormat="1" ht="15.75">
       <c r="A13" s="2">
         <v>100</v>
       </c>
@@ -9028,18 +9043,22 @@
       <c r="J13" s="10">
         <v>1</v>
       </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
+      <c r="K13" s="28">
+        <v>1</v>
+      </c>
+      <c r="L13" s="28">
+        <v>1</v>
+      </c>
       <c r="M13" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N13" s="38"/>
       <c r="O13" s="38"/>
       <c r="P13" s="38"/>
       <c r="Q13" s="27"/>
     </row>
-    <row r="14" spans="1:32" customFormat="1" ht="15.75" hidden="1">
+    <row r="14" spans="1:32" customFormat="1" ht="15.75">
       <c r="A14" s="2">
         <v>100</v>
       </c>
@@ -9071,18 +9090,22 @@
       <c r="J14" s="10">
         <v>1</v>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
+      <c r="K14" s="28">
+        <v>1</v>
+      </c>
+      <c r="L14" s="28">
+        <v>1</v>
+      </c>
       <c r="M14" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N14" s="38"/>
       <c r="O14" s="38"/>
       <c r="P14" s="38"/>
       <c r="Q14" s="27"/>
     </row>
-    <row r="15" spans="1:32" customFormat="1" ht="15.75" hidden="1">
+    <row r="15" spans="1:32" customFormat="1" ht="15.75">
       <c r="A15" s="2">
         <v>100</v>
       </c>
@@ -9114,18 +9137,22 @@
       <c r="J15" s="10">
         <v>1</v>
       </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
+      <c r="K15" s="28">
+        <v>1</v>
+      </c>
+      <c r="L15" s="28">
+        <v>1</v>
+      </c>
       <c r="M15" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N15" s="38"/>
       <c r="O15" s="38"/>
       <c r="P15" s="38"/>
       <c r="Q15" s="27"/>
     </row>
-    <row r="16" spans="1:32" customFormat="1" ht="15.75" hidden="1">
+    <row r="16" spans="1:32" customFormat="1" ht="15.75">
       <c r="A16" s="2">
         <v>100</v>
       </c>
@@ -9157,18 +9184,22 @@
       <c r="J16" s="10">
         <v>1</v>
       </c>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
+      <c r="K16" s="28">
+        <v>1</v>
+      </c>
+      <c r="L16" s="28">
+        <v>1</v>
+      </c>
       <c r="M16" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N16" s="38"/>
       <c r="O16" s="38"/>
       <c r="P16" s="38"/>
       <c r="Q16" s="27"/>
     </row>
-    <row r="17" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="17" spans="1:17" customFormat="1" ht="15.75">
       <c r="A17" s="2">
         <v>100</v>
       </c>
@@ -9200,18 +9231,22 @@
       <c r="J17" s="10">
         <v>1</v>
       </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
+      <c r="K17" s="28">
+        <v>1</v>
+      </c>
+      <c r="L17" s="28">
+        <v>1</v>
+      </c>
       <c r="M17" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N17" s="38"/>
       <c r="O17" s="38"/>
       <c r="P17" s="38"/>
       <c r="Q17" s="27"/>
     </row>
-    <row r="18" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="18" spans="1:17" customFormat="1" ht="15.75">
       <c r="A18" s="2">
         <v>100</v>
       </c>
@@ -9243,18 +9278,22 @@
       <c r="J18" s="10">
         <v>1</v>
       </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
+      <c r="K18" s="28">
+        <v>1</v>
+      </c>
+      <c r="L18" s="28">
+        <v>1</v>
+      </c>
       <c r="M18" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N18" s="38"/>
       <c r="O18" s="38"/>
       <c r="P18" s="38"/>
       <c r="Q18" s="27"/>
     </row>
-    <row r="19" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="19" spans="1:17" customFormat="1" ht="15.75">
       <c r="A19" s="2">
         <v>100</v>
       </c>
@@ -9286,18 +9325,22 @@
       <c r="J19" s="10">
         <v>1</v>
       </c>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
+      <c r="K19" s="28">
+        <v>1</v>
+      </c>
+      <c r="L19" s="28">
+        <v>1</v>
+      </c>
       <c r="M19" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N19" s="38"/>
       <c r="O19" s="38"/>
       <c r="P19" s="38"/>
       <c r="Q19" s="27"/>
     </row>
-    <row r="20" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="20" spans="1:17" customFormat="1" ht="15.75">
       <c r="A20" s="2">
         <v>100</v>
       </c>
@@ -9323,22 +9366,28 @@
       <c r="H20" s="10">
         <v>1</v>
       </c>
-      <c r="I20" s="10"/>
+      <c r="I20" s="10">
+        <v>1</v>
+      </c>
       <c r="J20" s="10">
         <v>1</v>
       </c>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
+      <c r="K20" s="10">
+        <v>1</v>
+      </c>
+      <c r="L20" s="10">
+        <v>1</v>
+      </c>
       <c r="M20" s="10">
         <f t="shared" si="2"/>
-        <v>0.43000000000000005</v>
+        <v>1</v>
       </c>
       <c r="N20" s="38"/>
       <c r="O20" s="38"/>
       <c r="P20" s="38"/>
       <c r="Q20" s="27"/>
     </row>
-    <row r="21" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="21" spans="1:17" customFormat="1" ht="15.75">
       <c r="A21" s="2">
         <v>100</v>
       </c>
@@ -9370,18 +9419,22 @@
       <c r="J21" s="10">
         <v>1</v>
       </c>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
+      <c r="K21" s="28">
+        <v>1</v>
+      </c>
+      <c r="L21" s="28">
+        <v>1</v>
+      </c>
       <c r="M21" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N21" s="38"/>
       <c r="O21" s="38"/>
       <c r="P21" s="38"/>
       <c r="Q21" s="27"/>
     </row>
-    <row r="22" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="22" spans="1:17" customFormat="1" ht="15.75">
       <c r="A22" s="2">
         <v>100</v>
       </c>
@@ -9413,18 +9466,22 @@
       <c r="J22" s="10">
         <v>1</v>
       </c>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
+      <c r="K22" s="28">
+        <v>1</v>
+      </c>
+      <c r="L22" s="28">
+        <v>1</v>
+      </c>
       <c r="M22" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N22" s="38"/>
       <c r="O22" s="38"/>
       <c r="P22" s="38"/>
       <c r="Q22" s="27"/>
     </row>
-    <row r="23" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="23" spans="1:17" customFormat="1" ht="15.75">
       <c r="A23" s="2">
         <v>100</v>
       </c>
@@ -9456,18 +9513,22 @@
       <c r="J23" s="10">
         <v>1</v>
       </c>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
+      <c r="K23" s="28">
+        <v>1</v>
+      </c>
+      <c r="L23" s="28">
+        <v>1</v>
+      </c>
       <c r="M23" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N23" s="38"/>
       <c r="O23" s="38"/>
       <c r="P23" s="38"/>
       <c r="Q23" s="27"/>
     </row>
-    <row r="24" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="24" spans="1:17" customFormat="1" ht="15.75">
       <c r="A24" s="2">
         <v>100</v>
       </c>
@@ -9499,18 +9560,22 @@
       <c r="J24" s="10">
         <v>1</v>
       </c>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
+      <c r="K24" s="28">
+        <v>1</v>
+      </c>
+      <c r="L24" s="28">
+        <v>1</v>
+      </c>
       <c r="M24" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N24" s="38"/>
       <c r="O24" s="38"/>
       <c r="P24" s="38"/>
       <c r="Q24" s="27"/>
     </row>
-    <row r="25" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="25" spans="1:17" customFormat="1" ht="15.75">
       <c r="A25" s="2">
         <v>100</v>
       </c>
@@ -9542,18 +9607,22 @@
       <c r="J25" s="10">
         <v>1</v>
       </c>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
+      <c r="K25" s="28">
+        <v>1</v>
+      </c>
+      <c r="L25" s="28">
+        <v>1</v>
+      </c>
       <c r="M25" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N25" s="38"/>
       <c r="O25" s="38"/>
       <c r="P25" s="38"/>
       <c r="Q25" s="27"/>
     </row>
-    <row r="26" spans="1:17" ht="15.75" hidden="1">
+    <row r="26" spans="1:17" ht="15.75">
       <c r="A26" s="30">
         <v>100</v>
       </c>
@@ -9583,16 +9652,20 @@
         <v>1</v>
       </c>
       <c r="J26" s="28">
-        <v>0.6</v>
-      </c>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="28">
+        <v>1</v>
+      </c>
+      <c r="L26" s="28">
+        <v>1</v>
+      </c>
       <c r="M26" s="28">
         <f t="shared" si="2"/>
-        <v>0.76800000000000002</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" customFormat="1" ht="15.75">
       <c r="A27" s="2">
         <v>100</v>
       </c>
@@ -9624,18 +9697,22 @@
       <c r="J27" s="10">
         <v>1</v>
       </c>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
+      <c r="K27" s="28">
+        <v>1</v>
+      </c>
+      <c r="L27" s="28">
+        <v>1</v>
+      </c>
       <c r="M27" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N27" s="38"/>
       <c r="O27" s="38"/>
       <c r="P27" s="38"/>
       <c r="Q27" s="27"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" hidden="1">
+    <row r="28" spans="1:17" ht="15.75">
       <c r="A28" s="30">
         <v>100</v>
       </c>
@@ -9667,14 +9744,18 @@
       <c r="J28" s="28">
         <v>1</v>
       </c>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
+      <c r="K28" s="28">
+        <v>1</v>
+      </c>
+      <c r="L28" s="28">
+        <v>1</v>
+      </c>
       <c r="M28" s="28">
         <f t="shared" si="2"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="15.75">
       <c r="A29" s="30">
         <v>100</v>
       </c>
@@ -9706,14 +9787,18 @@
       <c r="J29" s="28">
         <v>1</v>
       </c>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
+      <c r="K29" s="28">
+        <v>1</v>
+      </c>
+      <c r="L29" s="28">
+        <v>1</v>
+      </c>
       <c r="M29" s="28">
         <f t="shared" si="2"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="15.75">
       <c r="A30" s="30">
         <v>100</v>
       </c>
@@ -9745,14 +9830,18 @@
       <c r="J30" s="28">
         <v>1</v>
       </c>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
+      <c r="K30" s="28">
+        <v>1</v>
+      </c>
+      <c r="L30" s="28">
+        <v>1</v>
+      </c>
       <c r="M30" s="28">
         <f t="shared" si="2"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="15.75">
       <c r="A31" s="30">
         <v>100</v>
       </c>
@@ -9784,14 +9873,18 @@
       <c r="J31" s="28">
         <v>1</v>
       </c>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
+      <c r="K31" s="28">
+        <v>1</v>
+      </c>
+      <c r="L31" s="28">
+        <v>1</v>
+      </c>
       <c r="M31" s="28">
         <f t="shared" si="2"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="15.75">
       <c r="A32" s="30">
         <v>100</v>
       </c>
@@ -9823,14 +9916,18 @@
       <c r="J32" s="28">
         <v>1</v>
       </c>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
+      <c r="K32" s="28">
+        <v>1</v>
+      </c>
+      <c r="L32" s="28">
+        <v>1</v>
+      </c>
       <c r="M32" s="28">
         <f t="shared" si="2"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="15.75">
       <c r="A33" s="30">
         <v>100</v>
       </c>
@@ -9862,14 +9959,18 @@
       <c r="J33" s="28">
         <v>1</v>
       </c>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
+      <c r="K33" s="28">
+        <v>1</v>
+      </c>
+      <c r="L33" s="28">
+        <v>1</v>
+      </c>
       <c r="M33" s="28">
         <f t="shared" si="2"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" customFormat="1" ht="15.75">
       <c r="A34" s="2">
         <v>100</v>
       </c>
@@ -9901,18 +10002,22 @@
       <c r="J34" s="10">
         <v>1</v>
       </c>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
+      <c r="K34" s="28">
+        <v>1</v>
+      </c>
+      <c r="L34" s="28">
+        <v>1</v>
+      </c>
       <c r="M34" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N34" s="38"/>
       <c r="O34" s="38"/>
       <c r="P34" s="38"/>
       <c r="Q34" s="27"/>
     </row>
-    <row r="35" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="35" spans="1:17" customFormat="1" ht="15.75">
       <c r="A35" s="2">
         <v>100</v>
       </c>
@@ -9944,18 +10049,22 @@
       <c r="J35" s="10">
         <v>1</v>
       </c>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
+      <c r="K35" s="28">
+        <v>1</v>
+      </c>
+      <c r="L35" s="28">
+        <v>1</v>
+      </c>
       <c r="M35" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N35" s="38"/>
       <c r="O35" s="38"/>
       <c r="P35" s="38"/>
       <c r="Q35" s="27"/>
     </row>
-    <row r="36" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="36" spans="1:17" customFormat="1" ht="15.75">
       <c r="A36" s="2">
         <v>100</v>
       </c>
@@ -9996,7 +10105,7 @@
       <c r="P36" s="38"/>
       <c r="Q36" s="27"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" hidden="1">
+    <row r="37" spans="1:17" ht="15.75">
       <c r="A37" s="30">
         <v>100</v>
       </c>
@@ -10035,7 +10144,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="38" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="38" spans="1:17" customFormat="1" ht="15.75">
       <c r="A38" s="2">
         <v>100</v>
       </c>
@@ -10067,18 +10176,22 @@
       <c r="J38" s="10">
         <v>1</v>
       </c>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
+      <c r="K38" s="28">
+        <v>1</v>
+      </c>
+      <c r="L38" s="28">
+        <v>1</v>
+      </c>
       <c r="M38" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N38" s="38"/>
       <c r="O38" s="38"/>
       <c r="P38" s="38"/>
       <c r="Q38" s="27"/>
     </row>
-    <row r="39" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="39" spans="1:17" customFormat="1" ht="15.75">
       <c r="A39" s="2">
         <v>100</v>
       </c>
@@ -10110,18 +10223,22 @@
       <c r="J39" s="10">
         <v>1</v>
       </c>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
+      <c r="K39" s="28">
+        <v>1</v>
+      </c>
+      <c r="L39" s="28">
+        <v>1</v>
+      </c>
       <c r="M39" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N39" s="38"/>
       <c r="O39" s="38"/>
       <c r="P39" s="38"/>
       <c r="Q39" s="27"/>
     </row>
-    <row r="40" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="40" spans="1:17" customFormat="1" ht="15.75">
       <c r="A40" s="2">
         <v>100</v>
       </c>
@@ -10153,18 +10270,22 @@
       <c r="J40" s="10">
         <v>1</v>
       </c>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
+      <c r="K40" s="28">
+        <v>1</v>
+      </c>
+      <c r="L40" s="28">
+        <v>1</v>
+      </c>
       <c r="M40" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N40" s="38"/>
       <c r="O40" s="38"/>
       <c r="P40" s="38"/>
       <c r="Q40" s="27"/>
     </row>
-    <row r="41" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="41" spans="1:17" customFormat="1" ht="15.75">
       <c r="A41" s="2">
         <v>100</v>
       </c>
@@ -10196,18 +10317,22 @@
       <c r="J41" s="10">
         <v>1</v>
       </c>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
+      <c r="K41" s="28">
+        <v>1</v>
+      </c>
+      <c r="L41" s="28">
+        <v>1</v>
+      </c>
       <c r="M41" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N41" s="38"/>
       <c r="O41" s="38"/>
       <c r="P41" s="38"/>
       <c r="Q41" s="27"/>
     </row>
-    <row r="42" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="42" spans="1:17" customFormat="1" ht="15.75">
       <c r="A42" s="2">
         <v>100</v>
       </c>
@@ -10239,18 +10364,22 @@
       <c r="J42" s="10">
         <v>1</v>
       </c>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
+      <c r="K42" s="28">
+        <v>1</v>
+      </c>
+      <c r="L42" s="28">
+        <v>1</v>
+      </c>
       <c r="M42" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N42" s="38"/>
       <c r="O42" s="38"/>
       <c r="P42" s="38"/>
       <c r="Q42" s="27"/>
     </row>
-    <row r="43" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="43" spans="1:17" customFormat="1" ht="15.75">
       <c r="A43" s="2">
         <v>100</v>
       </c>
@@ -10291,7 +10420,7 @@
       <c r="P43" s="38"/>
       <c r="Q43" s="27"/>
     </row>
-    <row r="44" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="44" spans="1:17" customFormat="1" ht="15.75">
       <c r="A44" s="2">
         <v>100</v>
       </c>
@@ -10332,7 +10461,7 @@
       <c r="P44" s="38"/>
       <c r="Q44" s="27"/>
     </row>
-    <row r="45" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="45" spans="1:17" customFormat="1" ht="15.75">
       <c r="A45" s="2">
         <v>100</v>
       </c>
@@ -10373,7 +10502,7 @@
       <c r="P45" s="38"/>
       <c r="Q45" s="27"/>
     </row>
-    <row r="46" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="46" spans="1:17" customFormat="1" ht="15.75">
       <c r="A46" s="2">
         <v>100</v>
       </c>
@@ -10414,7 +10543,7 @@
       <c r="P46" s="38"/>
       <c r="Q46" s="27"/>
     </row>
-    <row r="47" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="47" spans="1:17" customFormat="1" ht="15.75">
       <c r="A47" s="2">
         <v>100</v>
       </c>
@@ -10455,7 +10584,7 @@
       <c r="P47" s="38"/>
       <c r="Q47" s="27"/>
     </row>
-    <row r="48" spans="1:17" ht="15.75" hidden="1">
+    <row r="48" spans="1:17" ht="15.75">
       <c r="A48" s="30">
         <v>100</v>
       </c>
@@ -10487,14 +10616,18 @@
       <c r="J48" s="28">
         <v>1</v>
       </c>
-      <c r="K48" s="28"/>
-      <c r="L48" s="28"/>
+      <c r="K48" s="28">
+        <v>1</v>
+      </c>
+      <c r="L48" s="28">
+        <v>1</v>
+      </c>
       <c r="M48" s="28">
         <f t="shared" si="2"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" ht="15.75">
       <c r="A49" s="30">
         <v>100</v>
       </c>
@@ -10526,14 +10659,18 @@
       <c r="J49" s="28">
         <v>1</v>
       </c>
-      <c r="K49" s="28"/>
-      <c r="L49" s="28"/>
+      <c r="K49" s="28">
+        <v>1</v>
+      </c>
+      <c r="L49" s="28">
+        <v>1</v>
+      </c>
       <c r="M49" s="28">
         <f t="shared" si="2"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" ht="15.75">
       <c r="A50" s="30">
         <v>100</v>
       </c>
@@ -10565,14 +10702,18 @@
       <c r="J50" s="28">
         <v>1</v>
       </c>
-      <c r="K50" s="28"/>
-      <c r="L50" s="28"/>
+      <c r="K50" s="28">
+        <v>1</v>
+      </c>
+      <c r="L50" s="28">
+        <v>1</v>
+      </c>
       <c r="M50" s="28">
         <f t="shared" si="2"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" customFormat="1" ht="15.75">
       <c r="A51" s="2">
         <v>100</v>
       </c>
@@ -10604,18 +10745,22 @@
       <c r="J51" s="10">
         <v>1</v>
       </c>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
+      <c r="K51" s="28">
+        <v>1</v>
+      </c>
+      <c r="L51" s="28">
+        <v>1</v>
+      </c>
       <c r="M51" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N51" s="38"/>
       <c r="O51" s="38"/>
       <c r="P51" s="38"/>
       <c r="Q51" s="27"/>
     </row>
-    <row r="52" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="52" spans="1:17" customFormat="1" ht="15.75">
       <c r="A52" s="2">
         <v>100</v>
       </c>
@@ -10656,7 +10801,7 @@
       <c r="P52" s="38"/>
       <c r="Q52" s="27"/>
     </row>
-    <row r="53" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="53" spans="1:17" customFormat="1" ht="15.75">
       <c r="A53" s="2">
         <v>100</v>
       </c>
@@ -10688,18 +10833,22 @@
       <c r="J53" s="10">
         <v>1</v>
       </c>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
+      <c r="K53" s="28">
+        <v>1</v>
+      </c>
+      <c r="L53" s="28">
+        <v>1</v>
+      </c>
       <c r="M53" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N53" s="38"/>
       <c r="O53" s="38"/>
       <c r="P53" s="38"/>
       <c r="Q53" s="27"/>
     </row>
-    <row r="54" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="54" spans="1:17" customFormat="1" ht="15.75">
       <c r="A54" s="2">
         <v>100</v>
       </c>
@@ -10740,7 +10889,7 @@
       <c r="P54" s="38"/>
       <c r="Q54" s="27"/>
     </row>
-    <row r="55" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="55" spans="1:17" customFormat="1" ht="15.75">
       <c r="A55" s="2">
         <v>100</v>
       </c>
@@ -10777,7 +10926,7 @@
       <c r="P55" s="38"/>
       <c r="Q55" s="27"/>
     </row>
-    <row r="56" spans="1:17" ht="15.75" hidden="1">
+    <row r="56" spans="1:17" ht="15.75">
       <c r="A56" s="30">
         <v>100</v>
       </c>
@@ -10809,14 +10958,18 @@
       <c r="J56" s="28">
         <v>1</v>
       </c>
-      <c r="K56" s="28"/>
-      <c r="L56" s="28"/>
+      <c r="K56" s="28">
+        <v>1</v>
+      </c>
+      <c r="L56" s="28">
+        <v>1</v>
+      </c>
       <c r="M56" s="28">
         <f t="shared" si="2"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" customFormat="1" ht="15.75">
       <c r="A57" s="2">
         <v>100</v>
       </c>
@@ -10848,18 +11001,22 @@
       <c r="J57" s="10">
         <v>1</v>
       </c>
-      <c r="K57" s="10"/>
-      <c r="L57" s="10"/>
+      <c r="K57" s="28">
+        <v>1</v>
+      </c>
+      <c r="L57" s="28">
+        <v>1</v>
+      </c>
       <c r="M57" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N57" s="38"/>
       <c r="O57" s="38"/>
       <c r="P57" s="38"/>
       <c r="Q57" s="27"/>
     </row>
-    <row r="58" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="58" spans="1:17" customFormat="1" ht="15.75">
       <c r="A58" s="2">
         <v>100</v>
       </c>
@@ -10891,18 +11048,22 @@
       <c r="J58" s="10">
         <v>1</v>
       </c>
-      <c r="K58" s="10"/>
-      <c r="L58" s="10"/>
+      <c r="K58" s="28">
+        <v>1</v>
+      </c>
+      <c r="L58" s="28">
+        <v>1</v>
+      </c>
       <c r="M58" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N58" s="38"/>
       <c r="O58" s="38"/>
       <c r="P58" s="38"/>
       <c r="Q58" s="27"/>
     </row>
-    <row r="59" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="59" spans="1:17" customFormat="1" ht="15.75">
       <c r="A59" s="2">
         <v>100</v>
       </c>
@@ -10934,18 +11095,22 @@
       <c r="J59" s="10">
         <v>1</v>
       </c>
-      <c r="K59" s="10"/>
-      <c r="L59" s="10"/>
+      <c r="K59" s="28">
+        <v>1</v>
+      </c>
+      <c r="L59" s="28">
+        <v>1</v>
+      </c>
       <c r="M59" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N59" s="38"/>
       <c r="O59" s="38"/>
       <c r="P59" s="38"/>
       <c r="Q59" s="27"/>
     </row>
-    <row r="60" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="60" spans="1:17" customFormat="1" ht="15.75">
       <c r="A60" s="2">
         <v>100</v>
       </c>
@@ -10977,18 +11142,22 @@
       <c r="J60" s="10">
         <v>1</v>
       </c>
-      <c r="K60" s="10"/>
-      <c r="L60" s="10"/>
+      <c r="K60" s="28">
+        <v>1</v>
+      </c>
+      <c r="L60" s="28">
+        <v>1</v>
+      </c>
       <c r="M60" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N60" s="38"/>
       <c r="O60" s="38"/>
       <c r="P60" s="38"/>
       <c r="Q60" s="27"/>
     </row>
-    <row r="61" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="61" spans="1:17" customFormat="1" ht="15.75">
       <c r="A61" s="2">
         <v>100</v>
       </c>
@@ -11020,18 +11189,22 @@
       <c r="J61" s="10">
         <v>1</v>
       </c>
-      <c r="K61" s="10"/>
-      <c r="L61" s="10"/>
+      <c r="K61" s="28">
+        <v>1</v>
+      </c>
+      <c r="L61" s="28">
+        <v>1</v>
+      </c>
       <c r="M61" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N61" s="38"/>
       <c r="O61" s="38"/>
       <c r="P61" s="38"/>
       <c r="Q61" s="27"/>
     </row>
-    <row r="62" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="62" spans="1:17" customFormat="1" ht="15.75">
       <c r="A62" s="2">
         <v>100</v>
       </c>
@@ -11063,18 +11236,22 @@
       <c r="J62" s="10">
         <v>1</v>
       </c>
-      <c r="K62" s="10"/>
-      <c r="L62" s="10"/>
+      <c r="K62" s="28">
+        <v>1</v>
+      </c>
+      <c r="L62" s="28">
+        <v>1</v>
+      </c>
       <c r="M62" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N62" s="38"/>
       <c r="O62" s="38"/>
       <c r="P62" s="38"/>
       <c r="Q62" s="27"/>
     </row>
-    <row r="63" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="63" spans="1:17" customFormat="1" ht="15.75">
       <c r="A63" s="2">
         <v>100</v>
       </c>
@@ -11106,18 +11283,22 @@
       <c r="J63" s="10">
         <v>1</v>
       </c>
-      <c r="K63" s="10"/>
-      <c r="L63" s="10"/>
+      <c r="K63" s="28">
+        <v>1</v>
+      </c>
+      <c r="L63" s="28">
+        <v>1</v>
+      </c>
       <c r="M63" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N63" s="38"/>
       <c r="O63" s="38"/>
       <c r="P63" s="38"/>
       <c r="Q63" s="27"/>
     </row>
-    <row r="64" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="64" spans="1:17" customFormat="1" ht="15.75">
       <c r="A64" s="2">
         <v>100</v>
       </c>
@@ -11149,18 +11330,22 @@
       <c r="J64" s="10">
         <v>1</v>
       </c>
-      <c r="K64" s="10"/>
-      <c r="L64" s="10"/>
+      <c r="K64" s="28">
+        <v>1</v>
+      </c>
+      <c r="L64" s="28">
+        <v>1</v>
+      </c>
       <c r="M64" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N64" s="38"/>
       <c r="O64" s="38"/>
       <c r="P64" s="38"/>
       <c r="Q64" s="27"/>
     </row>
-    <row r="65" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="65" spans="1:17" customFormat="1" ht="15.75">
       <c r="A65" s="2">
         <v>100</v>
       </c>
@@ -11192,18 +11377,22 @@
       <c r="J65" s="10">
         <v>1</v>
       </c>
-      <c r="K65" s="10"/>
-      <c r="L65" s="10"/>
+      <c r="K65" s="28">
+        <v>1</v>
+      </c>
+      <c r="L65" s="28">
+        <v>1</v>
+      </c>
       <c r="M65" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N65" s="38"/>
       <c r="O65" s="38"/>
       <c r="P65" s="38"/>
       <c r="Q65" s="27"/>
     </row>
-    <row r="66" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="66" spans="1:17" customFormat="1" ht="15.75">
       <c r="A66" s="2">
         <v>100</v>
       </c>
@@ -11235,18 +11424,22 @@
       <c r="J66" s="10">
         <v>1</v>
       </c>
-      <c r="K66" s="10"/>
-      <c r="L66" s="10"/>
+      <c r="K66" s="28">
+        <v>1</v>
+      </c>
+      <c r="L66" s="28">
+        <v>1</v>
+      </c>
       <c r="M66" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N66" s="38"/>
       <c r="O66" s="38"/>
       <c r="P66" s="38"/>
       <c r="Q66" s="27"/>
     </row>
-    <row r="67" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="67" spans="1:17" customFormat="1" ht="15.75">
       <c r="A67" s="2">
         <v>100</v>
       </c>
@@ -11278,18 +11471,22 @@
       <c r="J67" s="10">
         <v>1</v>
       </c>
-      <c r="K67" s="10"/>
-      <c r="L67" s="10"/>
+      <c r="K67" s="28">
+        <v>1</v>
+      </c>
+      <c r="L67" s="28">
+        <v>1</v>
+      </c>
       <c r="M67" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N67" s="38"/>
       <c r="O67" s="38"/>
       <c r="P67" s="38"/>
       <c r="Q67" s="27"/>
     </row>
-    <row r="68" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="68" spans="1:17" customFormat="1" ht="15.75">
       <c r="A68" s="2">
         <v>100</v>
       </c>
@@ -11321,18 +11518,22 @@
       <c r="J68" s="10">
         <v>1</v>
       </c>
-      <c r="K68" s="10"/>
-      <c r="L68" s="10"/>
+      <c r="K68" s="28">
+        <v>1</v>
+      </c>
+      <c r="L68" s="28">
+        <v>1</v>
+      </c>
       <c r="M68" s="10">
         <f t="shared" si="2"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N68" s="38"/>
       <c r="O68" s="38"/>
       <c r="P68" s="38"/>
       <c r="Q68" s="27"/>
     </row>
-    <row r="69" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="69" spans="1:17" customFormat="1" ht="15.75">
       <c r="A69" s="2">
         <v>100</v>
       </c>
@@ -11369,7 +11570,7 @@
       <c r="P69" s="38"/>
       <c r="Q69" s="27"/>
     </row>
-    <row r="70" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="70" spans="1:17" customFormat="1" ht="15.75">
       <c r="A70" s="2">
         <v>100</v>
       </c>
@@ -11408,7 +11609,7 @@
       <c r="P70" s="38"/>
       <c r="Q70" s="27"/>
     </row>
-    <row r="71" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="71" spans="1:17" customFormat="1" ht="15.75">
       <c r="A71" s="2">
         <v>100</v>
       </c>
@@ -11447,7 +11648,7 @@
       <c r="P71" s="38"/>
       <c r="Q71" s="27"/>
     </row>
-    <row r="72" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="72" spans="1:17" customFormat="1" ht="15.75">
       <c r="A72" s="2">
         <v>100</v>
       </c>
@@ -11488,7 +11689,7 @@
       <c r="P72" s="38"/>
       <c r="Q72" s="27"/>
     </row>
-    <row r="73" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="73" spans="1:17" customFormat="1" ht="15.75">
       <c r="A73" s="2">
         <v>100</v>
       </c>
@@ -11529,7 +11730,7 @@
       <c r="P73" s="38"/>
       <c r="Q73" s="27"/>
     </row>
-    <row r="74" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="74" spans="1:17" customFormat="1" ht="15.75">
       <c r="A74" s="2">
         <v>100</v>
       </c>
@@ -11561,18 +11762,22 @@
       <c r="J74" s="10">
         <v>1</v>
       </c>
-      <c r="K74" s="10"/>
-      <c r="L74" s="10"/>
+      <c r="K74" s="28">
+        <v>1</v>
+      </c>
+      <c r="L74" s="28">
+        <v>1</v>
+      </c>
       <c r="M74" s="10">
         <f t="shared" si="3"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N74" s="38"/>
       <c r="O74" s="38"/>
       <c r="P74" s="38"/>
       <c r="Q74" s="27"/>
     </row>
-    <row r="75" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="75" spans="1:17" customFormat="1" ht="15.75">
       <c r="A75" s="2">
         <v>200</v>
       </c>
@@ -11609,7 +11814,7 @@
       <c r="P75" s="38"/>
       <c r="Q75" s="27"/>
     </row>
-    <row r="76" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="76" spans="1:17" customFormat="1" ht="15.75">
       <c r="A76" s="2">
         <v>200</v>
       </c>
@@ -11646,7 +11851,7 @@
       <c r="P76" s="38"/>
       <c r="Q76" s="27"/>
     </row>
-    <row r="77" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="77" spans="1:17" customFormat="1" ht="15.75">
       <c r="A77" s="2">
         <v>200</v>
       </c>
@@ -11687,7 +11892,7 @@
       <c r="P77" s="38"/>
       <c r="Q77" s="27"/>
     </row>
-    <row r="78" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="78" spans="1:17" customFormat="1" ht="15.75">
       <c r="A78" s="2">
         <v>200</v>
       </c>
@@ -11724,7 +11929,7 @@
       <c r="P78" s="38"/>
       <c r="Q78" s="27"/>
     </row>
-    <row r="79" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="79" spans="1:17" customFormat="1" ht="15.75">
       <c r="A79" s="2">
         <v>200</v>
       </c>
@@ -11761,7 +11966,7 @@
       <c r="P79" s="38"/>
       <c r="Q79" s="27"/>
     </row>
-    <row r="80" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="80" spans="1:17" customFormat="1" ht="15.75">
       <c r="A80" s="2">
         <v>200</v>
       </c>
@@ -11798,7 +12003,7 @@
       <c r="P80" s="38"/>
       <c r="Q80" s="27"/>
     </row>
-    <row r="81" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="81" spans="1:17" customFormat="1" ht="15.75">
       <c r="A81" s="2">
         <v>200</v>
       </c>
@@ -11839,7 +12044,7 @@
       <c r="P81" s="38"/>
       <c r="Q81" s="27"/>
     </row>
-    <row r="82" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="82" spans="1:17" customFormat="1" ht="15.75">
       <c r="A82" s="2">
         <v>200</v>
       </c>
@@ -11876,7 +12081,7 @@
       <c r="P82" s="38"/>
       <c r="Q82" s="27"/>
     </row>
-    <row r="83" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="83" spans="1:17" customFormat="1" ht="15.75">
       <c r="A83" s="2">
         <v>200</v>
       </c>
@@ -11917,7 +12122,7 @@
       <c r="P83" s="38"/>
       <c r="Q83" s="27"/>
     </row>
-    <row r="84" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="84" spans="1:17" customFormat="1" ht="15.75">
       <c r="A84" s="2">
         <v>200</v>
       </c>
@@ -11958,7 +12163,7 @@
       <c r="P84" s="38"/>
       <c r="Q84" s="27"/>
     </row>
-    <row r="85" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="85" spans="1:17" customFormat="1" ht="15.75">
       <c r="A85" s="2">
         <v>200</v>
       </c>
@@ -11999,7 +12204,7 @@
       <c r="P85" s="38"/>
       <c r="Q85" s="27"/>
     </row>
-    <row r="86" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="86" spans="1:17" customFormat="1" ht="15.75">
       <c r="A86" s="2">
         <v>200</v>
       </c>
@@ -12040,7 +12245,7 @@
       <c r="P86" s="38"/>
       <c r="Q86" s="27"/>
     </row>
-    <row r="87" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="87" spans="1:17" customFormat="1" ht="15.75">
       <c r="A87" s="2">
         <v>200</v>
       </c>
@@ -12081,7 +12286,7 @@
       <c r="P87" s="38"/>
       <c r="Q87" s="27"/>
     </row>
-    <row r="88" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="88" spans="1:17" customFormat="1" ht="15.75">
       <c r="A88" s="2">
         <v>200</v>
       </c>
@@ -12118,7 +12323,7 @@
       <c r="P88" s="38"/>
       <c r="Q88" s="27"/>
     </row>
-    <row r="89" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="89" spans="1:17" customFormat="1" ht="15.75">
       <c r="A89" s="2">
         <v>200</v>
       </c>
@@ -12155,7 +12360,7 @@
       <c r="P89" s="38"/>
       <c r="Q89" s="27"/>
     </row>
-    <row r="90" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="90" spans="1:17" customFormat="1" ht="15.75">
       <c r="A90" s="2">
         <v>200</v>
       </c>
@@ -12192,7 +12397,7 @@
       <c r="P90" s="38"/>
       <c r="Q90" s="27"/>
     </row>
-    <row r="91" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="91" spans="1:17" customFormat="1" ht="15.75">
       <c r="A91" s="2">
         <v>200</v>
       </c>
@@ -12229,7 +12434,7 @@
       <c r="P91" s="38"/>
       <c r="Q91" s="27"/>
     </row>
-    <row r="92" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="92" spans="1:17" customFormat="1" ht="15.75">
       <c r="A92" s="2">
         <v>200</v>
       </c>
@@ -12578,7 +12783,7 @@
       <c r="P100" s="38"/>
       <c r="Q100" s="27"/>
     </row>
-    <row r="101" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="101" spans="1:17" customFormat="1" ht="15.75">
       <c r="A101" s="2">
         <v>300</v>
       </c>
@@ -12849,7 +13054,7 @@
       <c r="P107" s="38"/>
       <c r="Q107" s="27"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" hidden="1">
+    <row r="108" spans="1:17" ht="15.75">
       <c r="A108" s="30">
         <v>500</v>
       </c>
@@ -12879,16 +13084,20 @@
         <v>1</v>
       </c>
       <c r="J108" s="28">
-        <v>0.3</v>
-      </c>
-      <c r="K108" s="28"/>
-      <c r="L108" s="28"/>
+        <v>1</v>
+      </c>
+      <c r="K108" s="28">
+        <v>1</v>
+      </c>
+      <c r="L108" s="28">
+        <v>1</v>
+      </c>
       <c r="M108" s="28">
         <f t="shared" si="3"/>
-        <v>0.68399999999999994</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" ht="15.75">
       <c r="A109" s="30">
         <v>500</v>
       </c>
@@ -12918,16 +13127,20 @@
         <v>1</v>
       </c>
       <c r="J109" s="28">
-        <v>0.3</v>
-      </c>
-      <c r="K109" s="28"/>
-      <c r="L109" s="28"/>
+        <v>1</v>
+      </c>
+      <c r="K109" s="28">
+        <v>1</v>
+      </c>
+      <c r="L109" s="28">
+        <v>1</v>
+      </c>
       <c r="M109" s="28">
         <f t="shared" si="3"/>
-        <v>0.68399999999999994</v>
-      </c>
-    </row>
-    <row r="110" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" customFormat="1" ht="15.75">
       <c r="A110" s="2">
         <v>500</v>
       </c>
@@ -12968,7 +13181,7 @@
       <c r="P110" s="38"/>
       <c r="Q110" s="27"/>
     </row>
-    <row r="111" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="111" spans="1:17" customFormat="1" ht="15.75">
       <c r="A111" s="2">
         <v>500</v>
       </c>
@@ -13009,7 +13222,7 @@
       <c r="P111" s="38"/>
       <c r="Q111" s="27"/>
     </row>
-    <row r="112" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="112" spans="1:17" customFormat="1" ht="15.75">
       <c r="A112" s="2">
         <v>500</v>
       </c>
@@ -13041,18 +13254,22 @@
       <c r="J112" s="10">
         <v>1</v>
       </c>
-      <c r="K112" s="10"/>
-      <c r="L112" s="10"/>
+      <c r="K112" s="28">
+        <v>1</v>
+      </c>
+      <c r="L112" s="28">
+        <v>1</v>
+      </c>
       <c r="M112" s="10">
         <f t="shared" si="3"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N112" s="38"/>
       <c r="O112" s="38"/>
       <c r="P112" s="38"/>
       <c r="Q112" s="27"/>
     </row>
-    <row r="113" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="113" spans="1:17" customFormat="1" ht="15.75">
       <c r="A113" s="2">
         <v>500</v>
       </c>
@@ -13084,18 +13301,22 @@
       <c r="J113" s="10">
         <v>1</v>
       </c>
-      <c r="K113" s="10"/>
-      <c r="L113" s="10"/>
+      <c r="K113" s="28">
+        <v>1</v>
+      </c>
+      <c r="L113" s="28">
+        <v>1</v>
+      </c>
       <c r="M113" s="10">
         <f t="shared" si="3"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N113" s="38"/>
       <c r="O113" s="38"/>
       <c r="P113" s="38"/>
       <c r="Q113" s="27"/>
     </row>
-    <row r="114" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="114" spans="1:17" customFormat="1" ht="15.75">
       <c r="A114" s="2">
         <v>500</v>
       </c>
@@ -13127,18 +13348,22 @@
       <c r="J114" s="10">
         <v>1</v>
       </c>
-      <c r="K114" s="10"/>
-      <c r="L114" s="10"/>
+      <c r="K114" s="28">
+        <v>1</v>
+      </c>
+      <c r="L114" s="28">
+        <v>1</v>
+      </c>
       <c r="M114" s="10">
         <f t="shared" si="3"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N114" s="38"/>
       <c r="O114" s="38"/>
       <c r="P114" s="38"/>
       <c r="Q114" s="27"/>
     </row>
-    <row r="115" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="115" spans="1:17" customFormat="1" ht="15.75">
       <c r="A115" s="2">
         <v>500</v>
       </c>
@@ -13170,18 +13395,22 @@
       <c r="J115" s="10">
         <v>1</v>
       </c>
-      <c r="K115" s="10"/>
-      <c r="L115" s="10"/>
+      <c r="K115" s="28">
+        <v>1</v>
+      </c>
+      <c r="L115" s="28">
+        <v>1</v>
+      </c>
       <c r="M115" s="10">
         <f t="shared" si="3"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N115" s="38"/>
       <c r="O115" s="38"/>
       <c r="P115" s="38"/>
       <c r="Q115" s="27"/>
     </row>
-    <row r="116" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="116" spans="1:17" customFormat="1" ht="15.75">
       <c r="A116" s="2">
         <v>500</v>
       </c>
@@ -13218,7 +13447,7 @@
       <c r="P116" s="38"/>
       <c r="Q116" s="27"/>
     </row>
-    <row r="117" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="117" spans="1:17" customFormat="1" ht="15.75">
       <c r="A117" s="2">
         <v>500</v>
       </c>
@@ -13255,7 +13484,7 @@
       <c r="P117" s="38"/>
       <c r="Q117" s="27"/>
     </row>
-    <row r="118" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="118" spans="1:17" customFormat="1" ht="15.75">
       <c r="A118" s="2">
         <v>500</v>
       </c>
@@ -13292,7 +13521,7 @@
       <c r="P118" s="38"/>
       <c r="Q118" s="27"/>
     </row>
-    <row r="119" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="119" spans="1:17" customFormat="1" ht="15.75">
       <c r="A119" s="2">
         <v>500</v>
       </c>
@@ -13329,7 +13558,7 @@
       <c r="P119" s="38"/>
       <c r="Q119" s="27"/>
     </row>
-    <row r="120" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="120" spans="1:17" customFormat="1" ht="15.75">
       <c r="A120" s="2">
         <v>500</v>
       </c>
@@ -13366,7 +13595,7 @@
       <c r="P120" s="38"/>
       <c r="Q120" s="27"/>
     </row>
-    <row r="121" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="121" spans="1:17" customFormat="1" ht="15.75">
       <c r="A121" s="2">
         <v>500</v>
       </c>
@@ -13403,7 +13632,7 @@
       <c r="P121" s="38"/>
       <c r="Q121" s="27"/>
     </row>
-    <row r="122" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="122" spans="1:17" customFormat="1" ht="15.75">
       <c r="A122" s="2">
         <v>500</v>
       </c>
@@ -13440,7 +13669,7 @@
       <c r="P122" s="38"/>
       <c r="Q122" s="27"/>
     </row>
-    <row r="123" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="123" spans="1:17" customFormat="1" ht="15.75">
       <c r="A123" s="2">
         <v>500</v>
       </c>
@@ -13477,7 +13706,7 @@
       <c r="P123" s="38"/>
       <c r="Q123" s="27"/>
     </row>
-    <row r="124" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="124" spans="1:17" customFormat="1" ht="15.75">
       <c r="A124" s="2">
         <v>500</v>
       </c>
@@ -13509,18 +13738,22 @@
       <c r="J124" s="10">
         <v>1</v>
       </c>
-      <c r="K124" s="10"/>
-      <c r="L124" s="10"/>
+      <c r="K124" s="28">
+        <v>1</v>
+      </c>
+      <c r="L124" s="28">
+        <v>1</v>
+      </c>
       <c r="M124" s="10">
         <f t="shared" si="3"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N124" s="38"/>
       <c r="O124" s="38"/>
       <c r="P124" s="38"/>
       <c r="Q124" s="27"/>
     </row>
-    <row r="125" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="125" spans="1:17" customFormat="1" ht="15.75">
       <c r="A125" s="2">
         <v>500</v>
       </c>
@@ -13552,18 +13785,22 @@
       <c r="J125" s="10">
         <v>1</v>
       </c>
-      <c r="K125" s="10"/>
-      <c r="L125" s="10"/>
+      <c r="K125" s="28">
+        <v>1</v>
+      </c>
+      <c r="L125" s="28">
+        <v>1</v>
+      </c>
       <c r="M125" s="10">
         <f t="shared" si="3"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N125" s="38"/>
       <c r="O125" s="38"/>
       <c r="P125" s="38"/>
       <c r="Q125" s="27"/>
     </row>
-    <row r="126" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="126" spans="1:17" customFormat="1" ht="15.75">
       <c r="A126" s="2">
         <v>500</v>
       </c>
@@ -13595,18 +13832,22 @@
       <c r="J126" s="10">
         <v>1</v>
       </c>
-      <c r="K126" s="10"/>
-      <c r="L126" s="10"/>
+      <c r="K126" s="28">
+        <v>1</v>
+      </c>
+      <c r="L126" s="28">
+        <v>1</v>
+      </c>
       <c r="M126" s="10">
         <f t="shared" si="3"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N126" s="38"/>
       <c r="O126" s="38"/>
       <c r="P126" s="38"/>
       <c r="Q126" s="27"/>
     </row>
-    <row r="127" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="127" spans="1:17" customFormat="1" ht="15.75">
       <c r="A127" s="2">
         <v>500</v>
       </c>
@@ -13638,18 +13879,22 @@
       <c r="J127" s="10">
         <v>1</v>
       </c>
-      <c r="K127" s="10"/>
-      <c r="L127" s="10"/>
+      <c r="K127" s="28">
+        <v>1</v>
+      </c>
+      <c r="L127" s="28">
+        <v>1</v>
+      </c>
       <c r="M127" s="10">
         <f t="shared" si="3"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N127" s="38"/>
       <c r="O127" s="38"/>
       <c r="P127" s="38"/>
       <c r="Q127" s="27"/>
     </row>
-    <row r="128" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="128" spans="1:17" customFormat="1" ht="15.75">
       <c r="A128" s="2">
         <v>500</v>
       </c>
@@ -13681,18 +13926,22 @@
       <c r="J128" s="10">
         <v>1</v>
       </c>
-      <c r="K128" s="10"/>
-      <c r="L128" s="10"/>
+      <c r="K128" s="28">
+        <v>1</v>
+      </c>
+      <c r="L128" s="28">
+        <v>1</v>
+      </c>
       <c r="M128" s="10">
         <f t="shared" si="3"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N128" s="38"/>
       <c r="O128" s="38"/>
       <c r="P128" s="38"/>
       <c r="Q128" s="27"/>
     </row>
-    <row r="129" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="129" spans="1:17" customFormat="1" ht="15.75">
       <c r="A129" s="2">
         <v>500</v>
       </c>
@@ -13724,18 +13973,22 @@
       <c r="J129" s="10">
         <v>1</v>
       </c>
-      <c r="K129" s="10"/>
-      <c r="L129" s="10"/>
+      <c r="K129" s="28">
+        <v>1</v>
+      </c>
+      <c r="L129" s="28">
+        <v>1</v>
+      </c>
       <c r="M129" s="10">
         <f t="shared" si="3"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N129" s="38"/>
       <c r="O129" s="38"/>
       <c r="P129" s="38"/>
       <c r="Q129" s="27"/>
     </row>
-    <row r="130" spans="1:17" ht="15.75" hidden="1">
+    <row r="130" spans="1:17" ht="15.75">
       <c r="A130" s="30">
         <v>500</v>
       </c>
@@ -13772,7 +14025,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="131" spans="1:17" ht="15.75" hidden="1">
+    <row r="131" spans="1:17" ht="15.75">
       <c r="A131" s="30">
         <v>500</v>
       </c>
@@ -13809,7 +14062,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="132" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="132" spans="1:17" customFormat="1" ht="15.75">
       <c r="A132" s="2">
         <v>500</v>
       </c>
@@ -13846,7 +14099,7 @@
       <c r="P132" s="38"/>
       <c r="Q132" s="27"/>
     </row>
-    <row r="133" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="133" spans="1:17" customFormat="1" ht="15.75">
       <c r="A133" s="2">
         <v>500</v>
       </c>
@@ -13883,7 +14136,7 @@
       <c r="P133" s="38"/>
       <c r="Q133" s="27"/>
     </row>
-    <row r="134" spans="1:17" ht="15.75" hidden="1">
+    <row r="134" spans="1:17" ht="15.75">
       <c r="A134" s="30">
         <v>500</v>
       </c>
@@ -13915,14 +14168,18 @@
       <c r="J134" s="28">
         <v>1</v>
       </c>
-      <c r="K134" s="28"/>
-      <c r="L134" s="28"/>
+      <c r="K134" s="28">
+        <v>1</v>
+      </c>
+      <c r="L134" s="28">
+        <v>1</v>
+      </c>
       <c r="M134" s="28">
         <f t="shared" si="3"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="135" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" ht="15.75">
       <c r="A135" s="30">
         <v>500</v>
       </c>
@@ -13954,14 +14211,18 @@
       <c r="J135" s="28">
         <v>1</v>
       </c>
-      <c r="K135" s="28"/>
-      <c r="L135" s="28"/>
+      <c r="K135" s="28">
+        <v>1</v>
+      </c>
+      <c r="L135" s="28">
+        <v>1</v>
+      </c>
       <c r="M135" s="28">
         <f t="shared" si="3"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="136" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" ht="15.75">
       <c r="A136" s="30">
         <v>500</v>
       </c>
@@ -13993,14 +14254,18 @@
       <c r="J136" s="28">
         <v>1</v>
       </c>
-      <c r="K136" s="28"/>
-      <c r="L136" s="28"/>
+      <c r="K136" s="28">
+        <v>1</v>
+      </c>
+      <c r="L136" s="28">
+        <v>1</v>
+      </c>
       <c r="M136" s="28">
         <f t="shared" ref="M136:M199" si="4">SUMPRODUCT(H136:L136,$AA$2:$AE$2)</f>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="137" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" ht="15.75">
       <c r="A137" s="30">
         <v>500</v>
       </c>
@@ -14032,14 +14297,18 @@
       <c r="J137" s="28">
         <v>1</v>
       </c>
-      <c r="K137" s="28"/>
-      <c r="L137" s="28"/>
+      <c r="K137" s="28">
+        <v>1</v>
+      </c>
+      <c r="L137" s="28">
+        <v>1</v>
+      </c>
       <c r="M137" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" ht="15.75">
       <c r="A138" s="30">
         <v>500</v>
       </c>
@@ -14071,14 +14340,18 @@
       <c r="J138" s="28">
         <v>1</v>
       </c>
-      <c r="K138" s="28"/>
-      <c r="L138" s="28"/>
+      <c r="K138" s="28">
+        <v>1</v>
+      </c>
+      <c r="L138" s="28">
+        <v>1</v>
+      </c>
       <c r="M138" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="139" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" customFormat="1" ht="15.75">
       <c r="A139" s="2">
         <v>500</v>
       </c>
@@ -14115,7 +14388,7 @@
       <c r="P139" s="38"/>
       <c r="Q139" s="27"/>
     </row>
-    <row r="140" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="140" spans="1:17" customFormat="1" ht="15.75">
       <c r="A140" s="2">
         <v>500</v>
       </c>
@@ -14147,18 +14420,22 @@
       <c r="J140" s="10">
         <v>1</v>
       </c>
-      <c r="K140" s="10"/>
-      <c r="L140" s="10"/>
+      <c r="K140" s="28">
+        <v>1</v>
+      </c>
+      <c r="L140" s="28">
+        <v>1</v>
+      </c>
       <c r="M140" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N140" s="38"/>
       <c r="O140" s="38"/>
       <c r="P140" s="38"/>
       <c r="Q140" s="27"/>
     </row>
-    <row r="141" spans="1:17" ht="15.75" hidden="1">
+    <row r="141" spans="1:17" ht="15.75">
       <c r="A141" s="30">
         <v>500</v>
       </c>
@@ -14190,14 +14467,18 @@
       <c r="J141" s="28">
         <v>1</v>
       </c>
-      <c r="K141" s="28"/>
-      <c r="L141" s="28"/>
+      <c r="K141" s="28">
+        <v>1</v>
+      </c>
+      <c r="L141" s="28">
+        <v>1</v>
+      </c>
       <c r="M141" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="142" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" ht="15.75">
       <c r="A142" s="30">
         <v>500</v>
       </c>
@@ -14229,14 +14510,18 @@
       <c r="J142" s="28">
         <v>1</v>
       </c>
-      <c r="K142" s="28"/>
-      <c r="L142" s="28"/>
+      <c r="K142" s="28">
+        <v>1</v>
+      </c>
+      <c r="L142" s="28">
+        <v>1</v>
+      </c>
       <c r="M142" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="143" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" customFormat="1" ht="15.75">
       <c r="A143" s="2">
         <v>500</v>
       </c>
@@ -14273,7 +14558,7 @@
       <c r="P143" s="38"/>
       <c r="Q143" s="27"/>
     </row>
-    <row r="144" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="144" spans="1:17" customFormat="1" ht="15.75">
       <c r="A144" s="2">
         <v>500</v>
       </c>
@@ -14312,7 +14597,7 @@
       <c r="P144" s="38"/>
       <c r="Q144" s="27"/>
     </row>
-    <row r="145" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="145" spans="1:17" customFormat="1" ht="15.75">
       <c r="A145" s="2">
         <v>500</v>
       </c>
@@ -14351,7 +14636,7 @@
       <c r="P145" s="38"/>
       <c r="Q145" s="27"/>
     </row>
-    <row r="146" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="146" spans="1:17" customFormat="1" ht="15.75">
       <c r="A146" s="2">
         <v>500</v>
       </c>
@@ -14390,7 +14675,7 @@
       <c r="P146" s="38"/>
       <c r="Q146" s="27"/>
     </row>
-    <row r="147" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="147" spans="1:17" customFormat="1" ht="15.75">
       <c r="A147" s="2">
         <v>500</v>
       </c>
@@ -14429,7 +14714,7 @@
       <c r="P147" s="38"/>
       <c r="Q147" s="27"/>
     </row>
-    <row r="148" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="148" spans="1:17" customFormat="1" ht="15.75">
       <c r="A148" s="2">
         <v>500</v>
       </c>
@@ -14468,7 +14753,7 @@
       <c r="P148" s="38"/>
       <c r="Q148" s="27"/>
     </row>
-    <row r="149" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="149" spans="1:17" customFormat="1" ht="15.75">
       <c r="A149" s="2">
         <v>500</v>
       </c>
@@ -14507,7 +14792,7 @@
       <c r="P149" s="38"/>
       <c r="Q149" s="27"/>
     </row>
-    <row r="150" spans="1:17" ht="15.75" hidden="1">
+    <row r="150" spans="1:17" ht="15.75">
       <c r="A150" s="30">
         <v>500</v>
       </c>
@@ -14544,7 +14829,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="151" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="151" spans="1:17" customFormat="1" ht="15.75">
       <c r="A151" s="2">
         <v>600</v>
       </c>
@@ -14576,18 +14861,22 @@
       <c r="J151" s="10">
         <v>1</v>
       </c>
-      <c r="K151" s="10"/>
-      <c r="L151" s="10"/>
+      <c r="K151" s="28">
+        <v>1</v>
+      </c>
+      <c r="L151" s="28">
+        <v>1</v>
+      </c>
       <c r="M151" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N151" s="38"/>
       <c r="O151" s="38"/>
       <c r="P151" s="38"/>
       <c r="Q151" s="27"/>
     </row>
-    <row r="152" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="152" spans="1:17" customFormat="1" ht="15.75">
       <c r="A152" s="2">
         <v>600</v>
       </c>
@@ -14619,18 +14908,22 @@
       <c r="J152" s="10">
         <v>1</v>
       </c>
-      <c r="K152" s="10"/>
-      <c r="L152" s="10"/>
+      <c r="K152" s="28">
+        <v>1</v>
+      </c>
+      <c r="L152" s="28">
+        <v>1</v>
+      </c>
       <c r="M152" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N152" s="38"/>
       <c r="O152" s="38"/>
       <c r="P152" s="38"/>
       <c r="Q152" s="27"/>
     </row>
-    <row r="153" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="153" spans="1:17" customFormat="1" ht="15.75">
       <c r="A153" s="2">
         <v>600</v>
       </c>
@@ -14662,18 +14955,22 @@
       <c r="J153" s="10">
         <v>1</v>
       </c>
-      <c r="K153" s="10"/>
-      <c r="L153" s="10"/>
+      <c r="K153" s="28">
+        <v>1</v>
+      </c>
+      <c r="L153" s="28">
+        <v>1</v>
+      </c>
       <c r="M153" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N153" s="38"/>
       <c r="O153" s="38"/>
       <c r="P153" s="38"/>
       <c r="Q153" s="27"/>
     </row>
-    <row r="154" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="154" spans="1:17" customFormat="1" ht="15.75">
       <c r="A154" s="2">
         <v>600</v>
       </c>
@@ -14705,18 +15002,22 @@
       <c r="J154" s="10">
         <v>1</v>
       </c>
-      <c r="K154" s="10"/>
-      <c r="L154" s="10"/>
+      <c r="K154" s="28">
+        <v>1</v>
+      </c>
+      <c r="L154" s="28">
+        <v>1</v>
+      </c>
       <c r="M154" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N154" s="38"/>
       <c r="O154" s="38"/>
       <c r="P154" s="38"/>
       <c r="Q154" s="27"/>
     </row>
-    <row r="155" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="155" spans="1:17" customFormat="1" ht="15.75">
       <c r="A155" s="2">
         <v>600</v>
       </c>
@@ -14748,18 +15049,22 @@
       <c r="J155" s="10">
         <v>1</v>
       </c>
-      <c r="K155" s="10"/>
-      <c r="L155" s="10"/>
+      <c r="K155" s="28">
+        <v>1</v>
+      </c>
+      <c r="L155" s="28">
+        <v>1</v>
+      </c>
       <c r="M155" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N155" s="38"/>
       <c r="O155" s="38"/>
       <c r="P155" s="38"/>
       <c r="Q155" s="27"/>
     </row>
-    <row r="156" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="156" spans="1:17" customFormat="1" ht="15.75">
       <c r="A156" s="2">
         <v>600</v>
       </c>
@@ -14791,18 +15096,22 @@
       <c r="J156" s="10">
         <v>1</v>
       </c>
-      <c r="K156" s="10"/>
-      <c r="L156" s="10"/>
+      <c r="K156" s="28">
+        <v>1</v>
+      </c>
+      <c r="L156" s="28">
+        <v>1</v>
+      </c>
       <c r="M156" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N156" s="38"/>
       <c r="O156" s="38"/>
       <c r="P156" s="38"/>
       <c r="Q156" s="27"/>
     </row>
-    <row r="157" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="157" spans="1:17" customFormat="1" ht="15.75">
       <c r="A157" s="2">
         <v>600</v>
       </c>
@@ -14834,18 +15143,22 @@
       <c r="J157" s="10">
         <v>1</v>
       </c>
-      <c r="K157" s="10"/>
-      <c r="L157" s="10"/>
+      <c r="K157" s="28">
+        <v>1</v>
+      </c>
+      <c r="L157" s="28">
+        <v>1</v>
+      </c>
       <c r="M157" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N157" s="38"/>
       <c r="O157" s="38"/>
       <c r="P157" s="38"/>
       <c r="Q157" s="27"/>
     </row>
-    <row r="158" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="158" spans="1:17" customFormat="1" ht="15.75">
       <c r="A158" s="2">
         <v>600</v>
       </c>
@@ -14877,18 +15190,22 @@
       <c r="J158" s="10">
         <v>1</v>
       </c>
-      <c r="K158" s="10"/>
-      <c r="L158" s="10"/>
+      <c r="K158" s="28">
+        <v>1</v>
+      </c>
+      <c r="L158" s="28">
+        <v>1</v>
+      </c>
       <c r="M158" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N158" s="38"/>
       <c r="O158" s="38"/>
       <c r="P158" s="38"/>
       <c r="Q158" s="27"/>
     </row>
-    <row r="159" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="159" spans="1:17" customFormat="1" ht="15.75">
       <c r="A159" s="2">
         <v>600</v>
       </c>
@@ -14920,18 +15237,22 @@
       <c r="J159" s="10">
         <v>1</v>
       </c>
-      <c r="K159" s="10"/>
-      <c r="L159" s="10"/>
+      <c r="K159" s="28">
+        <v>1</v>
+      </c>
+      <c r="L159" s="28">
+        <v>1</v>
+      </c>
       <c r="M159" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N159" s="38"/>
       <c r="O159" s="38"/>
       <c r="P159" s="38"/>
       <c r="Q159" s="27"/>
     </row>
-    <row r="160" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="160" spans="1:17" customFormat="1" ht="15.75">
       <c r="A160" s="2">
         <v>600</v>
       </c>
@@ -14963,18 +15284,22 @@
       <c r="J160" s="10">
         <v>1</v>
       </c>
-      <c r="K160" s="10"/>
-      <c r="L160" s="10"/>
+      <c r="K160" s="28">
+        <v>1</v>
+      </c>
+      <c r="L160" s="28">
+        <v>1</v>
+      </c>
       <c r="M160" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N160" s="38"/>
       <c r="O160" s="38"/>
       <c r="P160" s="38"/>
       <c r="Q160" s="27"/>
     </row>
-    <row r="161" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="161" spans="1:17" customFormat="1" ht="15.75">
       <c r="A161" s="2">
         <v>600</v>
       </c>
@@ -15006,18 +15331,22 @@
       <c r="J161" s="10">
         <v>1</v>
       </c>
-      <c r="K161" s="10"/>
-      <c r="L161" s="10"/>
+      <c r="K161" s="28">
+        <v>1</v>
+      </c>
+      <c r="L161" s="28">
+        <v>1</v>
+      </c>
       <c r="M161" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N161" s="38"/>
       <c r="O161" s="38"/>
       <c r="P161" s="38"/>
       <c r="Q161" s="27"/>
     </row>
-    <row r="162" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="162" spans="1:17" customFormat="1" ht="15.75">
       <c r="A162" s="2">
         <v>600</v>
       </c>
@@ -15049,18 +15378,22 @@
       <c r="J162" s="10">
         <v>1</v>
       </c>
-      <c r="K162" s="10"/>
-      <c r="L162" s="10"/>
+      <c r="K162" s="28">
+        <v>1</v>
+      </c>
+      <c r="L162" s="28">
+        <v>1</v>
+      </c>
       <c r="M162" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N162" s="38"/>
       <c r="O162" s="38"/>
       <c r="P162" s="38"/>
       <c r="Q162" s="27"/>
     </row>
-    <row r="163" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="163" spans="1:17" customFormat="1" ht="15.75">
       <c r="A163" s="2">
         <v>600</v>
       </c>
@@ -15092,18 +15425,22 @@
       <c r="J163" s="10">
         <v>1</v>
       </c>
-      <c r="K163" s="10"/>
-      <c r="L163" s="10"/>
+      <c r="K163" s="28">
+        <v>1</v>
+      </c>
+      <c r="L163" s="28">
+        <v>1</v>
+      </c>
       <c r="M163" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N163" s="38"/>
       <c r="O163" s="38"/>
       <c r="P163" s="38"/>
       <c r="Q163" s="27"/>
     </row>
-    <row r="164" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="164" spans="1:17" customFormat="1" ht="15.75">
       <c r="A164" s="2">
         <v>600</v>
       </c>
@@ -15135,18 +15472,22 @@
       <c r="J164" s="10">
         <v>1</v>
       </c>
-      <c r="K164" s="10"/>
-      <c r="L164" s="10"/>
+      <c r="K164" s="28">
+        <v>1</v>
+      </c>
+      <c r="L164" s="28">
+        <v>1</v>
+      </c>
       <c r="M164" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N164" s="38"/>
       <c r="O164" s="38"/>
       <c r="P164" s="38"/>
       <c r="Q164" s="27"/>
     </row>
-    <row r="165" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="165" spans="1:17" customFormat="1" ht="15.75">
       <c r="A165" s="2">
         <v>600</v>
       </c>
@@ -15187,7 +15528,7 @@
       <c r="P165" s="38"/>
       <c r="Q165" s="27"/>
     </row>
-    <row r="166" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="166" spans="1:17" customFormat="1" ht="15.75">
       <c r="A166" s="2">
         <v>600</v>
       </c>
@@ -15228,7 +15569,7 @@
       <c r="P166" s="38"/>
       <c r="Q166" s="27"/>
     </row>
-    <row r="167" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="167" spans="1:17" customFormat="1" ht="15.75">
       <c r="A167" s="2">
         <v>600</v>
       </c>
@@ -15269,7 +15610,7 @@
       <c r="P167" s="38"/>
       <c r="Q167" s="27"/>
     </row>
-    <row r="168" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="168" spans="1:17" customFormat="1" ht="15.75">
       <c r="A168" s="2">
         <v>600</v>
       </c>
@@ -15310,7 +15651,7 @@
       <c r="P168" s="38"/>
       <c r="Q168" s="27"/>
     </row>
-    <row r="169" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="169" spans="1:17" customFormat="1" ht="15.75">
       <c r="A169" s="2">
         <v>600</v>
       </c>
@@ -15351,7 +15692,7 @@
       <c r="P169" s="38"/>
       <c r="Q169" s="27"/>
     </row>
-    <row r="170" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="170" spans="1:17" customFormat="1" ht="15.75">
       <c r="A170" s="2">
         <v>600</v>
       </c>
@@ -15392,7 +15733,7 @@
       <c r="P170" s="38"/>
       <c r="Q170" s="27"/>
     </row>
-    <row r="171" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="171" spans="1:17" customFormat="1" ht="15.75">
       <c r="A171" s="2">
         <v>600</v>
       </c>
@@ -15424,18 +15765,22 @@
       <c r="J171" s="10">
         <v>1</v>
       </c>
-      <c r="K171" s="10"/>
-      <c r="L171" s="10"/>
+      <c r="K171" s="28">
+        <v>1</v>
+      </c>
+      <c r="L171" s="28">
+        <v>1</v>
+      </c>
       <c r="M171" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N171" s="38"/>
       <c r="O171" s="38"/>
       <c r="P171" s="38"/>
       <c r="Q171" s="27"/>
     </row>
-    <row r="172" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="172" spans="1:17" customFormat="1" ht="15.75">
       <c r="A172" s="2">
         <v>600</v>
       </c>
@@ -15467,18 +15812,22 @@
       <c r="J172" s="10">
         <v>1</v>
       </c>
-      <c r="K172" s="10"/>
-      <c r="L172" s="10"/>
+      <c r="K172" s="28">
+        <v>1</v>
+      </c>
+      <c r="L172" s="28">
+        <v>1</v>
+      </c>
       <c r="M172" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N172" s="38"/>
       <c r="O172" s="38"/>
       <c r="P172" s="38"/>
       <c r="Q172" s="27"/>
     </row>
-    <row r="173" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="173" spans="1:17" customFormat="1" ht="15.75">
       <c r="A173" s="2">
         <v>600</v>
       </c>
@@ -15510,18 +15859,22 @@
       <c r="J173" s="10">
         <v>1</v>
       </c>
-      <c r="K173" s="10"/>
-      <c r="L173" s="10"/>
+      <c r="K173" s="28">
+        <v>1</v>
+      </c>
+      <c r="L173" s="28">
+        <v>1</v>
+      </c>
       <c r="M173" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N173" s="38"/>
       <c r="O173" s="38"/>
       <c r="P173" s="38"/>
       <c r="Q173" s="27"/>
     </row>
-    <row r="174" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="174" spans="1:17" customFormat="1" ht="15.75">
       <c r="A174" s="2">
         <v>600</v>
       </c>
@@ -15553,18 +15906,22 @@
       <c r="J174" s="10">
         <v>1</v>
       </c>
-      <c r="K174" s="10"/>
-      <c r="L174" s="10"/>
+      <c r="K174" s="28">
+        <v>1</v>
+      </c>
+      <c r="L174" s="28">
+        <v>1</v>
+      </c>
       <c r="M174" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N174" s="38"/>
       <c r="O174" s="38"/>
       <c r="P174" s="38"/>
       <c r="Q174" s="27"/>
     </row>
-    <row r="175" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="175" spans="1:17" customFormat="1" ht="15.75">
       <c r="A175" s="2">
         <v>600</v>
       </c>
@@ -15596,18 +15953,22 @@
       <c r="J175" s="10">
         <v>1</v>
       </c>
-      <c r="K175" s="10"/>
-      <c r="L175" s="10"/>
+      <c r="K175" s="28">
+        <v>1</v>
+      </c>
+      <c r="L175" s="28">
+        <v>1</v>
+      </c>
       <c r="M175" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N175" s="38"/>
       <c r="O175" s="38"/>
       <c r="P175" s="38"/>
       <c r="Q175" s="27"/>
     </row>
-    <row r="176" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="176" spans="1:17" customFormat="1" ht="15.75">
       <c r="A176" s="2">
         <v>600</v>
       </c>
@@ -15639,18 +16000,22 @@
       <c r="J176" s="10">
         <v>1</v>
       </c>
-      <c r="K176" s="10"/>
-      <c r="L176" s="10"/>
+      <c r="K176" s="28">
+        <v>1</v>
+      </c>
+      <c r="L176" s="28">
+        <v>1</v>
+      </c>
       <c r="M176" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N176" s="38"/>
       <c r="O176" s="38"/>
       <c r="P176" s="38"/>
       <c r="Q176" s="27"/>
     </row>
-    <row r="177" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="177" spans="1:17" customFormat="1" ht="15.75">
       <c r="A177" s="2">
         <v>600</v>
       </c>
@@ -15682,18 +16047,22 @@
       <c r="J177" s="10">
         <v>1</v>
       </c>
-      <c r="K177" s="10"/>
-      <c r="L177" s="10"/>
+      <c r="K177" s="28">
+        <v>1</v>
+      </c>
+      <c r="L177" s="28">
+        <v>1</v>
+      </c>
       <c r="M177" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N177" s="38"/>
       <c r="O177" s="38"/>
       <c r="P177" s="38"/>
       <c r="Q177" s="27"/>
     </row>
-    <row r="178" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="178" spans="1:17" customFormat="1" ht="15.75">
       <c r="A178" s="2">
         <v>600</v>
       </c>
@@ -15725,18 +16094,22 @@
       <c r="J178" s="10">
         <v>1</v>
       </c>
-      <c r="K178" s="10"/>
-      <c r="L178" s="10"/>
+      <c r="K178" s="28">
+        <v>1</v>
+      </c>
+      <c r="L178" s="28">
+        <v>1</v>
+      </c>
       <c r="M178" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N178" s="38"/>
       <c r="O178" s="38"/>
       <c r="P178" s="38"/>
       <c r="Q178" s="27"/>
     </row>
-    <row r="179" spans="1:17" ht="15.75" hidden="1">
+    <row r="179" spans="1:17" ht="15.75">
       <c r="A179" s="30">
         <v>600</v>
       </c>
@@ -15768,14 +16141,18 @@
       <c r="J179" s="28">
         <v>1</v>
       </c>
-      <c r="K179" s="28"/>
-      <c r="L179" s="28"/>
+      <c r="K179" s="28">
+        <v>1</v>
+      </c>
+      <c r="L179" s="28">
+        <v>1</v>
+      </c>
       <c r="M179" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="180" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" ht="15.75">
       <c r="A180" s="30">
         <v>600</v>
       </c>
@@ -15807,14 +16184,18 @@
       <c r="J180" s="28">
         <v>1</v>
       </c>
-      <c r="K180" s="28"/>
-      <c r="L180" s="28"/>
+      <c r="K180" s="28">
+        <v>1</v>
+      </c>
+      <c r="L180" s="28">
+        <v>1</v>
+      </c>
       <c r="M180" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="181" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" ht="15.75">
       <c r="A181" s="30">
         <v>600</v>
       </c>
@@ -15846,14 +16227,18 @@
       <c r="J181" s="28">
         <v>1</v>
       </c>
-      <c r="K181" s="28"/>
-      <c r="L181" s="28"/>
+      <c r="K181" s="28">
+        <v>1</v>
+      </c>
+      <c r="L181" s="28">
+        <v>1</v>
+      </c>
       <c r="M181" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="182" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" ht="15.75">
       <c r="A182" s="30">
         <v>600</v>
       </c>
@@ -15885,14 +16270,18 @@
       <c r="J182" s="28">
         <v>1</v>
       </c>
-      <c r="K182" s="28"/>
-      <c r="L182" s="28"/>
+      <c r="K182" s="28">
+        <v>1</v>
+      </c>
+      <c r="L182" s="28">
+        <v>1</v>
+      </c>
       <c r="M182" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="183" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" ht="15.75">
       <c r="A183" s="30">
         <v>600</v>
       </c>
@@ -15924,14 +16313,18 @@
       <c r="J183" s="28">
         <v>1</v>
       </c>
-      <c r="K183" s="28"/>
-      <c r="L183" s="28"/>
+      <c r="K183" s="28">
+        <v>1</v>
+      </c>
+      <c r="L183" s="28">
+        <v>1</v>
+      </c>
       <c r="M183" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="184" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" ht="15.75">
       <c r="A184" s="30">
         <v>600</v>
       </c>
@@ -15963,14 +16356,18 @@
       <c r="J184" s="28">
         <v>1</v>
       </c>
-      <c r="K184" s="28"/>
-      <c r="L184" s="28"/>
+      <c r="K184" s="28">
+        <v>1</v>
+      </c>
+      <c r="L184" s="28">
+        <v>1</v>
+      </c>
       <c r="M184" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="185" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17" ht="15.75">
       <c r="A185" s="30">
         <v>600</v>
       </c>
@@ -16002,14 +16399,18 @@
       <c r="J185" s="28">
         <v>1</v>
       </c>
-      <c r="K185" s="28"/>
-      <c r="L185" s="28"/>
+      <c r="K185" s="28">
+        <v>1</v>
+      </c>
+      <c r="L185" s="28">
+        <v>1</v>
+      </c>
       <c r="M185" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="186" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:17" ht="15.75">
       <c r="A186" s="30">
         <v>600</v>
       </c>
@@ -16041,14 +16442,18 @@
       <c r="J186" s="28">
         <v>1</v>
       </c>
-      <c r="K186" s="28"/>
-      <c r="L186" s="28"/>
+      <c r="K186" s="28">
+        <v>1</v>
+      </c>
+      <c r="L186" s="28">
+        <v>1</v>
+      </c>
       <c r="M186" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="187" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17" ht="15.75">
       <c r="A187" s="30">
         <v>600</v>
       </c>
@@ -16080,14 +16485,18 @@
       <c r="J187" s="28">
         <v>1</v>
       </c>
-      <c r="K187" s="28"/>
-      <c r="L187" s="28"/>
+      <c r="K187" s="28">
+        <v>1</v>
+      </c>
+      <c r="L187" s="28">
+        <v>1</v>
+      </c>
       <c r="M187" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="188" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17" ht="15.75">
       <c r="A188" s="30">
         <v>600</v>
       </c>
@@ -16119,14 +16528,18 @@
       <c r="J188" s="28">
         <v>1</v>
       </c>
-      <c r="K188" s="28"/>
-      <c r="L188" s="28"/>
+      <c r="K188" s="28">
+        <v>1</v>
+      </c>
+      <c r="L188" s="28">
+        <v>1</v>
+      </c>
       <c r="M188" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="189" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" ht="15.75">
       <c r="A189" s="30">
         <v>600</v>
       </c>
@@ -16158,14 +16571,18 @@
       <c r="J189" s="28">
         <v>1</v>
       </c>
-      <c r="K189" s="28"/>
-      <c r="L189" s="28"/>
+      <c r="K189" s="28">
+        <v>1</v>
+      </c>
+      <c r="L189" s="28">
+        <v>1</v>
+      </c>
       <c r="M189" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="190" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17" ht="15.75">
       <c r="A190" s="30">
         <v>600</v>
       </c>
@@ -16197,14 +16614,18 @@
       <c r="J190" s="28">
         <v>1</v>
       </c>
-      <c r="K190" s="28"/>
-      <c r="L190" s="28"/>
+      <c r="K190" s="28">
+        <v>1</v>
+      </c>
+      <c r="L190" s="28">
+        <v>1</v>
+      </c>
       <c r="M190" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="191" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" ht="15.75">
       <c r="A191" s="30">
         <v>600</v>
       </c>
@@ -16236,14 +16657,18 @@
       <c r="J191" s="28">
         <v>1</v>
       </c>
-      <c r="K191" s="28"/>
-      <c r="L191" s="28"/>
+      <c r="K191" s="28">
+        <v>1</v>
+      </c>
+      <c r="L191" s="28">
+        <v>1</v>
+      </c>
       <c r="M191" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="192" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" ht="15.75">
       <c r="A192" s="30">
         <v>600</v>
       </c>
@@ -16275,14 +16700,18 @@
       <c r="J192" s="28">
         <v>1</v>
       </c>
-      <c r="K192" s="28"/>
-      <c r="L192" s="28"/>
+      <c r="K192" s="28">
+        <v>1</v>
+      </c>
+      <c r="L192" s="28">
+        <v>1</v>
+      </c>
       <c r="M192" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="193" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" ht="15.75">
       <c r="A193" s="30">
         <v>600</v>
       </c>
@@ -16314,14 +16743,18 @@
       <c r="J193" s="28">
         <v>1</v>
       </c>
-      <c r="K193" s="28"/>
-      <c r="L193" s="28"/>
+      <c r="K193" s="28">
+        <v>1</v>
+      </c>
+      <c r="L193" s="28">
+        <v>1</v>
+      </c>
       <c r="M193" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="194" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" ht="15.75">
       <c r="A194" s="30">
         <v>600</v>
       </c>
@@ -16353,14 +16786,18 @@
       <c r="J194" s="28">
         <v>1</v>
       </c>
-      <c r="K194" s="28"/>
-      <c r="L194" s="28"/>
+      <c r="K194" s="28">
+        <v>1</v>
+      </c>
+      <c r="L194" s="28">
+        <v>1</v>
+      </c>
       <c r="M194" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="195" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" ht="15.75">
       <c r="A195" s="30">
         <v>600</v>
       </c>
@@ -16392,14 +16829,18 @@
       <c r="J195" s="28">
         <v>1</v>
       </c>
-      <c r="K195" s="28"/>
-      <c r="L195" s="28"/>
+      <c r="K195" s="28">
+        <v>1</v>
+      </c>
+      <c r="L195" s="28">
+        <v>1</v>
+      </c>
       <c r="M195" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="196" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17" ht="15.75">
       <c r="A196" s="30">
         <v>600</v>
       </c>
@@ -16431,14 +16872,18 @@
       <c r="J196" s="28">
         <v>1</v>
       </c>
-      <c r="K196" s="28"/>
-      <c r="L196" s="28"/>
+      <c r="K196" s="28">
+        <v>1</v>
+      </c>
+      <c r="L196" s="28">
+        <v>1</v>
+      </c>
       <c r="M196" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="197" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17" ht="15.75">
       <c r="A197" s="30">
         <v>600</v>
       </c>
@@ -16470,14 +16915,18 @@
       <c r="J197" s="28">
         <v>1</v>
       </c>
-      <c r="K197" s="28"/>
-      <c r="L197" s="28"/>
+      <c r="K197" s="28">
+        <v>1</v>
+      </c>
+      <c r="L197" s="28">
+        <v>1</v>
+      </c>
       <c r="M197" s="28">
         <f t="shared" si="4"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="198" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:17" customFormat="1" ht="15.75">
       <c r="A198" s="2">
         <v>600</v>
       </c>
@@ -16509,18 +16958,22 @@
       <c r="J198" s="10">
         <v>1</v>
       </c>
-      <c r="K198" s="10"/>
-      <c r="L198" s="10"/>
+      <c r="K198" s="28">
+        <v>1</v>
+      </c>
+      <c r="L198" s="28">
+        <v>1</v>
+      </c>
       <c r="M198" s="10">
         <f t="shared" si="4"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N198" s="38"/>
       <c r="O198" s="38"/>
       <c r="P198" s="38"/>
       <c r="Q198" s="27"/>
     </row>
-    <row r="199" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="199" spans="1:17" customFormat="1" ht="15.75">
       <c r="A199" s="2">
         <v>600</v>
       </c>
@@ -16557,7 +17010,7 @@
       <c r="P199" s="38"/>
       <c r="Q199" s="27"/>
     </row>
-    <row r="200" spans="1:17" ht="15.75" hidden="1">
+    <row r="200" spans="1:17" ht="15.75">
       <c r="A200" s="30">
         <v>700</v>
       </c>
@@ -16589,14 +17042,18 @@
       <c r="J200" s="28">
         <v>1</v>
       </c>
-      <c r="K200" s="28"/>
-      <c r="L200" s="28"/>
+      <c r="K200" s="28">
+        <v>1</v>
+      </c>
+      <c r="L200" s="28">
+        <v>1</v>
+      </c>
       <c r="M200" s="28">
         <f t="shared" ref="M200:M263" si="5">SUMPRODUCT(H200:L200,$AA$2:$AE$2)</f>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="201" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" customFormat="1" ht="15.75">
       <c r="A201" s="2">
         <v>700</v>
       </c>
@@ -16633,7 +17090,7 @@
       <c r="P201" s="38"/>
       <c r="Q201" s="27"/>
     </row>
-    <row r="202" spans="1:17" ht="15.75" hidden="1">
+    <row r="202" spans="1:17" ht="15.75">
       <c r="A202" s="30">
         <v>700</v>
       </c>
@@ -16665,14 +17122,18 @@
       <c r="J202" s="28">
         <v>1</v>
       </c>
-      <c r="K202" s="28"/>
-      <c r="L202" s="28"/>
+      <c r="K202" s="28">
+        <v>1</v>
+      </c>
+      <c r="L202" s="28">
+        <v>1</v>
+      </c>
       <c r="M202" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="203" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:17" ht="15.75">
       <c r="A203" s="30">
         <v>700</v>
       </c>
@@ -16704,14 +17165,18 @@
       <c r="J203" s="28">
         <v>1</v>
       </c>
-      <c r="K203" s="28"/>
-      <c r="L203" s="28"/>
+      <c r="K203" s="28">
+        <v>1</v>
+      </c>
+      <c r="L203" s="28">
+        <v>1</v>
+      </c>
       <c r="M203" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="204" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17" customFormat="1" ht="15.75">
       <c r="A204" s="2">
         <v>700</v>
       </c>
@@ -16743,18 +17208,22 @@
       <c r="J204" s="10">
         <v>1</v>
       </c>
-      <c r="K204" s="10"/>
-      <c r="L204" s="10"/>
+      <c r="K204" s="28">
+        <v>1</v>
+      </c>
+      <c r="L204" s="28">
+        <v>1</v>
+      </c>
       <c r="M204" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N204" s="38"/>
       <c r="O204" s="38"/>
       <c r="P204" s="38"/>
       <c r="Q204" s="27"/>
     </row>
-    <row r="205" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="205" spans="1:17" customFormat="1" ht="15.75">
       <c r="A205" s="2">
         <v>700</v>
       </c>
@@ -16786,18 +17255,22 @@
       <c r="J205" s="10">
         <v>1</v>
       </c>
-      <c r="K205" s="10"/>
-      <c r="L205" s="10"/>
+      <c r="K205" s="28">
+        <v>1</v>
+      </c>
+      <c r="L205" s="28">
+        <v>1</v>
+      </c>
       <c r="M205" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N205" s="38"/>
       <c r="O205" s="38"/>
       <c r="P205" s="38"/>
       <c r="Q205" s="27"/>
     </row>
-    <row r="206" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="206" spans="1:17" customFormat="1" ht="15.75">
       <c r="A206" s="2">
         <v>700</v>
       </c>
@@ -16829,18 +17302,22 @@
       <c r="J206" s="10">
         <v>1</v>
       </c>
-      <c r="K206" s="10"/>
-      <c r="L206" s="10"/>
+      <c r="K206" s="28">
+        <v>1</v>
+      </c>
+      <c r="L206" s="28">
+        <v>1</v>
+      </c>
       <c r="M206" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N206" s="38"/>
       <c r="O206" s="38"/>
       <c r="P206" s="38"/>
       <c r="Q206" s="27"/>
     </row>
-    <row r="207" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="207" spans="1:17" customFormat="1" ht="15.75">
       <c r="A207" s="2">
         <v>700</v>
       </c>
@@ -16872,18 +17349,22 @@
       <c r="J207" s="10">
         <v>1</v>
       </c>
-      <c r="K207" s="10"/>
-      <c r="L207" s="10"/>
+      <c r="K207" s="28">
+        <v>1</v>
+      </c>
+      <c r="L207" s="28">
+        <v>1</v>
+      </c>
       <c r="M207" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N207" s="38"/>
       <c r="O207" s="38"/>
       <c r="P207" s="38"/>
       <c r="Q207" s="27"/>
     </row>
-    <row r="208" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="208" spans="1:17" customFormat="1" ht="15.75">
       <c r="A208" s="2">
         <v>700</v>
       </c>
@@ -16915,18 +17396,22 @@
       <c r="J208" s="10">
         <v>1</v>
       </c>
-      <c r="K208" s="10"/>
-      <c r="L208" s="10"/>
+      <c r="K208" s="28">
+        <v>1</v>
+      </c>
+      <c r="L208" s="28">
+        <v>1</v>
+      </c>
       <c r="M208" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N208" s="38"/>
       <c r="O208" s="38"/>
       <c r="P208" s="38"/>
       <c r="Q208" s="27"/>
     </row>
-    <row r="209" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="209" spans="1:17" customFormat="1" ht="15.75">
       <c r="A209" s="2">
         <v>700</v>
       </c>
@@ -16958,18 +17443,22 @@
       <c r="J209" s="10">
         <v>1</v>
       </c>
-      <c r="K209" s="10"/>
-      <c r="L209" s="10"/>
+      <c r="K209" s="28">
+        <v>1</v>
+      </c>
+      <c r="L209" s="28">
+        <v>1</v>
+      </c>
       <c r="M209" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N209" s="38"/>
       <c r="O209" s="38"/>
       <c r="P209" s="38"/>
       <c r="Q209" s="27"/>
     </row>
-    <row r="210" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="210" spans="1:17" customFormat="1" ht="15.75">
       <c r="A210" s="2">
         <v>700</v>
       </c>
@@ -17001,18 +17490,22 @@
       <c r="J210" s="10">
         <v>1</v>
       </c>
-      <c r="K210" s="10"/>
-      <c r="L210" s="10"/>
+      <c r="K210" s="28">
+        <v>1</v>
+      </c>
+      <c r="L210" s="28">
+        <v>1</v>
+      </c>
       <c r="M210" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N210" s="38"/>
       <c r="O210" s="38"/>
       <c r="P210" s="38"/>
       <c r="Q210" s="27"/>
     </row>
-    <row r="211" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="211" spans="1:17" customFormat="1" ht="15.75">
       <c r="A211" s="2">
         <v>700</v>
       </c>
@@ -17044,18 +17537,22 @@
       <c r="J211" s="10">
         <v>1</v>
       </c>
-      <c r="K211" s="10"/>
-      <c r="L211" s="10"/>
+      <c r="K211" s="28">
+        <v>1</v>
+      </c>
+      <c r="L211" s="28">
+        <v>1</v>
+      </c>
       <c r="M211" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N211" s="38"/>
       <c r="O211" s="38"/>
       <c r="P211" s="38"/>
       <c r="Q211" s="27"/>
     </row>
-    <row r="212" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="212" spans="1:17" customFormat="1" ht="15.75">
       <c r="A212" s="2">
         <v>700</v>
       </c>
@@ -17087,18 +17584,22 @@
       <c r="J212" s="10">
         <v>1</v>
       </c>
-      <c r="K212" s="10"/>
-      <c r="L212" s="10"/>
+      <c r="K212" s="28">
+        <v>1</v>
+      </c>
+      <c r="L212" s="28">
+        <v>1</v>
+      </c>
       <c r="M212" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N212" s="38"/>
       <c r="O212" s="38"/>
       <c r="P212" s="38"/>
       <c r="Q212" s="27"/>
     </row>
-    <row r="213" spans="1:17" ht="15.75" hidden="1">
+    <row r="213" spans="1:17" ht="15.75">
       <c r="A213" s="30">
         <v>700</v>
       </c>
@@ -17130,14 +17631,18 @@
       <c r="J213" s="28">
         <v>1</v>
       </c>
-      <c r="K213" s="28"/>
-      <c r="L213" s="28"/>
+      <c r="K213" s="28">
+        <v>1</v>
+      </c>
+      <c r="L213" s="28">
+        <v>1</v>
+      </c>
       <c r="M213" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="214" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:17" ht="15.75">
       <c r="A214" s="30">
         <v>700</v>
       </c>
@@ -17169,14 +17674,18 @@
       <c r="J214" s="28">
         <v>1</v>
       </c>
-      <c r="K214" s="28"/>
-      <c r="L214" s="28"/>
+      <c r="K214" s="28">
+        <v>1</v>
+      </c>
+      <c r="L214" s="28">
+        <v>1</v>
+      </c>
       <c r="M214" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="215" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:17" ht="15.75">
       <c r="A215" s="30">
         <v>700</v>
       </c>
@@ -17208,14 +17717,18 @@
       <c r="J215" s="28">
         <v>1</v>
       </c>
-      <c r="K215" s="28"/>
-      <c r="L215" s="28"/>
+      <c r="K215" s="28">
+        <v>1</v>
+      </c>
+      <c r="L215" s="28">
+        <v>1</v>
+      </c>
       <c r="M215" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="216" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" ht="15.75">
       <c r="A216" s="30">
         <v>700</v>
       </c>
@@ -17247,14 +17760,18 @@
       <c r="J216" s="28">
         <v>1</v>
       </c>
-      <c r="K216" s="28"/>
-      <c r="L216" s="28"/>
+      <c r="K216" s="28">
+        <v>1</v>
+      </c>
+      <c r="L216" s="28">
+        <v>1</v>
+      </c>
       <c r="M216" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="217" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" ht="15.75">
       <c r="A217" s="30">
         <v>700</v>
       </c>
@@ -17286,14 +17803,18 @@
       <c r="J217" s="28">
         <v>1</v>
       </c>
-      <c r="K217" s="28"/>
-      <c r="L217" s="28"/>
+      <c r="K217" s="28">
+        <v>1</v>
+      </c>
+      <c r="L217" s="28">
+        <v>1</v>
+      </c>
       <c r="M217" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="218" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:17" ht="15.75">
       <c r="A218" s="30">
         <v>700</v>
       </c>
@@ -17325,14 +17846,18 @@
       <c r="J218" s="28">
         <v>1</v>
       </c>
-      <c r="K218" s="28"/>
-      <c r="L218" s="28"/>
+      <c r="K218" s="28">
+        <v>1</v>
+      </c>
+      <c r="L218" s="28">
+        <v>1</v>
+      </c>
       <c r="M218" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="219" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" ht="15.75">
       <c r="A219" s="30">
         <v>700</v>
       </c>
@@ -17364,14 +17889,18 @@
       <c r="J219" s="28">
         <v>1</v>
       </c>
-      <c r="K219" s="28"/>
-      <c r="L219" s="28"/>
+      <c r="K219" s="28">
+        <v>1</v>
+      </c>
+      <c r="L219" s="28">
+        <v>1</v>
+      </c>
       <c r="M219" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="220" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:17" ht="15.75">
       <c r="A220" s="30">
         <v>700</v>
       </c>
@@ -17403,14 +17932,18 @@
       <c r="J220" s="28">
         <v>1</v>
       </c>
-      <c r="K220" s="28"/>
-      <c r="L220" s="28"/>
+      <c r="K220" s="28">
+        <v>1</v>
+      </c>
+      <c r="L220" s="28">
+        <v>1</v>
+      </c>
       <c r="M220" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="221" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17" customFormat="1" ht="15.75">
       <c r="A221" s="2">
         <v>700</v>
       </c>
@@ -17442,18 +17975,22 @@
       <c r="J221" s="10">
         <v>1</v>
       </c>
-      <c r="K221" s="10"/>
-      <c r="L221" s="10"/>
+      <c r="K221" s="28">
+        <v>1</v>
+      </c>
+      <c r="L221" s="28">
+        <v>1</v>
+      </c>
       <c r="M221" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N221" s="38"/>
       <c r="O221" s="38"/>
       <c r="P221" s="38"/>
       <c r="Q221" s="27"/>
     </row>
-    <row r="222" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="222" spans="1:17" customFormat="1" ht="15.75">
       <c r="A222" s="2">
         <v>700</v>
       </c>
@@ -17485,18 +18022,22 @@
       <c r="J222" s="10">
         <v>1</v>
       </c>
-      <c r="K222" s="10"/>
-      <c r="L222" s="10"/>
+      <c r="K222" s="28">
+        <v>1</v>
+      </c>
+      <c r="L222" s="28">
+        <v>1</v>
+      </c>
       <c r="M222" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N222" s="38"/>
       <c r="O222" s="38"/>
       <c r="P222" s="38"/>
       <c r="Q222" s="27"/>
     </row>
-    <row r="223" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="223" spans="1:17" customFormat="1" ht="15.75">
       <c r="A223" s="2">
         <v>700</v>
       </c>
@@ -17528,18 +18069,22 @@
       <c r="J223" s="10">
         <v>1</v>
       </c>
-      <c r="K223" s="10"/>
-      <c r="L223" s="10"/>
+      <c r="K223" s="28">
+        <v>1</v>
+      </c>
+      <c r="L223" s="28">
+        <v>1</v>
+      </c>
       <c r="M223" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N223" s="38"/>
       <c r="O223" s="38"/>
       <c r="P223" s="38"/>
       <c r="Q223" s="27"/>
     </row>
-    <row r="224" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="224" spans="1:17" customFormat="1" ht="15.75">
       <c r="A224" s="2">
         <v>700</v>
       </c>
@@ -17580,7 +18125,7 @@
       <c r="P224" s="38"/>
       <c r="Q224" s="27"/>
     </row>
-    <row r="225" spans="1:17" ht="15.75" hidden="1">
+    <row r="225" spans="1:17" ht="15.75">
       <c r="A225" s="30">
         <v>700</v>
       </c>
@@ -17612,14 +18157,18 @@
       <c r="J225" s="28">
         <v>1</v>
       </c>
-      <c r="K225" s="28"/>
-      <c r="L225" s="28"/>
+      <c r="K225" s="28">
+        <v>1</v>
+      </c>
+      <c r="L225" s="28">
+        <v>1</v>
+      </c>
       <c r="M225" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="226" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:17" ht="15.75">
       <c r="A226" s="30">
         <v>700</v>
       </c>
@@ -17651,14 +18200,18 @@
       <c r="J226" s="28">
         <v>1</v>
       </c>
-      <c r="K226" s="28"/>
-      <c r="L226" s="28"/>
+      <c r="K226" s="28">
+        <v>1</v>
+      </c>
+      <c r="L226" s="28">
+        <v>1</v>
+      </c>
       <c r="M226" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="227" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:17" customFormat="1" ht="15.75">
       <c r="A227" s="2">
         <v>700</v>
       </c>
@@ -17690,18 +18243,22 @@
       <c r="J227" s="10">
         <v>1</v>
       </c>
-      <c r="K227" s="10"/>
-      <c r="L227" s="10"/>
+      <c r="K227" s="28">
+        <v>1</v>
+      </c>
+      <c r="L227" s="28">
+        <v>1</v>
+      </c>
       <c r="M227" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N227" s="38"/>
       <c r="O227" s="38"/>
       <c r="P227" s="38"/>
       <c r="Q227" s="27"/>
     </row>
-    <row r="228" spans="1:17" ht="15.75" hidden="1">
+    <row r="228" spans="1:17" ht="15.75">
       <c r="A228" s="30">
         <v>700</v>
       </c>
@@ -17733,14 +18290,18 @@
       <c r="J228" s="28">
         <v>1</v>
       </c>
-      <c r="K228" s="28"/>
-      <c r="L228" s="28"/>
+      <c r="K228" s="28">
+        <v>1</v>
+      </c>
+      <c r="L228" s="28">
+        <v>1</v>
+      </c>
       <c r="M228" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="229" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:17" ht="15.75">
       <c r="A229" s="30">
         <v>700</v>
       </c>
@@ -17772,14 +18333,18 @@
       <c r="J229" s="10">
         <v>1</v>
       </c>
-      <c r="K229" s="28"/>
-      <c r="L229" s="28"/>
+      <c r="K229" s="28">
+        <v>1</v>
+      </c>
+      <c r="L229" s="28">
+        <v>1</v>
+      </c>
       <c r="M229" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="230" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:17" ht="15.75">
       <c r="A230" s="30">
         <v>700</v>
       </c>
@@ -17811,14 +18376,18 @@
       <c r="J230" s="28">
         <v>1</v>
       </c>
-      <c r="K230" s="28"/>
-      <c r="L230" s="28"/>
+      <c r="K230" s="28">
+        <v>1</v>
+      </c>
+      <c r="L230" s="28">
+        <v>1</v>
+      </c>
       <c r="M230" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="231" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" customFormat="1" ht="15.75">
       <c r="A231" s="2">
         <v>700</v>
       </c>
@@ -17850,18 +18419,22 @@
       <c r="J231" s="10">
         <v>1</v>
       </c>
-      <c r="K231" s="10"/>
-      <c r="L231" s="10"/>
+      <c r="K231" s="28">
+        <v>1</v>
+      </c>
+      <c r="L231" s="28">
+        <v>1</v>
+      </c>
       <c r="M231" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N231" s="38"/>
       <c r="O231" s="38"/>
       <c r="P231" s="38"/>
       <c r="Q231" s="27"/>
     </row>
-    <row r="232" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="232" spans="1:17" customFormat="1" ht="15.75">
       <c r="A232" s="2">
         <v>700</v>
       </c>
@@ -17893,18 +18466,22 @@
       <c r="J232" s="10">
         <v>1</v>
       </c>
-      <c r="K232" s="10"/>
-      <c r="L232" s="10"/>
+      <c r="K232" s="28">
+        <v>1</v>
+      </c>
+      <c r="L232" s="28">
+        <v>1</v>
+      </c>
       <c r="M232" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N232" s="38"/>
       <c r="O232" s="38"/>
       <c r="P232" s="38"/>
       <c r="Q232" s="27"/>
     </row>
-    <row r="233" spans="1:17" ht="15.75" hidden="1">
+    <row r="233" spans="1:17" ht="15.75">
       <c r="A233" s="30">
         <v>700</v>
       </c>
@@ -17936,14 +18513,18 @@
       <c r="J233" s="28">
         <v>1</v>
       </c>
-      <c r="K233" s="28"/>
-      <c r="L233" s="28"/>
+      <c r="K233" s="28">
+        <v>1</v>
+      </c>
+      <c r="L233" s="28">
+        <v>1</v>
+      </c>
       <c r="M233" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="234" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:17" customFormat="1" ht="15.75">
       <c r="A234" s="2">
         <v>700</v>
       </c>
@@ -17975,18 +18556,22 @@
       <c r="J234" s="10">
         <v>1</v>
       </c>
-      <c r="K234" s="10"/>
-      <c r="L234" s="10"/>
+      <c r="K234" s="28">
+        <v>1</v>
+      </c>
+      <c r="L234" s="28">
+        <v>1</v>
+      </c>
       <c r="M234" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N234" s="38"/>
       <c r="O234" s="38"/>
       <c r="P234" s="38"/>
       <c r="Q234" s="27"/>
     </row>
-    <row r="235" spans="1:17" ht="15.75" hidden="1">
+    <row r="235" spans="1:17" ht="15.75">
       <c r="A235" s="30">
         <v>700</v>
       </c>
@@ -18018,14 +18603,18 @@
       <c r="J235" s="28">
         <v>1</v>
       </c>
-      <c r="K235" s="28"/>
-      <c r="L235" s="28"/>
+      <c r="K235" s="28">
+        <v>1</v>
+      </c>
+      <c r="L235" s="28">
+        <v>1</v>
+      </c>
       <c r="M235" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="236" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:17" customFormat="1" ht="15.75">
       <c r="A236" s="2">
         <v>700</v>
       </c>
@@ -18057,18 +18646,22 @@
       <c r="J236" s="10">
         <v>1</v>
       </c>
-      <c r="K236" s="10"/>
-      <c r="L236" s="10"/>
+      <c r="K236" s="28">
+        <v>1</v>
+      </c>
+      <c r="L236" s="28">
+        <v>1</v>
+      </c>
       <c r="M236" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N236" s="38"/>
       <c r="O236" s="38"/>
       <c r="P236" s="38"/>
       <c r="Q236" s="27"/>
     </row>
-    <row r="237" spans="1:17" ht="15.75" hidden="1">
+    <row r="237" spans="1:17" ht="15.75">
       <c r="A237" s="30">
         <v>700</v>
       </c>
@@ -18100,14 +18693,18 @@
       <c r="J237" s="28">
         <v>1</v>
       </c>
-      <c r="K237" s="28"/>
-      <c r="L237" s="28"/>
+      <c r="K237" s="28">
+        <v>1</v>
+      </c>
+      <c r="L237" s="28">
+        <v>1</v>
+      </c>
       <c r="M237" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="238" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:17" customFormat="1" ht="15.75">
       <c r="A238" s="2">
         <v>700</v>
       </c>
@@ -18139,18 +18736,22 @@
       <c r="J238" s="10">
         <v>1</v>
       </c>
-      <c r="K238" s="10"/>
-      <c r="L238" s="10"/>
+      <c r="K238" s="28">
+        <v>1</v>
+      </c>
+      <c r="L238" s="28">
+        <v>1</v>
+      </c>
       <c r="M238" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N238" s="38"/>
       <c r="O238" s="38"/>
       <c r="P238" s="38"/>
       <c r="Q238" s="27"/>
     </row>
-    <row r="239" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="239" spans="1:17" customFormat="1" ht="15.75">
       <c r="A239" s="2">
         <v>700</v>
       </c>
@@ -18182,18 +18783,22 @@
       <c r="J239" s="10">
         <v>1</v>
       </c>
-      <c r="K239" s="10"/>
-      <c r="L239" s="10"/>
+      <c r="K239" s="28">
+        <v>1</v>
+      </c>
+      <c r="L239" s="28">
+        <v>1</v>
+      </c>
       <c r="M239" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N239" s="38"/>
       <c r="O239" s="38"/>
       <c r="P239" s="38"/>
       <c r="Q239" s="27"/>
     </row>
-    <row r="240" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="240" spans="1:17" customFormat="1" ht="15.75">
       <c r="A240" s="2">
         <v>700</v>
       </c>
@@ -18225,18 +18830,22 @@
       <c r="J240" s="10">
         <v>1</v>
       </c>
-      <c r="K240" s="10"/>
-      <c r="L240" s="10"/>
+      <c r="K240" s="28">
+        <v>1</v>
+      </c>
+      <c r="L240" s="28">
+        <v>1</v>
+      </c>
       <c r="M240" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N240" s="38"/>
       <c r="O240" s="38"/>
       <c r="P240" s="38"/>
       <c r="Q240" s="27"/>
     </row>
-    <row r="241" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="241" spans="1:17" customFormat="1" ht="15.75">
       <c r="A241" s="2">
         <v>700</v>
       </c>
@@ -18268,18 +18877,22 @@
       <c r="J241" s="10">
         <v>1</v>
       </c>
-      <c r="K241" s="10"/>
-      <c r="L241" s="10"/>
+      <c r="K241" s="28">
+        <v>1</v>
+      </c>
+      <c r="L241" s="28">
+        <v>1</v>
+      </c>
       <c r="M241" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N241" s="38"/>
       <c r="O241" s="38"/>
       <c r="P241" s="38"/>
       <c r="Q241" s="27"/>
     </row>
-    <row r="242" spans="1:17" ht="15.75" hidden="1">
+    <row r="242" spans="1:17" ht="15.75">
       <c r="A242" s="30">
         <v>700</v>
       </c>
@@ -18311,14 +18924,18 @@
       <c r="J242" s="28">
         <v>1</v>
       </c>
-      <c r="K242" s="28"/>
-      <c r="L242" s="28"/>
+      <c r="K242" s="28">
+        <v>1</v>
+      </c>
+      <c r="L242" s="28">
+        <v>1</v>
+      </c>
       <c r="M242" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="243" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:17" ht="15.75">
       <c r="A243" s="30">
         <v>700</v>
       </c>
@@ -18350,14 +18967,18 @@
       <c r="J243" s="28">
         <v>1</v>
       </c>
-      <c r="K243" s="28"/>
-      <c r="L243" s="28"/>
+      <c r="K243" s="28">
+        <v>1</v>
+      </c>
+      <c r="L243" s="28">
+        <v>1</v>
+      </c>
       <c r="M243" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="244" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:17" ht="15.75">
       <c r="A244" s="30">
         <v>700</v>
       </c>
@@ -18389,14 +19010,18 @@
       <c r="J244" s="28">
         <v>1</v>
       </c>
-      <c r="K244" s="28"/>
-      <c r="L244" s="28"/>
+      <c r="K244" s="28">
+        <v>1</v>
+      </c>
+      <c r="L244" s="28">
+        <v>1</v>
+      </c>
       <c r="M244" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="245" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:17" ht="15.75">
       <c r="A245" s="30">
         <v>700</v>
       </c>
@@ -18428,14 +19053,18 @@
       <c r="J245" s="28">
         <v>1</v>
       </c>
-      <c r="K245" s="28"/>
-      <c r="L245" s="28"/>
+      <c r="K245" s="28">
+        <v>1</v>
+      </c>
+      <c r="L245" s="28">
+        <v>1</v>
+      </c>
       <c r="M245" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="246" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:17" ht="15.75">
       <c r="A246" s="30">
         <v>700</v>
       </c>
@@ -18467,14 +19096,18 @@
       <c r="J246" s="28">
         <v>1</v>
       </c>
-      <c r="K246" s="28"/>
-      <c r="L246" s="28"/>
+      <c r="K246" s="28">
+        <v>1</v>
+      </c>
+      <c r="L246" s="28">
+        <v>1</v>
+      </c>
       <c r="M246" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="247" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:17" customFormat="1" ht="15.75">
       <c r="A247" s="2">
         <v>700</v>
       </c>
@@ -18506,18 +19139,22 @@
       <c r="J247" s="10">
         <v>1</v>
       </c>
-      <c r="K247" s="10"/>
-      <c r="L247" s="10"/>
+      <c r="K247" s="28">
+        <v>1</v>
+      </c>
+      <c r="L247" s="28">
+        <v>1</v>
+      </c>
       <c r="M247" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N247" s="38"/>
       <c r="O247" s="38"/>
       <c r="P247" s="38"/>
       <c r="Q247" s="27"/>
     </row>
-    <row r="248" spans="1:17" ht="15.75" hidden="1">
+    <row r="248" spans="1:17" ht="15.75">
       <c r="A248" s="30">
         <v>700</v>
       </c>
@@ -18549,14 +19186,18 @@
       <c r="J248" s="28">
         <v>1</v>
       </c>
-      <c r="K248" s="28"/>
-      <c r="L248" s="28"/>
+      <c r="K248" s="28">
+        <v>1</v>
+      </c>
+      <c r="L248" s="28">
+        <v>1</v>
+      </c>
       <c r="M248" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="249" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:17" ht="15.75">
       <c r="A249" s="30">
         <v>700</v>
       </c>
@@ -18588,14 +19229,18 @@
       <c r="J249" s="28">
         <v>1</v>
       </c>
-      <c r="K249" s="28"/>
-      <c r="L249" s="28"/>
+      <c r="K249" s="28">
+        <v>1</v>
+      </c>
+      <c r="L249" s="28">
+        <v>1</v>
+      </c>
       <c r="M249" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="250" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:17" customFormat="1" ht="15.75">
       <c r="A250" s="2">
         <v>700</v>
       </c>
@@ -18627,18 +19272,22 @@
       <c r="J250" s="10">
         <v>1</v>
       </c>
-      <c r="K250" s="10"/>
-      <c r="L250" s="10"/>
+      <c r="K250" s="28">
+        <v>1</v>
+      </c>
+      <c r="L250" s="28">
+        <v>1</v>
+      </c>
       <c r="M250" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N250" s="38"/>
       <c r="O250" s="38"/>
       <c r="P250" s="38"/>
       <c r="Q250" s="27"/>
     </row>
-    <row r="251" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="251" spans="1:17" customFormat="1" ht="15.75">
       <c r="A251" s="2">
         <v>700</v>
       </c>
@@ -18670,18 +19319,22 @@
       <c r="J251" s="10">
         <v>1</v>
       </c>
-      <c r="K251" s="10"/>
-      <c r="L251" s="10"/>
+      <c r="K251" s="28">
+        <v>1</v>
+      </c>
+      <c r="L251" s="28">
+        <v>1</v>
+      </c>
       <c r="M251" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N251" s="38"/>
       <c r="O251" s="38"/>
       <c r="P251" s="38"/>
       <c r="Q251" s="27"/>
     </row>
-    <row r="252" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="252" spans="1:17" customFormat="1" ht="15.75">
       <c r="A252" s="2">
         <v>700</v>
       </c>
@@ -18722,7 +19375,7 @@
       <c r="P252" s="38"/>
       <c r="Q252" s="27"/>
     </row>
-    <row r="253" spans="1:17" ht="15.75" hidden="1">
+    <row r="253" spans="1:17" ht="15.75">
       <c r="A253" s="30">
         <v>700</v>
       </c>
@@ -18754,14 +19407,18 @@
       <c r="J253" s="10">
         <v>1</v>
       </c>
-      <c r="K253" s="28"/>
-      <c r="L253" s="28"/>
+      <c r="K253" s="28">
+        <v>1</v>
+      </c>
+      <c r="L253" s="28">
+        <v>1</v>
+      </c>
       <c r="M253" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="254" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:17" customFormat="1" ht="15.75">
       <c r="A254" s="2">
         <v>700</v>
       </c>
@@ -18793,18 +19450,22 @@
       <c r="J254" s="10">
         <v>1</v>
       </c>
-      <c r="K254" s="10"/>
-      <c r="L254" s="10"/>
+      <c r="K254" s="28">
+        <v>1</v>
+      </c>
+      <c r="L254" s="28">
+        <v>1</v>
+      </c>
       <c r="M254" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N254" s="38"/>
       <c r="O254" s="38"/>
       <c r="P254" s="38"/>
       <c r="Q254" s="27"/>
     </row>
-    <row r="255" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="255" spans="1:17" customFormat="1" ht="15.75">
       <c r="A255" s="2">
         <v>700</v>
       </c>
@@ -18836,18 +19497,22 @@
       <c r="J255" s="10">
         <v>1</v>
       </c>
-      <c r="K255" s="10"/>
-      <c r="L255" s="10"/>
+      <c r="K255" s="28">
+        <v>1</v>
+      </c>
+      <c r="L255" s="28">
+        <v>1</v>
+      </c>
       <c r="M255" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N255" s="38"/>
       <c r="O255" s="38"/>
       <c r="P255" s="38"/>
       <c r="Q255" s="27"/>
     </row>
-    <row r="256" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="256" spans="1:17" customFormat="1" ht="15.75">
       <c r="A256" s="13">
         <v>700</v>
       </c>
@@ -18877,18 +19542,22 @@
       <c r="J256" s="16">
         <v>1</v>
       </c>
-      <c r="K256" s="16"/>
-      <c r="L256" s="16"/>
+      <c r="K256" s="28">
+        <v>1</v>
+      </c>
+      <c r="L256" s="28">
+        <v>1</v>
+      </c>
       <c r="M256" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N256" s="38"/>
       <c r="O256" s="38"/>
       <c r="P256" s="38"/>
       <c r="Q256" s="27"/>
     </row>
-    <row r="257" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="257" spans="1:17" customFormat="1" ht="15.75">
       <c r="A257" s="2">
         <v>700</v>
       </c>
@@ -18920,18 +19589,22 @@
       <c r="J257" s="10">
         <v>1</v>
       </c>
-      <c r="K257" s="10"/>
-      <c r="L257" s="10"/>
+      <c r="K257" s="28">
+        <v>1</v>
+      </c>
+      <c r="L257" s="28">
+        <v>1</v>
+      </c>
       <c r="M257" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N257" s="38"/>
       <c r="O257" s="38"/>
       <c r="P257" s="38"/>
       <c r="Q257" s="27"/>
     </row>
-    <row r="258" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="258" spans="1:17" customFormat="1" ht="15.75">
       <c r="A258" s="2">
         <v>700</v>
       </c>
@@ -18968,7 +19641,7 @@
       <c r="P258" s="38"/>
       <c r="Q258" s="27"/>
     </row>
-    <row r="259" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="259" spans="1:17" customFormat="1" ht="15.75">
       <c r="A259" s="2">
         <v>700</v>
       </c>
@@ -19000,18 +19673,22 @@
       <c r="J259" s="10">
         <v>1</v>
       </c>
-      <c r="K259" s="10"/>
-      <c r="L259" s="10"/>
+      <c r="K259" s="28">
+        <v>1</v>
+      </c>
+      <c r="L259" s="28">
+        <v>1</v>
+      </c>
       <c r="M259" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N259" s="38"/>
       <c r="O259" s="38"/>
       <c r="P259" s="38"/>
       <c r="Q259" s="27"/>
     </row>
-    <row r="260" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="260" spans="1:17" customFormat="1" ht="15.75">
       <c r="A260" s="2">
         <v>700</v>
       </c>
@@ -19048,7 +19725,7 @@
       <c r="P260" s="38"/>
       <c r="Q260" s="27"/>
     </row>
-    <row r="261" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="261" spans="1:17" customFormat="1" ht="15.75">
       <c r="A261" s="2">
         <v>700</v>
       </c>
@@ -19080,18 +19757,22 @@
       <c r="J261" s="10">
         <v>1</v>
       </c>
-      <c r="K261" s="10"/>
-      <c r="L261" s="10"/>
+      <c r="K261" s="28">
+        <v>1</v>
+      </c>
+      <c r="L261" s="28">
+        <v>1</v>
+      </c>
       <c r="M261" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N261" s="38"/>
       <c r="O261" s="38"/>
       <c r="P261" s="38"/>
       <c r="Q261" s="27"/>
     </row>
-    <row r="262" spans="1:17" ht="15.75" hidden="1">
+    <row r="262" spans="1:17" ht="15.75">
       <c r="A262" s="30">
         <v>700</v>
       </c>
@@ -19123,14 +19804,18 @@
       <c r="J262" s="10">
         <v>1</v>
       </c>
-      <c r="K262" s="28"/>
-      <c r="L262" s="28"/>
+      <c r="K262" s="28">
+        <v>1</v>
+      </c>
+      <c r="L262" s="28">
+        <v>1</v>
+      </c>
       <c r="M262" s="28">
         <f t="shared" si="5"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="263" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:17" customFormat="1" ht="15.75">
       <c r="A263" s="2">
         <v>700</v>
       </c>
@@ -19160,18 +19845,22 @@
       <c r="J263" s="10">
         <v>1</v>
       </c>
-      <c r="K263" s="10"/>
-      <c r="L263" s="10"/>
+      <c r="K263" s="28">
+        <v>1</v>
+      </c>
+      <c r="L263" s="28">
+        <v>1</v>
+      </c>
       <c r="M263" s="10">
         <f t="shared" si="5"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N263" s="38"/>
       <c r="O263" s="38"/>
       <c r="P263" s="38"/>
       <c r="Q263" s="27"/>
     </row>
-    <row r="264" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="264" spans="1:17" customFormat="1" ht="15.75">
       <c r="A264" s="2">
         <v>700</v>
       </c>
@@ -19201,18 +19890,22 @@
       <c r="J264" s="10">
         <v>1</v>
       </c>
-      <c r="K264" s="10"/>
-      <c r="L264" s="10"/>
+      <c r="K264" s="28">
+        <v>1</v>
+      </c>
+      <c r="L264" s="28">
+        <v>1</v>
+      </c>
       <c r="M264" s="10">
         <f t="shared" ref="M264:M327" si="6">SUMPRODUCT(H264:L264,$AA$2:$AE$2)</f>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N264" s="38"/>
       <c r="O264" s="38"/>
       <c r="P264" s="38"/>
       <c r="Q264" s="27"/>
     </row>
-    <row r="265" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="265" spans="1:17" customFormat="1" ht="15.75">
       <c r="A265" s="2">
         <v>700</v>
       </c>
@@ -19242,18 +19935,22 @@
       <c r="J265" s="10">
         <v>1</v>
       </c>
-      <c r="K265" s="10"/>
-      <c r="L265" s="10"/>
+      <c r="K265" s="28">
+        <v>1</v>
+      </c>
+      <c r="L265" s="28">
+        <v>1</v>
+      </c>
       <c r="M265" s="10">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N265" s="38"/>
       <c r="O265" s="38"/>
       <c r="P265" s="38"/>
       <c r="Q265" s="27"/>
     </row>
-    <row r="266" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="266" spans="1:17" customFormat="1" ht="15.75">
       <c r="A266" s="2">
         <v>700</v>
       </c>
@@ -19283,18 +19980,22 @@
       <c r="J266" s="10">
         <v>1</v>
       </c>
-      <c r="K266" s="10"/>
-      <c r="L266" s="10"/>
+      <c r="K266" s="28">
+        <v>1</v>
+      </c>
+      <c r="L266" s="28">
+        <v>1</v>
+      </c>
       <c r="M266" s="10">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N266" s="38"/>
       <c r="O266" s="38"/>
       <c r="P266" s="38"/>
       <c r="Q266" s="27"/>
     </row>
-    <row r="267" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="267" spans="1:17" customFormat="1" ht="15.75">
       <c r="A267" s="2">
         <v>700</v>
       </c>
@@ -19326,18 +20027,22 @@
       <c r="J267" s="10">
         <v>1</v>
       </c>
-      <c r="K267" s="10"/>
-      <c r="L267" s="10"/>
+      <c r="K267" s="28">
+        <v>1</v>
+      </c>
+      <c r="L267" s="28">
+        <v>1</v>
+      </c>
       <c r="M267" s="10">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N267" s="38"/>
       <c r="O267" s="38"/>
       <c r="P267" s="38"/>
       <c r="Q267" s="27"/>
     </row>
-    <row r="268" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="268" spans="1:17" customFormat="1" ht="15.75">
       <c r="A268" s="2">
         <v>700</v>
       </c>
@@ -19369,18 +20074,22 @@
       <c r="J268" s="10">
         <v>1</v>
       </c>
-      <c r="K268" s="10"/>
-      <c r="L268" s="10"/>
+      <c r="K268" s="28">
+        <v>1</v>
+      </c>
+      <c r="L268" s="28">
+        <v>1</v>
+      </c>
       <c r="M268" s="10">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N268" s="38"/>
       <c r="O268" s="38"/>
       <c r="P268" s="38"/>
       <c r="Q268" s="27"/>
     </row>
-    <row r="269" spans="1:17" ht="15.75" hidden="1">
+    <row r="269" spans="1:17" ht="15.75">
       <c r="A269" s="30">
         <v>700</v>
       </c>
@@ -19412,14 +20121,18 @@
       <c r="J269" s="28">
         <v>1</v>
       </c>
-      <c r="K269" s="28"/>
-      <c r="L269" s="28"/>
+      <c r="K269" s="28">
+        <v>1</v>
+      </c>
+      <c r="L269" s="28">
+        <v>1</v>
+      </c>
       <c r="M269" s="28">
         <f t="shared" si="6"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="270" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:17" customFormat="1" ht="15.75">
       <c r="A270" s="2">
         <v>700</v>
       </c>
@@ -19451,18 +20164,22 @@
       <c r="J270" s="28">
         <v>1</v>
       </c>
-      <c r="K270" s="10"/>
-      <c r="L270" s="10"/>
+      <c r="K270" s="28">
+        <v>1</v>
+      </c>
+      <c r="L270" s="28">
+        <v>1</v>
+      </c>
       <c r="M270" s="10">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N270" s="38"/>
       <c r="O270" s="38"/>
       <c r="P270" s="38"/>
       <c r="Q270" s="27"/>
     </row>
-    <row r="271" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="271" spans="1:17" customFormat="1" ht="15.75">
       <c r="A271" s="2">
         <v>700</v>
       </c>
@@ -19494,18 +20211,22 @@
       <c r="J271" s="28">
         <v>1</v>
       </c>
-      <c r="K271" s="10"/>
-      <c r="L271" s="10"/>
+      <c r="K271" s="28">
+        <v>1</v>
+      </c>
+      <c r="L271" s="28">
+        <v>1</v>
+      </c>
       <c r="M271" s="10">
         <f t="shared" si="6"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N271" s="38"/>
       <c r="O271" s="38"/>
       <c r="P271" s="38"/>
       <c r="Q271" s="27"/>
     </row>
-    <row r="272" spans="1:17" ht="15.75" hidden="1">
+    <row r="272" spans="1:17" ht="15.75">
       <c r="A272" s="30">
         <v>700</v>
       </c>
@@ -19537,14 +20258,18 @@
       <c r="J272" s="28">
         <v>1</v>
       </c>
-      <c r="K272" s="28"/>
-      <c r="L272" s="28"/>
+      <c r="K272" s="28">
+        <v>1</v>
+      </c>
+      <c r="L272" s="28">
+        <v>1</v>
+      </c>
       <c r="M272" s="28">
         <f t="shared" si="6"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="273" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:17" ht="15.75">
       <c r="A273" s="30">
         <v>700</v>
       </c>
@@ -19576,14 +20301,18 @@
       <c r="J273" s="28">
         <v>1</v>
       </c>
-      <c r="K273" s="28"/>
-      <c r="L273" s="28"/>
+      <c r="K273" s="28">
+        <v>1</v>
+      </c>
+      <c r="L273" s="28">
+        <v>1</v>
+      </c>
       <c r="M273" s="28">
         <f t="shared" si="6"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="274" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:17" customFormat="1" ht="15.75">
       <c r="A274" s="2">
         <v>800</v>
       </c>
@@ -19624,7 +20353,7 @@
       <c r="P274" s="38"/>
       <c r="Q274" s="27"/>
     </row>
-    <row r="275" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="275" spans="1:17" customFormat="1" ht="15.75">
       <c r="A275" s="2">
         <v>800</v>
       </c>
@@ -19665,7 +20394,7 @@
       <c r="P275" s="38"/>
       <c r="Q275" s="27"/>
     </row>
-    <row r="276" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="276" spans="1:17" customFormat="1" ht="15.75">
       <c r="A276" s="2">
         <v>800</v>
       </c>
@@ -19704,7 +20433,7 @@
       <c r="P276" s="38"/>
       <c r="Q276" s="27"/>
     </row>
-    <row r="277" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="277" spans="1:17" customFormat="1" ht="15.75">
       <c r="A277" s="2">
         <v>800</v>
       </c>
@@ -19741,7 +20470,7 @@
       <c r="P277" s="38"/>
       <c r="Q277" s="27"/>
     </row>
-    <row r="278" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="278" spans="1:17" customFormat="1" ht="15.75">
       <c r="A278" s="2">
         <v>800</v>
       </c>
@@ -19780,7 +20509,7 @@
       <c r="P278" s="38"/>
       <c r="Q278" s="27"/>
     </row>
-    <row r="279" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="279" spans="1:17" customFormat="1" ht="15.75">
       <c r="A279" s="2">
         <v>800</v>
       </c>
@@ -19821,7 +20550,7 @@
       <c r="P279" s="38"/>
       <c r="Q279" s="27"/>
     </row>
-    <row r="280" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="280" spans="1:17" customFormat="1" ht="15.75">
       <c r="A280" s="2">
         <v>800</v>
       </c>
@@ -19858,7 +20587,7 @@
       <c r="P280" s="38"/>
       <c r="Q280" s="27"/>
     </row>
-    <row r="281" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="281" spans="1:17" customFormat="1" ht="15.75">
       <c r="A281" s="2">
         <v>800</v>
       </c>
@@ -19895,7 +20624,7 @@
       <c r="P281" s="38"/>
       <c r="Q281" s="27"/>
     </row>
-    <row r="282" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="282" spans="1:17" customFormat="1" ht="15.75">
       <c r="A282" s="2">
         <v>800</v>
       </c>
@@ -19936,7 +20665,7 @@
       <c r="P282" s="38"/>
       <c r="Q282" s="27"/>
     </row>
-    <row r="283" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="283" spans="1:17" customFormat="1" ht="15.75">
       <c r="A283" s="2">
         <v>800</v>
       </c>
@@ -19977,7 +20706,7 @@
       <c r="P283" s="38"/>
       <c r="Q283" s="27"/>
     </row>
-    <row r="284" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="284" spans="1:17" customFormat="1" ht="15.75">
       <c r="A284" s="2">
         <v>800</v>
       </c>
@@ -20018,7 +20747,7 @@
       <c r="P284" s="38"/>
       <c r="Q284" s="27"/>
     </row>
-    <row r="285" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="285" spans="1:17" customFormat="1" ht="15.75">
       <c r="A285" s="2">
         <v>800</v>
       </c>
@@ -20059,7 +20788,7 @@
       <c r="P285" s="38"/>
       <c r="Q285" s="27"/>
     </row>
-    <row r="286" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="286" spans="1:17" customFormat="1" ht="15.75">
       <c r="A286" s="2">
         <v>800</v>
       </c>
@@ -20100,7 +20829,7 @@
       <c r="P286" s="38"/>
       <c r="Q286" s="27"/>
     </row>
-    <row r="287" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="287" spans="1:17" customFormat="1" ht="15.75">
       <c r="A287" s="2">
         <v>800</v>
       </c>
@@ -20141,7 +20870,7 @@
       <c r="P287" s="38"/>
       <c r="Q287" s="27"/>
     </row>
-    <row r="288" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="288" spans="1:17" customFormat="1" ht="15.75">
       <c r="A288" s="2">
         <v>800</v>
       </c>
@@ -20182,7 +20911,7 @@
       <c r="P288" s="38"/>
       <c r="Q288" s="27"/>
     </row>
-    <row r="289" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="289" spans="1:17" customFormat="1" ht="15.75">
       <c r="A289" s="2">
         <v>800</v>
       </c>
@@ -20219,7 +20948,7 @@
       <c r="P289" s="38"/>
       <c r="Q289" s="27"/>
     </row>
-    <row r="290" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="290" spans="1:17" customFormat="1" ht="15.75">
       <c r="A290" s="2">
         <v>800</v>
       </c>
@@ -20256,7 +20985,7 @@
       <c r="P290" s="38"/>
       <c r="Q290" s="27"/>
     </row>
-    <row r="291" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="291" spans="1:17" customFormat="1" ht="15.75">
       <c r="A291" s="2">
         <v>800</v>
       </c>
@@ -20293,7 +21022,7 @@
       <c r="P291" s="38"/>
       <c r="Q291" s="27"/>
     </row>
-    <row r="292" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="292" spans="1:17" customFormat="1" ht="15.75">
       <c r="A292" s="2">
         <v>800</v>
       </c>
@@ -20332,7 +21061,7 @@
       <c r="P292" s="38"/>
       <c r="Q292" s="27"/>
     </row>
-    <row r="293" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="293" spans="1:17" customFormat="1" ht="15.75">
       <c r="A293" s="2">
         <v>800</v>
       </c>
@@ -20371,7 +21100,7 @@
       <c r="P293" s="38"/>
       <c r="Q293" s="27"/>
     </row>
-    <row r="294" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="294" spans="1:17" customFormat="1" ht="15.75">
       <c r="A294" s="2">
         <v>800</v>
       </c>
@@ -20410,7 +21139,7 @@
       <c r="P294" s="38"/>
       <c r="Q294" s="27"/>
     </row>
-    <row r="295" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="295" spans="1:17" customFormat="1" ht="15.75">
       <c r="A295" s="2">
         <v>800</v>
       </c>
@@ -20449,7 +21178,7 @@
       <c r="P295" s="38"/>
       <c r="Q295" s="27"/>
     </row>
-    <row r="296" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="296" spans="1:17" customFormat="1" ht="15.75">
       <c r="A296" s="2">
         <v>800</v>
       </c>
@@ -20488,7 +21217,7 @@
       <c r="P296" s="38"/>
       <c r="Q296" s="27"/>
     </row>
-    <row r="297" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="297" spans="1:17" customFormat="1" ht="15.75">
       <c r="A297" s="2">
         <v>800</v>
       </c>
@@ -20527,7 +21256,7 @@
       <c r="P297" s="38"/>
       <c r="Q297" s="27"/>
     </row>
-    <row r="298" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="298" spans="1:17" customFormat="1" ht="15.75">
       <c r="A298" s="2">
         <v>800</v>
       </c>
@@ -20566,7 +21295,7 @@
       <c r="P298" s="38"/>
       <c r="Q298" s="27"/>
     </row>
-    <row r="299" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="299" spans="1:17" customFormat="1" ht="15.75">
       <c r="A299" s="2">
         <v>800</v>
       </c>
@@ -20605,7 +21334,7 @@
       <c r="P299" s="38"/>
       <c r="Q299" s="27"/>
     </row>
-    <row r="300" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="300" spans="1:17" customFormat="1" ht="15.75">
       <c r="A300" s="2">
         <v>800</v>
       </c>
@@ -20644,7 +21373,7 @@
       <c r="P300" s="38"/>
       <c r="Q300" s="27"/>
     </row>
-    <row r="301" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="301" spans="1:17" customFormat="1" ht="15.75">
       <c r="A301" s="2">
         <v>800</v>
       </c>
@@ -20681,7 +21410,7 @@
       <c r="P301" s="38"/>
       <c r="Q301" s="27"/>
     </row>
-    <row r="302" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="302" spans="1:17" customFormat="1" ht="15.75">
       <c r="A302" s="2">
         <v>800</v>
       </c>
@@ -20718,7 +21447,7 @@
       <c r="P302" s="38"/>
       <c r="Q302" s="27"/>
     </row>
-    <row r="303" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="303" spans="1:17" customFormat="1" ht="15.75">
       <c r="A303" s="2">
         <v>800</v>
       </c>
@@ -20755,7 +21484,7 @@
       <c r="P303" s="38"/>
       <c r="Q303" s="27"/>
     </row>
-    <row r="304" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="304" spans="1:17" customFormat="1" ht="15.75">
       <c r="A304" s="2">
         <v>800</v>
       </c>
@@ -20794,7 +21523,7 @@
       <c r="P304" s="38"/>
       <c r="Q304" s="27"/>
     </row>
-    <row r="305" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="305" spans="1:17" customFormat="1" ht="15.75">
       <c r="A305" s="2">
         <v>800</v>
       </c>
@@ -20831,7 +21560,7 @@
       <c r="P305" s="38"/>
       <c r="Q305" s="27"/>
     </row>
-    <row r="306" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="306" spans="1:17" customFormat="1" ht="15.75">
       <c r="A306" s="2">
         <v>800</v>
       </c>
@@ -20868,7 +21597,7 @@
       <c r="P306" s="38"/>
       <c r="Q306" s="27"/>
     </row>
-    <row r="307" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="307" spans="1:17" customFormat="1" ht="15.75">
       <c r="A307" s="2">
         <v>800</v>
       </c>
@@ -20905,7 +21634,7 @@
       <c r="P307" s="38"/>
       <c r="Q307" s="27"/>
     </row>
-    <row r="308" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="308" spans="1:17" customFormat="1" ht="15.75">
       <c r="A308" s="2">
         <v>800</v>
       </c>
@@ -20942,7 +21671,7 @@
       <c r="P308" s="38"/>
       <c r="Q308" s="27"/>
     </row>
-    <row r="309" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="309" spans="1:17" customFormat="1" ht="15.75">
       <c r="A309" s="2">
         <v>800</v>
       </c>
@@ -20979,7 +21708,7 @@
       <c r="P309" s="38"/>
       <c r="Q309" s="27"/>
     </row>
-    <row r="310" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="310" spans="1:17" customFormat="1" ht="15.75">
       <c r="A310" s="2">
         <v>800</v>
       </c>
@@ -21016,7 +21745,7 @@
       <c r="P310" s="38"/>
       <c r="Q310" s="27"/>
     </row>
-    <row r="311" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="311" spans="1:17" customFormat="1" ht="15.75">
       <c r="A311" s="2">
         <v>800</v>
       </c>
@@ -21053,7 +21782,7 @@
       <c r="P311" s="38"/>
       <c r="Q311" s="27"/>
     </row>
-    <row r="312" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="312" spans="1:17" customFormat="1" ht="15.75">
       <c r="A312" s="2">
         <v>800</v>
       </c>
@@ -21090,7 +21819,7 @@
       <c r="P312" s="38"/>
       <c r="Q312" s="27"/>
     </row>
-    <row r="313" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="313" spans="1:17" customFormat="1" ht="15.75">
       <c r="A313" s="2">
         <v>800</v>
       </c>
@@ -21127,7 +21856,7 @@
       <c r="P313" s="38"/>
       <c r="Q313" s="27"/>
     </row>
-    <row r="314" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="314" spans="1:17" customFormat="1" ht="15.75">
       <c r="A314" s="2">
         <v>800</v>
       </c>
@@ -21164,7 +21893,7 @@
       <c r="P314" s="38"/>
       <c r="Q314" s="27"/>
     </row>
-    <row r="315" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="315" spans="1:17" customFormat="1" ht="15.75">
       <c r="A315" s="2">
         <v>800</v>
       </c>
@@ -21201,7 +21930,7 @@
       <c r="P315" s="38"/>
       <c r="Q315" s="27"/>
     </row>
-    <row r="316" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="316" spans="1:17" customFormat="1" ht="15.75">
       <c r="A316" s="2">
         <v>800</v>
       </c>
@@ -21238,7 +21967,7 @@
       <c r="P316" s="38"/>
       <c r="Q316" s="27"/>
     </row>
-    <row r="317" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="317" spans="1:17" customFormat="1" ht="15.75">
       <c r="A317" s="2">
         <v>800</v>
       </c>
@@ -21275,7 +22004,7 @@
       <c r="P317" s="38"/>
       <c r="Q317" s="27"/>
     </row>
-    <row r="318" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="318" spans="1:17" customFormat="1" ht="15.75">
       <c r="A318" s="2">
         <v>800</v>
       </c>
@@ -21312,7 +22041,7 @@
       <c r="P318" s="38"/>
       <c r="Q318" s="27"/>
     </row>
-    <row r="319" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="319" spans="1:17" customFormat="1" ht="15.75">
       <c r="A319" s="2">
         <v>800</v>
       </c>
@@ -21349,7 +22078,7 @@
       <c r="P319" s="38"/>
       <c r="Q319" s="27"/>
     </row>
-    <row r="320" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="320" spans="1:17" customFormat="1" ht="15.75">
       <c r="A320" s="2">
         <v>800</v>
       </c>
@@ -21386,7 +22115,7 @@
       <c r="P320" s="38"/>
       <c r="Q320" s="27"/>
     </row>
-    <row r="321" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="321" spans="1:17" customFormat="1" ht="15.75">
       <c r="A321" s="2">
         <v>800</v>
       </c>
@@ -21423,7 +22152,7 @@
       <c r="P321" s="38"/>
       <c r="Q321" s="27"/>
     </row>
-    <row r="322" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="322" spans="1:17" customFormat="1" ht="15.75">
       <c r="A322" s="2">
         <v>800</v>
       </c>
@@ -21460,7 +22189,7 @@
       <c r="P322" s="38"/>
       <c r="Q322" s="27"/>
     </row>
-    <row r="323" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="323" spans="1:17" customFormat="1" ht="15.75">
       <c r="A323" s="2">
         <v>800</v>
       </c>
@@ -21497,7 +22226,7 @@
       <c r="P323" s="38"/>
       <c r="Q323" s="27"/>
     </row>
-    <row r="324" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="324" spans="1:17" customFormat="1" ht="15.75">
       <c r="A324" s="2">
         <v>800</v>
       </c>
@@ -21534,7 +22263,7 @@
       <c r="P324" s="38"/>
       <c r="Q324" s="27"/>
     </row>
-    <row r="325" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="325" spans="1:17" customFormat="1" ht="15.75">
       <c r="A325" s="2">
         <v>800</v>
       </c>
@@ -21571,7 +22300,7 @@
       <c r="P325" s="38"/>
       <c r="Q325" s="27"/>
     </row>
-    <row r="326" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="326" spans="1:17" customFormat="1" ht="15.75">
       <c r="A326" s="2">
         <v>800</v>
       </c>
@@ -21608,7 +22337,7 @@
       <c r="P326" s="38"/>
       <c r="Q326" s="27"/>
     </row>
-    <row r="327" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="327" spans="1:17" customFormat="1" ht="15.75">
       <c r="A327" s="2">
         <v>800</v>
       </c>
@@ -21645,7 +22374,7 @@
       <c r="P327" s="38"/>
       <c r="Q327" s="27"/>
     </row>
-    <row r="328" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="328" spans="1:17" customFormat="1" ht="15.75">
       <c r="A328" s="2">
         <v>800</v>
       </c>
@@ -21682,7 +22411,7 @@
       <c r="P328" s="38"/>
       <c r="Q328" s="27"/>
     </row>
-    <row r="329" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="329" spans="1:17" customFormat="1" ht="15.75">
       <c r="A329" s="2">
         <v>800</v>
       </c>
@@ -21719,7 +22448,7 @@
       <c r="P329" s="38"/>
       <c r="Q329" s="27"/>
     </row>
-    <row r="330" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="330" spans="1:17" customFormat="1" ht="15.75">
       <c r="A330" s="2">
         <v>800</v>
       </c>
@@ -21756,7 +22485,7 @@
       <c r="P330" s="38"/>
       <c r="Q330" s="27"/>
     </row>
-    <row r="331" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="331" spans="1:17" customFormat="1" ht="15.75">
       <c r="A331" s="2">
         <v>800</v>
       </c>
@@ -21793,7 +22522,7 @@
       <c r="P331" s="38"/>
       <c r="Q331" s="27"/>
     </row>
-    <row r="332" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="332" spans="1:17" customFormat="1" ht="15.75">
       <c r="A332" s="2">
         <v>800</v>
       </c>
@@ -21830,7 +22559,7 @@
       <c r="P332" s="38"/>
       <c r="Q332" s="27"/>
     </row>
-    <row r="333" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="333" spans="1:17" customFormat="1" ht="15.75">
       <c r="A333" s="2">
         <v>800</v>
       </c>
@@ -21867,7 +22596,7 @@
       <c r="P333" s="38"/>
       <c r="Q333" s="27"/>
     </row>
-    <row r="334" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="334" spans="1:17" customFormat="1" ht="15.75">
       <c r="A334" s="2">
         <v>800</v>
       </c>
@@ -21904,7 +22633,7 @@
       <c r="P334" s="38"/>
       <c r="Q334" s="27"/>
     </row>
-    <row r="335" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="335" spans="1:17" customFormat="1" ht="15.75">
       <c r="A335" s="2">
         <v>800</v>
       </c>
@@ -21941,7 +22670,7 @@
       <c r="P335" s="38"/>
       <c r="Q335" s="27"/>
     </row>
-    <row r="336" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="336" spans="1:17" customFormat="1" ht="15.75">
       <c r="A336" s="2">
         <v>800</v>
       </c>
@@ -21978,7 +22707,7 @@
       <c r="P336" s="38"/>
       <c r="Q336" s="27"/>
     </row>
-    <row r="337" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="337" spans="1:17" customFormat="1" ht="15.75">
       <c r="A337" s="2">
         <v>800</v>
       </c>
@@ -22015,7 +22744,7 @@
       <c r="P337" s="38"/>
       <c r="Q337" s="27"/>
     </row>
-    <row r="338" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="338" spans="1:17" customFormat="1" ht="15.75">
       <c r="A338" s="2">
         <v>800</v>
       </c>
@@ -22052,7 +22781,7 @@
       <c r="P338" s="38"/>
       <c r="Q338" s="27"/>
     </row>
-    <row r="339" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="339" spans="1:17" customFormat="1" ht="15.75">
       <c r="A339" s="2">
         <v>800</v>
       </c>
@@ -22089,7 +22818,7 @@
       <c r="P339" s="38"/>
       <c r="Q339" s="27"/>
     </row>
-    <row r="340" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="340" spans="1:17" customFormat="1" ht="15.75">
       <c r="A340" s="2">
         <v>800</v>
       </c>
@@ -22126,7 +22855,7 @@
       <c r="P340" s="38"/>
       <c r="Q340" s="27"/>
     </row>
-    <row r="341" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="341" spans="1:17" customFormat="1" ht="15.75">
       <c r="A341" s="2">
         <v>800</v>
       </c>
@@ -22163,7 +22892,7 @@
       <c r="P341" s="38"/>
       <c r="Q341" s="27"/>
     </row>
-    <row r="342" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="342" spans="1:17" customFormat="1" ht="15.75">
       <c r="A342" s="2">
         <v>800</v>
       </c>
@@ -22200,7 +22929,7 @@
       <c r="P342" s="38"/>
       <c r="Q342" s="27"/>
     </row>
-    <row r="343" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="343" spans="1:17" customFormat="1" ht="15.75">
       <c r="A343" s="2">
         <v>800</v>
       </c>
@@ -22237,7 +22966,7 @@
       <c r="P343" s="38"/>
       <c r="Q343" s="27"/>
     </row>
-    <row r="344" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="344" spans="1:17" customFormat="1" ht="15.75">
       <c r="A344" s="2">
         <v>800</v>
       </c>
@@ -22274,7 +23003,7 @@
       <c r="P344" s="38"/>
       <c r="Q344" s="27"/>
     </row>
-    <row r="345" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="345" spans="1:17" customFormat="1" ht="15.75">
       <c r="A345" s="2">
         <v>800</v>
       </c>
@@ -22311,7 +23040,7 @@
       <c r="P345" s="38"/>
       <c r="Q345" s="27"/>
     </row>
-    <row r="346" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="346" spans="1:17" customFormat="1" ht="15.75">
       <c r="A346" s="2">
         <v>800</v>
       </c>
@@ -22348,7 +23077,7 @@
       <c r="P346" s="38"/>
       <c r="Q346" s="27"/>
     </row>
-    <row r="347" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="347" spans="1:17" customFormat="1" ht="15.75">
       <c r="A347" s="2">
         <v>800</v>
       </c>
@@ -22385,7 +23114,7 @@
       <c r="P347" s="38"/>
       <c r="Q347" s="27"/>
     </row>
-    <row r="348" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="348" spans="1:17" customFormat="1" ht="15.75">
       <c r="A348" s="2">
         <v>800</v>
       </c>
@@ -22422,7 +23151,7 @@
       <c r="P348" s="38"/>
       <c r="Q348" s="27"/>
     </row>
-    <row r="349" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="349" spans="1:17" customFormat="1" ht="15.75">
       <c r="A349" s="2">
         <v>800</v>
       </c>
@@ -22459,7 +23188,7 @@
       <c r="P349" s="38"/>
       <c r="Q349" s="27"/>
     </row>
-    <row r="350" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="350" spans="1:17" customFormat="1" ht="15.75">
       <c r="A350" s="2">
         <v>800</v>
       </c>
@@ -22496,7 +23225,7 @@
       <c r="P350" s="38"/>
       <c r="Q350" s="27"/>
     </row>
-    <row r="351" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="351" spans="1:17" customFormat="1" ht="15.75">
       <c r="A351" s="2">
         <v>800</v>
       </c>
@@ -22533,7 +23262,7 @@
       <c r="P351" s="38"/>
       <c r="Q351" s="27"/>
     </row>
-    <row r="352" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="352" spans="1:17" customFormat="1" ht="15.75">
       <c r="A352" s="2">
         <v>800</v>
       </c>
@@ -22570,7 +23299,7 @@
       <c r="P352" s="38"/>
       <c r="Q352" s="27"/>
     </row>
-    <row r="353" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="353" spans="1:17" customFormat="1" ht="15.75">
       <c r="A353" s="2">
         <v>800</v>
       </c>
@@ -22607,7 +23336,7 @@
       <c r="P353" s="38"/>
       <c r="Q353" s="27"/>
     </row>
-    <row r="354" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="354" spans="1:17" customFormat="1" ht="15.75">
       <c r="A354" s="2">
         <v>800</v>
       </c>
@@ -22644,7 +23373,7 @@
       <c r="P354" s="38"/>
       <c r="Q354" s="27"/>
     </row>
-    <row r="355" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="355" spans="1:17" customFormat="1" ht="15.75">
       <c r="A355" s="2">
         <v>800</v>
       </c>
@@ -22681,7 +23410,7 @@
       <c r="P355" s="38"/>
       <c r="Q355" s="27"/>
     </row>
-    <row r="356" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="356" spans="1:17" customFormat="1" ht="15.75">
       <c r="A356" s="2">
         <v>800</v>
       </c>
@@ -22718,7 +23447,7 @@
       <c r="P356" s="38"/>
       <c r="Q356" s="27"/>
     </row>
-    <row r="357" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="357" spans="1:17" customFormat="1" ht="15.75">
       <c r="A357" s="2">
         <v>800</v>
       </c>
@@ -22755,7 +23484,7 @@
       <c r="P357" s="38"/>
       <c r="Q357" s="27"/>
     </row>
-    <row r="358" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="358" spans="1:17" customFormat="1" ht="15.75">
       <c r="A358" s="2">
         <v>800</v>
       </c>
@@ -22792,7 +23521,7 @@
       <c r="P358" s="38"/>
       <c r="Q358" s="27"/>
     </row>
-    <row r="359" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="359" spans="1:17" customFormat="1" ht="15.75">
       <c r="A359" s="2">
         <v>800</v>
       </c>
@@ -22829,7 +23558,7 @@
       <c r="P359" s="38"/>
       <c r="Q359" s="27"/>
     </row>
-    <row r="360" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="360" spans="1:17" customFormat="1" ht="15.75">
       <c r="A360" s="2">
         <v>800</v>
       </c>
@@ -22866,7 +23595,7 @@
       <c r="P360" s="38"/>
       <c r="Q360" s="27"/>
     </row>
-    <row r="361" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="361" spans="1:17" customFormat="1" ht="15.75">
       <c r="A361" s="2">
         <v>800</v>
       </c>
@@ -22903,7 +23632,7 @@
       <c r="P361" s="38"/>
       <c r="Q361" s="27"/>
     </row>
-    <row r="362" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="362" spans="1:17" customFormat="1" ht="15.75">
       <c r="A362" s="2">
         <v>800</v>
       </c>
@@ -22940,7 +23669,7 @@
       <c r="P362" s="38"/>
       <c r="Q362" s="27"/>
     </row>
-    <row r="363" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="363" spans="1:17" customFormat="1" ht="15.75">
       <c r="A363" s="2">
         <v>800</v>
       </c>
@@ -22977,7 +23706,7 @@
       <c r="P363" s="38"/>
       <c r="Q363" s="27"/>
     </row>
-    <row r="364" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="364" spans="1:17" customFormat="1" ht="15.75">
       <c r="A364" s="2">
         <v>800</v>
       </c>
@@ -23014,7 +23743,7 @@
       <c r="P364" s="38"/>
       <c r="Q364" s="27"/>
     </row>
-    <row r="365" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="365" spans="1:17" customFormat="1" ht="15.75">
       <c r="A365" s="2">
         <v>800</v>
       </c>
@@ -23051,7 +23780,7 @@
       <c r="P365" s="38"/>
       <c r="Q365" s="27"/>
     </row>
-    <row r="366" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="366" spans="1:17" customFormat="1" ht="15.75">
       <c r="A366" s="2">
         <v>800</v>
       </c>
@@ -23088,7 +23817,7 @@
       <c r="P366" s="38"/>
       <c r="Q366" s="27"/>
     </row>
-    <row r="367" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="367" spans="1:17" customFormat="1" ht="15.75">
       <c r="A367" s="2">
         <v>800</v>
       </c>
@@ -23125,7 +23854,7 @@
       <c r="P367" s="38"/>
       <c r="Q367" s="27"/>
     </row>
-    <row r="368" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="368" spans="1:17" customFormat="1" ht="15.75">
       <c r="A368" s="2">
         <v>800</v>
       </c>
@@ -23162,7 +23891,7 @@
       <c r="P368" s="38"/>
       <c r="Q368" s="27"/>
     </row>
-    <row r="369" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="369" spans="1:17" customFormat="1" ht="15.75">
       <c r="A369" s="2">
         <v>800</v>
       </c>
@@ -23199,7 +23928,7 @@
       <c r="P369" s="38"/>
       <c r="Q369" s="27"/>
     </row>
-    <row r="370" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="370" spans="1:17" customFormat="1" ht="15.75">
       <c r="A370" s="2">
         <v>800</v>
       </c>
@@ -23236,7 +23965,7 @@
       <c r="P370" s="38"/>
       <c r="Q370" s="27"/>
     </row>
-    <row r="371" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="371" spans="1:17" customFormat="1" ht="15.75">
       <c r="A371" s="2">
         <v>800</v>
       </c>
@@ -23273,7 +24002,7 @@
       <c r="P371" s="38"/>
       <c r="Q371" s="27"/>
     </row>
-    <row r="372" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="372" spans="1:17" customFormat="1" ht="15.75">
       <c r="A372" s="2">
         <v>800</v>
       </c>
@@ -23310,7 +24039,7 @@
       <c r="P372" s="38"/>
       <c r="Q372" s="27"/>
     </row>
-    <row r="373" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="373" spans="1:17" customFormat="1" ht="15.75">
       <c r="A373" s="2">
         <v>800</v>
       </c>
@@ -23347,7 +24076,7 @@
       <c r="P373" s="38"/>
       <c r="Q373" s="27"/>
     </row>
-    <row r="374" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="374" spans="1:17" customFormat="1" ht="15.75">
       <c r="A374" s="2">
         <v>800</v>
       </c>
@@ -23384,7 +24113,7 @@
       <c r="P374" s="38"/>
       <c r="Q374" s="27"/>
     </row>
-    <row r="375" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="375" spans="1:17" customFormat="1" ht="15.75">
       <c r="A375" s="2">
         <v>800</v>
       </c>
@@ -23421,7 +24150,7 @@
       <c r="P375" s="38"/>
       <c r="Q375" s="27"/>
     </row>
-    <row r="376" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="376" spans="1:17" customFormat="1" ht="15.75">
       <c r="A376" s="2">
         <v>800</v>
       </c>
@@ -23458,7 +24187,7 @@
       <c r="P376" s="38"/>
       <c r="Q376" s="27"/>
     </row>
-    <row r="377" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="377" spans="1:17" customFormat="1" ht="15.75">
       <c r="A377" s="2">
         <v>800</v>
       </c>
@@ -23495,7 +24224,7 @@
       <c r="P377" s="38"/>
       <c r="Q377" s="27"/>
     </row>
-    <row r="378" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="378" spans="1:17" customFormat="1" ht="15.75">
       <c r="A378" s="2">
         <v>800</v>
       </c>
@@ -23534,7 +24263,7 @@
       <c r="P378" s="38"/>
       <c r="Q378" s="27"/>
     </row>
-    <row r="379" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="379" spans="1:17" customFormat="1" ht="15.75">
       <c r="A379" s="2">
         <v>800</v>
       </c>
@@ -23571,7 +24300,7 @@
       <c r="P379" s="38"/>
       <c r="Q379" s="27"/>
     </row>
-    <row r="380" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="380" spans="1:17" customFormat="1" ht="15.75">
       <c r="A380" s="2">
         <v>800</v>
       </c>
@@ -23608,7 +24337,7 @@
       <c r="P380" s="38"/>
       <c r="Q380" s="27"/>
     </row>
-    <row r="381" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="381" spans="1:17" customFormat="1" ht="15.75">
       <c r="A381" s="2">
         <v>800</v>
       </c>
@@ -23643,7 +24372,7 @@
       <c r="P381" s="38"/>
       <c r="Q381" s="27"/>
     </row>
-    <row r="382" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="382" spans="1:17" customFormat="1" ht="15.75">
       <c r="A382" s="2">
         <v>800</v>
       </c>
@@ -23680,7 +24409,7 @@
       <c r="P382" s="38"/>
       <c r="Q382" s="27"/>
     </row>
-    <row r="383" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="383" spans="1:17" customFormat="1" ht="15.75">
       <c r="A383" s="2">
         <v>800</v>
       </c>
@@ -23721,7 +24450,7 @@
       <c r="P383" s="38"/>
       <c r="Q383" s="27"/>
     </row>
-    <row r="384" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="384" spans="1:17" customFormat="1" ht="15.75">
       <c r="A384" s="2">
         <v>800</v>
       </c>
@@ -23762,7 +24491,7 @@
       <c r="P384" s="38"/>
       <c r="Q384" s="27"/>
     </row>
-    <row r="385" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="385" spans="1:17" customFormat="1" ht="15.75">
       <c r="A385" s="2">
         <v>800</v>
       </c>
@@ -23803,7 +24532,7 @@
       <c r="P385" s="38"/>
       <c r="Q385" s="27"/>
     </row>
-    <row r="386" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="386" spans="1:17" customFormat="1" ht="15.75">
       <c r="A386" s="2">
         <v>800</v>
       </c>
@@ -23844,7 +24573,7 @@
       <c r="P386" s="38"/>
       <c r="Q386" s="27"/>
     </row>
-    <row r="387" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="387" spans="1:17" customFormat="1" ht="15.75">
       <c r="A387" s="2">
         <v>800</v>
       </c>
@@ -23883,7 +24612,7 @@
       <c r="P387" s="38"/>
       <c r="Q387" s="27"/>
     </row>
-    <row r="388" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="388" spans="1:17" customFormat="1" ht="15.75">
       <c r="A388" s="2">
         <v>800</v>
       </c>
@@ -23920,7 +24649,7 @@
       <c r="P388" s="38"/>
       <c r="Q388" s="27"/>
     </row>
-    <row r="389" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="389" spans="1:17" customFormat="1" ht="15.75">
       <c r="A389" s="2">
         <v>800</v>
       </c>
@@ -23957,7 +24686,7 @@
       <c r="P389" s="38"/>
       <c r="Q389" s="27"/>
     </row>
-    <row r="390" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="390" spans="1:17" customFormat="1" ht="15.75">
       <c r="A390" s="2">
         <v>800</v>
       </c>
@@ -23994,7 +24723,7 @@
       <c r="P390" s="38"/>
       <c r="Q390" s="27"/>
     </row>
-    <row r="391" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="391" spans="1:17" customFormat="1" ht="15.75">
       <c r="A391" s="2">
         <v>800</v>
       </c>
@@ -24031,7 +24760,7 @@
       <c r="P391" s="38"/>
       <c r="Q391" s="27"/>
     </row>
-    <row r="392" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="392" spans="1:17" customFormat="1" ht="15.75">
       <c r="A392" s="2">
         <v>800</v>
       </c>
@@ -24070,7 +24799,7 @@
       <c r="P392" s="38"/>
       <c r="Q392" s="27"/>
     </row>
-    <row r="393" spans="1:17" ht="15.75" hidden="1">
+    <row r="393" spans="1:17" ht="15.75">
       <c r="A393" s="30">
         <v>900</v>
       </c>
@@ -24102,14 +24831,18 @@
       <c r="J393" s="28">
         <v>1</v>
       </c>
-      <c r="K393" s="28"/>
-      <c r="L393" s="28"/>
+      <c r="K393" s="28">
+        <v>1</v>
+      </c>
+      <c r="L393" s="28">
+        <v>1</v>
+      </c>
       <c r="M393" s="28">
         <f t="shared" si="8"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="394" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:17" customFormat="1" ht="15.75">
       <c r="A394" s="2">
         <v>900</v>
       </c>
@@ -24141,18 +24874,22 @@
       <c r="J394" s="10">
         <v>1</v>
       </c>
-      <c r="K394" s="10"/>
-      <c r="L394" s="10"/>
+      <c r="K394" s="28">
+        <v>1</v>
+      </c>
+      <c r="L394" s="28">
+        <v>1</v>
+      </c>
       <c r="M394" s="10">
         <f t="shared" si="8"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N394" s="38"/>
       <c r="O394" s="38"/>
       <c r="P394" s="38"/>
       <c r="Q394" s="27"/>
     </row>
-    <row r="395" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="395" spans="1:17" customFormat="1" ht="15.75">
       <c r="A395" s="2">
         <v>900</v>
       </c>
@@ -24184,18 +24921,22 @@
       <c r="J395" s="10">
         <v>1</v>
       </c>
-      <c r="K395" s="10"/>
-      <c r="L395" s="10"/>
+      <c r="K395" s="28">
+        <v>1</v>
+      </c>
+      <c r="L395" s="28">
+        <v>1</v>
+      </c>
       <c r="M395" s="10">
         <f t="shared" si="8"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N395" s="38"/>
       <c r="O395" s="38"/>
       <c r="P395" s="38"/>
       <c r="Q395" s="27"/>
     </row>
-    <row r="396" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="396" spans="1:17" customFormat="1" ht="15.75">
       <c r="A396" s="2">
         <v>900</v>
       </c>
@@ -24236,7 +24977,7 @@
       <c r="P396" s="38"/>
       <c r="Q396" s="27"/>
     </row>
-    <row r="397" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="397" spans="1:17" customFormat="1" ht="15.75">
       <c r="A397" s="2">
         <v>900</v>
       </c>
@@ -24277,7 +25018,7 @@
       <c r="P397" s="38"/>
       <c r="Q397" s="27"/>
     </row>
-    <row r="398" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="398" spans="1:17" customFormat="1" ht="15.75">
       <c r="A398" s="2">
         <v>900</v>
       </c>
@@ -24314,7 +25055,7 @@
       <c r="P398" s="38"/>
       <c r="Q398" s="27"/>
     </row>
-    <row r="399" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="399" spans="1:17" customFormat="1" ht="15.75">
       <c r="A399" s="2">
         <v>900</v>
       </c>
@@ -24355,7 +25096,7 @@
       <c r="P399" s="38"/>
       <c r="Q399" s="27"/>
     </row>
-    <row r="400" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="400" spans="1:17" customFormat="1" ht="15.75">
       <c r="A400" s="2">
         <v>900</v>
       </c>
@@ -24387,18 +25128,22 @@
       <c r="J400" s="10">
         <v>1</v>
       </c>
-      <c r="K400" s="10"/>
-      <c r="L400" s="10"/>
+      <c r="K400" s="28">
+        <v>1</v>
+      </c>
+      <c r="L400" s="28">
+        <v>1</v>
+      </c>
       <c r="M400" s="10">
         <f t="shared" si="8"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N400" s="38"/>
       <c r="O400" s="38"/>
       <c r="P400" s="38"/>
       <c r="Q400" s="27"/>
     </row>
-    <row r="401" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="401" spans="1:17" customFormat="1" ht="15.75">
       <c r="A401" s="2">
         <v>900</v>
       </c>
@@ -24430,18 +25175,22 @@
       <c r="J401" s="10">
         <v>1</v>
       </c>
-      <c r="K401" s="10"/>
-      <c r="L401" s="10"/>
+      <c r="K401" s="28">
+        <v>1</v>
+      </c>
+      <c r="L401" s="28">
+        <v>1</v>
+      </c>
       <c r="M401" s="10">
         <f t="shared" si="8"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N401" s="38"/>
       <c r="O401" s="38"/>
       <c r="P401" s="38"/>
       <c r="Q401" s="27"/>
     </row>
-    <row r="402" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="402" spans="1:17" customFormat="1" ht="15.75">
       <c r="A402" s="2">
         <v>900</v>
       </c>
@@ -24473,18 +25222,22 @@
       <c r="J402" s="10">
         <v>1</v>
       </c>
-      <c r="K402" s="10"/>
-      <c r="L402" s="10"/>
+      <c r="K402" s="28">
+        <v>1</v>
+      </c>
+      <c r="L402" s="28">
+        <v>1</v>
+      </c>
       <c r="M402" s="10">
         <f t="shared" si="8"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N402" s="38"/>
       <c r="O402" s="38"/>
       <c r="P402" s="38"/>
       <c r="Q402" s="27"/>
     </row>
-    <row r="403" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="403" spans="1:17" customFormat="1" ht="15.75">
       <c r="A403" s="2">
         <v>900</v>
       </c>
@@ -24525,7 +25278,7 @@
       <c r="P403" s="38"/>
       <c r="Q403" s="27"/>
     </row>
-    <row r="404" spans="1:17" ht="15.75" hidden="1">
+    <row r="404" spans="1:17" ht="15.75">
       <c r="A404" s="30">
         <v>900</v>
       </c>
@@ -24557,7 +25310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="405" spans="1:17" customFormat="1" ht="15.75">
       <c r="A405" s="2">
         <v>900</v>
       </c>
@@ -24594,7 +25347,7 @@
       <c r="P405" s="38"/>
       <c r="Q405" s="27"/>
     </row>
-    <row r="406" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="406" spans="1:17" customFormat="1" ht="15.75">
       <c r="A406" s="2">
         <v>900</v>
       </c>
@@ -24626,18 +25379,22 @@
       <c r="J406" s="10">
         <v>1</v>
       </c>
-      <c r="K406" s="10"/>
-      <c r="L406" s="10"/>
+      <c r="K406" s="28">
+        <v>1</v>
+      </c>
+      <c r="L406" s="28">
+        <v>1</v>
+      </c>
       <c r="M406" s="10">
         <f t="shared" si="9"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N406" s="38"/>
       <c r="O406" s="38"/>
       <c r="P406" s="38"/>
       <c r="Q406" s="27"/>
     </row>
-    <row r="407" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="407" spans="1:17" customFormat="1" ht="15.75">
       <c r="A407" s="2">
         <v>900</v>
       </c>
@@ -24678,7 +25435,7 @@
       <c r="P407" s="38"/>
       <c r="Q407" s="27"/>
     </row>
-    <row r="408" spans="1:17" ht="15.75" hidden="1">
+    <row r="408" spans="1:17" ht="15.75">
       <c r="A408" s="30">
         <v>900</v>
       </c>
@@ -24710,14 +25467,18 @@
       <c r="J408" s="28">
         <v>1</v>
       </c>
-      <c r="K408" s="28"/>
-      <c r="L408" s="28"/>
+      <c r="K408" s="28">
+        <v>1</v>
+      </c>
+      <c r="L408" s="28">
+        <v>1</v>
+      </c>
       <c r="M408" s="28">
         <f t="shared" si="9"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="409" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:17" customFormat="1" ht="15.75">
       <c r="A409" s="2">
         <v>900</v>
       </c>
@@ -24758,7 +25519,7 @@
       <c r="P409" s="38"/>
       <c r="Q409" s="27"/>
     </row>
-    <row r="410" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="410" spans="1:17" customFormat="1" ht="15.75">
       <c r="A410" s="2">
         <v>900</v>
       </c>
@@ -24795,7 +25556,7 @@
       <c r="P410" s="38"/>
       <c r="Q410" s="27"/>
     </row>
-    <row r="411" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="411" spans="1:17" customFormat="1" ht="15.75">
       <c r="A411" s="2">
         <v>900</v>
       </c>
@@ -24834,7 +25595,7 @@
       <c r="P411" s="38"/>
       <c r="Q411" s="27"/>
     </row>
-    <row r="412" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="412" spans="1:17" customFormat="1" ht="15.75">
       <c r="A412" s="2">
         <v>900</v>
       </c>
@@ -24875,7 +25636,7 @@
       <c r="P412" s="38"/>
       <c r="Q412" s="27"/>
     </row>
-    <row r="413" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="413" spans="1:17" customFormat="1" ht="15.75">
       <c r="A413" s="2">
         <v>900</v>
       </c>
@@ -24907,18 +25668,22 @@
       <c r="J413" s="10">
         <v>1</v>
       </c>
-      <c r="K413" s="10"/>
-      <c r="L413" s="10"/>
+      <c r="K413" s="28">
+        <v>1</v>
+      </c>
+      <c r="L413" s="28">
+        <v>1</v>
+      </c>
       <c r="M413" s="10">
         <f t="shared" si="9"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N413" s="38"/>
       <c r="O413" s="38"/>
       <c r="P413" s="38"/>
       <c r="Q413" s="27"/>
     </row>
-    <row r="414" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="414" spans="1:17" customFormat="1" ht="15.75">
       <c r="A414" s="2">
         <v>900</v>
       </c>
@@ -24950,18 +25715,22 @@
       <c r="J414" s="10">
         <v>1</v>
       </c>
-      <c r="K414" s="10"/>
-      <c r="L414" s="10"/>
+      <c r="K414" s="28">
+        <v>1</v>
+      </c>
+      <c r="L414" s="28">
+        <v>1</v>
+      </c>
       <c r="M414" s="10">
         <f t="shared" si="9"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N414" s="38"/>
       <c r="O414" s="38"/>
       <c r="P414" s="38"/>
       <c r="Q414" s="27"/>
     </row>
-    <row r="415" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="415" spans="1:17" customFormat="1" ht="15.75">
       <c r="A415" s="2">
         <v>900</v>
       </c>
@@ -25002,7 +25771,7 @@
       <c r="P415" s="38"/>
       <c r="Q415" s="27"/>
     </row>
-    <row r="416" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="416" spans="1:17" customFormat="1" ht="15.75">
       <c r="A416" s="2">
         <v>900</v>
       </c>
@@ -25034,18 +25803,22 @@
       <c r="J416" s="10">
         <v>1</v>
       </c>
-      <c r="K416" s="10"/>
-      <c r="L416" s="10"/>
+      <c r="K416" s="28">
+        <v>1</v>
+      </c>
+      <c r="L416" s="28">
+        <v>1</v>
+      </c>
       <c r="M416" s="10">
         <f t="shared" si="9"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N416" s="38"/>
       <c r="O416" s="38"/>
       <c r="P416" s="38"/>
       <c r="Q416" s="27"/>
     </row>
-    <row r="417" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="417" spans="1:17" customFormat="1" ht="15.75">
       <c r="A417" s="2">
         <v>900</v>
       </c>
@@ -25082,7 +25855,7 @@
       <c r="P417" s="38"/>
       <c r="Q417" s="27"/>
     </row>
-    <row r="418" spans="1:17" ht="15.75" hidden="1">
+    <row r="418" spans="1:17" ht="15.75">
       <c r="A418" s="30">
         <v>900</v>
       </c>
@@ -25117,7 +25890,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="419" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="419" spans="1:17" customFormat="1" ht="15.75">
       <c r="A419" s="2">
         <v>900</v>
       </c>
@@ -25156,7 +25929,7 @@
       <c r="P419" s="38"/>
       <c r="Q419" s="27"/>
     </row>
-    <row r="420" spans="1:17" ht="15.75" hidden="1">
+    <row r="420" spans="1:17" ht="15.75">
       <c r="A420" s="30">
         <v>900</v>
       </c>
@@ -25191,7 +25964,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="421" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="421" spans="1:17" customFormat="1" ht="15.75">
       <c r="A421" s="2">
         <v>900</v>
       </c>
@@ -25232,7 +26005,7 @@
       <c r="P421" s="38"/>
       <c r="Q421" s="27"/>
     </row>
-    <row r="422" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="422" spans="1:17" customFormat="1" ht="15.75">
       <c r="A422" s="2">
         <v>900</v>
       </c>
@@ -25273,7 +26046,7 @@
       <c r="P422" s="38"/>
       <c r="Q422" s="27"/>
     </row>
-    <row r="423" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="423" spans="1:17" customFormat="1" ht="15.75">
       <c r="A423" s="2">
         <v>900</v>
       </c>
@@ -25314,7 +26087,7 @@
       <c r="P423" s="38"/>
       <c r="Q423" s="27"/>
     </row>
-    <row r="424" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="424" spans="1:17" customFormat="1" ht="15.75">
       <c r="A424" s="2">
         <v>900</v>
       </c>
@@ -25355,7 +26128,7 @@
       <c r="P424" s="38"/>
       <c r="Q424" s="27"/>
     </row>
-    <row r="425" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="425" spans="1:17" customFormat="1" ht="15.75">
       <c r="A425" s="2">
         <v>900</v>
       </c>
@@ -25396,7 +26169,7 @@
       <c r="P425" s="38"/>
       <c r="Q425" s="27"/>
     </row>
-    <row r="426" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="426" spans="1:17" customFormat="1" ht="15.75">
       <c r="A426" s="2">
         <v>900</v>
       </c>
@@ -25437,7 +26210,7 @@
       <c r="P426" s="38"/>
       <c r="Q426" s="27"/>
     </row>
-    <row r="427" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="427" spans="1:17" customFormat="1" ht="15.75">
       <c r="A427" s="2">
         <v>900</v>
       </c>
@@ -25478,7 +26251,7 @@
       <c r="P427" s="38"/>
       <c r="Q427" s="27"/>
     </row>
-    <row r="428" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="428" spans="1:17" customFormat="1" ht="15.75">
       <c r="A428" s="2">
         <v>900</v>
       </c>
@@ -25519,7 +26292,7 @@
       <c r="P428" s="38"/>
       <c r="Q428" s="27"/>
     </row>
-    <row r="429" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="429" spans="1:17" customFormat="1" ht="15.75">
       <c r="A429" s="2">
         <v>900</v>
       </c>
@@ -25560,7 +26333,7 @@
       <c r="P429" s="38"/>
       <c r="Q429" s="27"/>
     </row>
-    <row r="430" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="430" spans="1:17" customFormat="1" ht="15.75">
       <c r="A430" s="2">
         <v>900</v>
       </c>
@@ -25601,7 +26374,7 @@
       <c r="P430" s="38"/>
       <c r="Q430" s="27"/>
     </row>
-    <row r="431" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="431" spans="1:17" customFormat="1" ht="15.75">
       <c r="A431" s="2">
         <v>900</v>
       </c>
@@ -25638,7 +26411,7 @@
       <c r="P431" s="38"/>
       <c r="Q431" s="27"/>
     </row>
-    <row r="432" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="432" spans="1:17" customFormat="1" ht="15.75">
       <c r="A432" s="2">
         <v>900</v>
       </c>
@@ -25677,7 +26450,7 @@
       <c r="P432" s="38"/>
       <c r="Q432" s="27"/>
     </row>
-    <row r="433" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="433" spans="1:17" customFormat="1" ht="15.75">
       <c r="A433" s="2">
         <v>900</v>
       </c>
@@ -25716,7 +26489,7 @@
       <c r="P433" s="38"/>
       <c r="Q433" s="27"/>
     </row>
-    <row r="434" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="434" spans="1:17" customFormat="1" ht="15.75">
       <c r="A434" s="2">
         <v>900</v>
       </c>
@@ -25755,7 +26528,7 @@
       <c r="P434" s="38"/>
       <c r="Q434" s="27"/>
     </row>
-    <row r="435" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="435" spans="1:17" customFormat="1" ht="15.75">
       <c r="A435" s="2">
         <v>900</v>
       </c>
@@ -25794,7 +26567,7 @@
       <c r="P435" s="38"/>
       <c r="Q435" s="27"/>
     </row>
-    <row r="436" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="436" spans="1:17" customFormat="1" ht="15.75">
       <c r="A436" s="2">
         <v>900</v>
       </c>
@@ -25833,7 +26606,7 @@
       <c r="P436" s="38"/>
       <c r="Q436" s="27"/>
     </row>
-    <row r="437" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="437" spans="1:17" customFormat="1" ht="15.75">
       <c r="A437" s="2">
         <v>900</v>
       </c>
@@ -25870,7 +26643,7 @@
       <c r="P437" s="38"/>
       <c r="Q437" s="27"/>
     </row>
-    <row r="438" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="438" spans="1:17" customFormat="1" ht="15.75">
       <c r="A438" s="2">
         <v>900</v>
       </c>
@@ -25902,18 +26675,22 @@
       <c r="J438" s="10">
         <v>1</v>
       </c>
-      <c r="K438" s="10"/>
-      <c r="L438" s="10"/>
+      <c r="K438" s="28">
+        <v>1</v>
+      </c>
+      <c r="L438" s="28">
+        <v>1</v>
+      </c>
       <c r="M438" s="10">
         <f t="shared" si="10"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N438" s="38"/>
       <c r="O438" s="38"/>
       <c r="P438" s="38"/>
       <c r="Q438" s="27"/>
     </row>
-    <row r="439" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="439" spans="1:17" customFormat="1" ht="15.75">
       <c r="A439" s="2">
         <v>900</v>
       </c>
@@ -25945,18 +26722,22 @@
       <c r="J439" s="10">
         <v>1</v>
       </c>
-      <c r="K439" s="10"/>
-      <c r="L439" s="10"/>
+      <c r="K439" s="28">
+        <v>1</v>
+      </c>
+      <c r="L439" s="28">
+        <v>1</v>
+      </c>
       <c r="M439" s="10">
         <f t="shared" si="10"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N439" s="38"/>
       <c r="O439" s="38"/>
       <c r="P439" s="38"/>
       <c r="Q439" s="27"/>
     </row>
-    <row r="440" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="440" spans="1:17" customFormat="1" ht="15.75">
       <c r="A440" s="2">
         <v>900</v>
       </c>
@@ -25988,18 +26769,22 @@
       <c r="J440" s="10">
         <v>1</v>
       </c>
-      <c r="K440" s="10"/>
-      <c r="L440" s="10"/>
+      <c r="K440" s="28">
+        <v>1</v>
+      </c>
+      <c r="L440" s="28">
+        <v>1</v>
+      </c>
       <c r="M440" s="10">
         <f t="shared" si="10"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N440" s="38"/>
       <c r="O440" s="38"/>
       <c r="P440" s="38"/>
       <c r="Q440" s="27"/>
     </row>
-    <row r="441" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="441" spans="1:17" customFormat="1" ht="15.75">
       <c r="A441" s="2">
         <v>900</v>
       </c>
@@ -26031,18 +26816,22 @@
       <c r="J441" s="10">
         <v>1</v>
       </c>
-      <c r="K441" s="10"/>
-      <c r="L441" s="10"/>
+      <c r="K441" s="28">
+        <v>1</v>
+      </c>
+      <c r="L441" s="28">
+        <v>1</v>
+      </c>
       <c r="M441" s="10">
         <f t="shared" si="10"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N441" s="38"/>
       <c r="O441" s="38"/>
       <c r="P441" s="38"/>
       <c r="Q441" s="27"/>
     </row>
-    <row r="442" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="442" spans="1:17" customFormat="1" ht="15.75">
       <c r="A442" s="2">
         <v>900</v>
       </c>
@@ -26074,18 +26863,22 @@
       <c r="J442" s="10">
         <v>1</v>
       </c>
-      <c r="K442" s="10"/>
-      <c r="L442" s="10"/>
+      <c r="K442" s="28">
+        <v>1</v>
+      </c>
+      <c r="L442" s="28">
+        <v>1</v>
+      </c>
       <c r="M442" s="10">
         <f t="shared" si="10"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N442" s="38"/>
       <c r="O442" s="38"/>
       <c r="P442" s="38"/>
       <c r="Q442" s="27"/>
     </row>
-    <row r="443" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="443" spans="1:17" customFormat="1" ht="15.75">
       <c r="A443" s="2">
         <v>900</v>
       </c>
@@ -26117,18 +26910,22 @@
       <c r="J443" s="10">
         <v>1</v>
       </c>
-      <c r="K443" s="10"/>
-      <c r="L443" s="10"/>
+      <c r="K443" s="28">
+        <v>1</v>
+      </c>
+      <c r="L443" s="28">
+        <v>1</v>
+      </c>
       <c r="M443" s="10">
         <f t="shared" si="10"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N443" s="38"/>
       <c r="O443" s="38"/>
       <c r="P443" s="38"/>
       <c r="Q443" s="27"/>
     </row>
-    <row r="444" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="444" spans="1:17" customFormat="1" ht="15.75">
       <c r="A444" s="2">
         <v>900</v>
       </c>
@@ -26160,18 +26957,22 @@
       <c r="J444" s="10">
         <v>1</v>
       </c>
-      <c r="K444" s="10"/>
-      <c r="L444" s="10"/>
+      <c r="K444" s="28">
+        <v>1</v>
+      </c>
+      <c r="L444" s="28">
+        <v>1</v>
+      </c>
       <c r="M444" s="10">
         <f t="shared" si="10"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N444" s="38"/>
       <c r="O444" s="38"/>
       <c r="P444" s="38"/>
       <c r="Q444" s="27"/>
     </row>
-    <row r="445" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="445" spans="1:17" customFormat="1" ht="15.75">
       <c r="A445" s="2">
         <v>900</v>
       </c>
@@ -26203,18 +27004,22 @@
       <c r="J445" s="10">
         <v>1</v>
       </c>
-      <c r="K445" s="10"/>
-      <c r="L445" s="10"/>
+      <c r="K445" s="28">
+        <v>1</v>
+      </c>
+      <c r="L445" s="28">
+        <v>1</v>
+      </c>
       <c r="M445" s="10">
         <f t="shared" si="10"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N445" s="38"/>
       <c r="O445" s="38"/>
       <c r="P445" s="38"/>
       <c r="Q445" s="27"/>
     </row>
-    <row r="446" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="446" spans="1:17" customFormat="1" ht="15.75">
       <c r="A446" s="2">
         <v>900</v>
       </c>
@@ -26246,18 +27051,22 @@
       <c r="J446" s="10">
         <v>1</v>
       </c>
-      <c r="K446" s="10"/>
-      <c r="L446" s="10"/>
+      <c r="K446" s="28">
+        <v>1</v>
+      </c>
+      <c r="L446" s="28">
+        <v>1</v>
+      </c>
       <c r="M446" s="10">
         <f t="shared" si="10"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N446" s="38"/>
       <c r="O446" s="38"/>
       <c r="P446" s="38"/>
       <c r="Q446" s="27"/>
     </row>
-    <row r="447" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="447" spans="1:17" customFormat="1" ht="15.75">
       <c r="A447" s="2">
         <v>900</v>
       </c>
@@ -26289,18 +27098,22 @@
       <c r="J447" s="10">
         <v>1</v>
       </c>
-      <c r="K447" s="10"/>
-      <c r="L447" s="10"/>
+      <c r="K447" s="28">
+        <v>1</v>
+      </c>
+      <c r="L447" s="28">
+        <v>1</v>
+      </c>
       <c r="M447" s="10">
         <f t="shared" si="10"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N447" s="38"/>
       <c r="O447" s="38"/>
       <c r="P447" s="38"/>
       <c r="Q447" s="27"/>
     </row>
-    <row r="448" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="448" spans="1:17" customFormat="1" ht="15.75">
       <c r="A448" s="2">
         <v>900</v>
       </c>
@@ -26332,18 +27145,22 @@
       <c r="J448" s="10">
         <v>1</v>
       </c>
-      <c r="K448" s="10"/>
-      <c r="L448" s="10"/>
+      <c r="K448" s="28">
+        <v>1</v>
+      </c>
+      <c r="L448" s="28">
+        <v>1</v>
+      </c>
       <c r="M448" s="10">
         <f t="shared" si="10"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N448" s="38"/>
       <c r="O448" s="38"/>
       <c r="P448" s="38"/>
       <c r="Q448" s="27"/>
     </row>
-    <row r="449" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="449" spans="1:17" customFormat="1" ht="15.75">
       <c r="A449" s="2">
         <v>900</v>
       </c>
@@ -26375,18 +27192,22 @@
       <c r="J449" s="10">
         <v>1</v>
       </c>
-      <c r="K449" s="10"/>
-      <c r="L449" s="10"/>
+      <c r="K449" s="28">
+        <v>1</v>
+      </c>
+      <c r="L449" s="28">
+        <v>1</v>
+      </c>
       <c r="M449" s="10">
         <f t="shared" si="10"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N449" s="38"/>
       <c r="O449" s="38"/>
       <c r="P449" s="38"/>
       <c r="Q449" s="27"/>
     </row>
-    <row r="450" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="450" spans="1:17" customFormat="1" ht="15.75">
       <c r="A450" s="2">
         <v>900</v>
       </c>
@@ -26418,18 +27239,22 @@
       <c r="J450" s="10">
         <v>1</v>
       </c>
-      <c r="K450" s="10"/>
-      <c r="L450" s="10"/>
+      <c r="K450" s="28">
+        <v>1</v>
+      </c>
+      <c r="L450" s="28">
+        <v>1</v>
+      </c>
       <c r="M450" s="10">
         <f t="shared" si="10"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N450" s="38"/>
       <c r="O450" s="38"/>
       <c r="P450" s="38"/>
       <c r="Q450" s="27"/>
     </row>
-    <row r="451" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="451" spans="1:17" customFormat="1" ht="15.75">
       <c r="A451" s="2">
         <v>900</v>
       </c>
@@ -26461,18 +27286,22 @@
       <c r="J451" s="10">
         <v>1</v>
       </c>
-      <c r="K451" s="10"/>
-      <c r="L451" s="10"/>
+      <c r="K451" s="28">
+        <v>1</v>
+      </c>
+      <c r="L451" s="28">
+        <v>1</v>
+      </c>
       <c r="M451" s="10">
         <f t="shared" si="10"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N451" s="38"/>
       <c r="O451" s="38"/>
       <c r="P451" s="38"/>
       <c r="Q451" s="27"/>
     </row>
-    <row r="452" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="452" spans="1:17" customFormat="1" ht="15.75">
       <c r="A452" s="2">
         <v>900</v>
       </c>
@@ -26509,7 +27338,7 @@
       <c r="P452" s="38"/>
       <c r="Q452" s="27"/>
     </row>
-    <row r="453" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="453" spans="1:17" customFormat="1" ht="15.75">
       <c r="A453" s="2">
         <v>900</v>
       </c>
@@ -26546,7 +27375,7 @@
       <c r="P453" s="38"/>
       <c r="Q453" s="27"/>
     </row>
-    <row r="454" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="454" spans="1:17" customFormat="1" ht="15.75">
       <c r="A454" s="2">
         <v>900</v>
       </c>
@@ -26583,7 +27412,7 @@
       <c r="P454" s="38"/>
       <c r="Q454" s="27"/>
     </row>
-    <row r="455" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="455" spans="1:17" customFormat="1" ht="15.75">
       <c r="A455" s="2">
         <v>900</v>
       </c>
@@ -26620,7 +27449,7 @@
       <c r="P455" s="38"/>
       <c r="Q455" s="27"/>
     </row>
-    <row r="456" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="456" spans="1:17" customFormat="1" ht="15.75">
       <c r="A456" s="2">
         <v>900</v>
       </c>
@@ -26657,7 +27486,7 @@
       <c r="P456" s="38"/>
       <c r="Q456" s="27"/>
     </row>
-    <row r="457" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="457" spans="1:17" customFormat="1" ht="15.75">
       <c r="A457" s="2">
         <v>900</v>
       </c>
@@ -26694,7 +27523,7 @@
       <c r="P457" s="38"/>
       <c r="Q457" s="27"/>
     </row>
-    <row r="458" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="458" spans="1:17" customFormat="1" ht="15.75">
       <c r="A458" s="2">
         <v>900</v>
       </c>
@@ -26733,7 +27562,7 @@
       <c r="P458" s="38"/>
       <c r="Q458" s="27"/>
     </row>
-    <row r="459" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="459" spans="1:17" customFormat="1" ht="15.75">
       <c r="A459" s="2">
         <v>900</v>
       </c>
@@ -26772,7 +27601,7 @@
       <c r="P459" s="38"/>
       <c r="Q459" s="27"/>
     </row>
-    <row r="460" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="460" spans="1:17" customFormat="1" ht="15.75">
       <c r="A460" s="2">
         <v>900</v>
       </c>
@@ -26811,7 +27640,7 @@
       <c r="P460" s="38"/>
       <c r="Q460" s="27"/>
     </row>
-    <row r="461" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="461" spans="1:17" customFormat="1" ht="15.75">
       <c r="A461" s="2">
         <v>900</v>
       </c>
@@ -26850,7 +27679,7 @@
       <c r="P461" s="38"/>
       <c r="Q461" s="27"/>
     </row>
-    <row r="462" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="462" spans="1:17" customFormat="1" ht="15.75">
       <c r="A462" s="2">
         <v>900</v>
       </c>
@@ -26889,7 +27718,7 @@
       <c r="P462" s="38"/>
       <c r="Q462" s="27"/>
     </row>
-    <row r="463" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="463" spans="1:17" customFormat="1" ht="15.75">
       <c r="A463" s="2">
         <v>900</v>
       </c>
@@ -26928,7 +27757,7 @@
       <c r="P463" s="38"/>
       <c r="Q463" s="27"/>
     </row>
-    <row r="464" spans="1:17" ht="15.75" hidden="1">
+    <row r="464" spans="1:17" ht="15.75">
       <c r="A464" s="30">
         <v>900</v>
       </c>
@@ -26960,14 +27789,18 @@
       <c r="J464" s="28">
         <v>1</v>
       </c>
-      <c r="K464" s="28"/>
-      <c r="L464" s="28"/>
+      <c r="K464" s="28">
+        <v>1</v>
+      </c>
+      <c r="L464" s="28">
+        <v>1</v>
+      </c>
       <c r="M464" s="28">
         <f t="shared" si="10"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="465" spans="1:17" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465" spans="1:17" ht="15.75">
       <c r="A465" s="30">
         <v>900</v>
       </c>
@@ -26999,14 +27832,18 @@
       <c r="J465" s="28">
         <v>1</v>
       </c>
-      <c r="K465" s="28"/>
-      <c r="L465" s="28"/>
+      <c r="K465" s="28">
+        <v>1</v>
+      </c>
+      <c r="L465" s="28">
+        <v>1</v>
+      </c>
       <c r="M465" s="28">
         <f t="shared" si="10"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="466" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="466" spans="1:17" customFormat="1" ht="15.75">
       <c r="A466" s="2">
         <v>900</v>
       </c>
@@ -27043,7 +27880,7 @@
       <c r="P466" s="38"/>
       <c r="Q466" s="27"/>
     </row>
-    <row r="467" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="467" spans="1:17" customFormat="1" ht="15.75">
       <c r="A467" s="2">
         <v>900</v>
       </c>
@@ -27080,7 +27917,7 @@
       <c r="P467" s="38"/>
       <c r="Q467" s="27"/>
     </row>
-    <row r="468" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="468" spans="1:17" customFormat="1" ht="15.75">
       <c r="A468" s="2">
         <v>900</v>
       </c>
@@ -27117,7 +27954,7 @@
       <c r="P468" s="38"/>
       <c r="Q468" s="27"/>
     </row>
-    <row r="469" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="469" spans="1:17" customFormat="1" ht="15.75">
       <c r="A469" s="2">
         <v>900</v>
       </c>
@@ -27154,7 +27991,7 @@
       <c r="P469" s="38"/>
       <c r="Q469" s="27"/>
     </row>
-    <row r="470" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="470" spans="1:17" customFormat="1" ht="15.75">
       <c r="A470" s="2">
         <v>900</v>
       </c>
@@ -27191,7 +28028,7 @@
       <c r="P470" s="38"/>
       <c r="Q470" s="27"/>
     </row>
-    <row r="471" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="471" spans="1:17" customFormat="1" ht="15.75">
       <c r="A471" s="2">
         <v>900</v>
       </c>
@@ -27228,7 +28065,7 @@
       <c r="P471" s="38"/>
       <c r="Q471" s="27"/>
     </row>
-    <row r="472" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="472" spans="1:17" customFormat="1" ht="15.75">
       <c r="A472" s="2">
         <v>900</v>
       </c>
@@ -27265,7 +28102,7 @@
       <c r="P472" s="38"/>
       <c r="Q472" s="27"/>
     </row>
-    <row r="473" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="473" spans="1:17" customFormat="1" ht="15.75">
       <c r="A473" s="2">
         <v>900</v>
       </c>
@@ -27302,7 +28139,7 @@
       <c r="P473" s="38"/>
       <c r="Q473" s="27"/>
     </row>
-    <row r="474" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="474" spans="1:17" customFormat="1" ht="15.75">
       <c r="A474" s="2">
         <v>900</v>
       </c>
@@ -27334,18 +28171,22 @@
       <c r="J474" s="10">
         <v>1</v>
       </c>
-      <c r="K474" s="10"/>
-      <c r="L474" s="10"/>
+      <c r="K474" s="28">
+        <v>1</v>
+      </c>
+      <c r="L474" s="28">
+        <v>1</v>
+      </c>
       <c r="M474" s="10">
         <f t="shared" si="11"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N474" s="38"/>
       <c r="O474" s="38"/>
       <c r="P474" s="38"/>
       <c r="Q474" s="27"/>
     </row>
-    <row r="475" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="475" spans="1:17" customFormat="1" ht="15.75">
       <c r="A475" s="2">
         <v>900</v>
       </c>
@@ -27384,7 +28225,7 @@
       <c r="P475" s="38"/>
       <c r="Q475" s="27"/>
     </row>
-    <row r="476" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="476" spans="1:17" customFormat="1" ht="15.75">
       <c r="A476" s="2">
         <v>900</v>
       </c>
@@ -27425,7 +28266,7 @@
       <c r="P476" s="38"/>
       <c r="Q476" s="27"/>
     </row>
-    <row r="477" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="477" spans="1:17" customFormat="1" ht="15.75">
       <c r="A477" s="2">
         <v>900</v>
       </c>
@@ -27466,7 +28307,7 @@
       <c r="P477" s="38"/>
       <c r="Q477" s="27"/>
     </row>
-    <row r="478" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="478" spans="1:17" customFormat="1" ht="15.75">
       <c r="A478" s="2">
         <v>900</v>
       </c>
@@ -27505,7 +28346,7 @@
       <c r="P478" s="38"/>
       <c r="Q478" s="27"/>
     </row>
-    <row r="479" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="479" spans="1:17" customFormat="1" ht="15.75">
       <c r="A479" s="2">
         <v>900</v>
       </c>
@@ -27544,7 +28385,7 @@
       <c r="P479" s="38"/>
       <c r="Q479" s="27"/>
     </row>
-    <row r="480" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="480" spans="1:17" customFormat="1" ht="15.75">
       <c r="A480" s="2">
         <v>900</v>
       </c>
@@ -27583,7 +28424,7 @@
       <c r="P480" s="38"/>
       <c r="Q480" s="27"/>
     </row>
-    <row r="481" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="481" spans="1:17" customFormat="1" ht="15.75">
       <c r="A481" s="2">
         <v>900</v>
       </c>
@@ -27620,7 +28461,7 @@
       <c r="P481" s="38"/>
       <c r="Q481" s="27"/>
     </row>
-    <row r="482" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="482" spans="1:17" customFormat="1" ht="15.75">
       <c r="A482" s="2">
         <v>900</v>
       </c>
@@ -27652,18 +28493,22 @@
       <c r="J482" s="10">
         <v>1</v>
       </c>
-      <c r="K482" s="10"/>
-      <c r="L482" s="10"/>
+      <c r="K482" s="28">
+        <v>1</v>
+      </c>
+      <c r="L482" s="28">
+        <v>1</v>
+      </c>
       <c r="M482" s="10">
         <f t="shared" si="11"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N482" s="38"/>
       <c r="O482" s="38"/>
       <c r="P482" s="38"/>
       <c r="Q482" s="27"/>
     </row>
-    <row r="483" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="483" spans="1:17" customFormat="1" ht="15.75">
       <c r="A483" s="2">
         <v>900</v>
       </c>
@@ -27695,18 +28540,22 @@
       <c r="J483" s="10">
         <v>1</v>
       </c>
-      <c r="K483" s="10"/>
-      <c r="L483" s="10"/>
+      <c r="K483" s="28">
+        <v>1</v>
+      </c>
+      <c r="L483" s="28">
+        <v>1</v>
+      </c>
       <c r="M483" s="10">
         <f t="shared" si="11"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N483" s="38"/>
       <c r="O483" s="38"/>
       <c r="P483" s="38"/>
       <c r="Q483" s="27"/>
     </row>
-    <row r="484" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="484" spans="1:17" customFormat="1" ht="15.75">
       <c r="A484" s="2">
         <v>900</v>
       </c>
@@ -27738,18 +28587,22 @@
       <c r="J484" s="10">
         <v>1</v>
       </c>
-      <c r="K484" s="10"/>
-      <c r="L484" s="10"/>
+      <c r="K484" s="28">
+        <v>1</v>
+      </c>
+      <c r="L484" s="28">
+        <v>1</v>
+      </c>
       <c r="M484" s="10">
         <f t="shared" si="11"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N484" s="38"/>
       <c r="O484" s="38"/>
       <c r="P484" s="38"/>
       <c r="Q484" s="27"/>
     </row>
-    <row r="485" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="485" spans="1:17" customFormat="1" ht="15.75">
       <c r="A485" s="2">
         <v>900</v>
       </c>
@@ -27781,18 +28634,22 @@
       <c r="J485" s="10">
         <v>1</v>
       </c>
-      <c r="K485" s="10"/>
-      <c r="L485" s="10"/>
+      <c r="K485" s="28">
+        <v>1</v>
+      </c>
+      <c r="L485" s="28">
+        <v>1</v>
+      </c>
       <c r="M485" s="10">
         <f t="shared" si="11"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N485" s="38"/>
       <c r="O485" s="38"/>
       <c r="P485" s="38"/>
       <c r="Q485" s="27"/>
     </row>
-    <row r="486" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="486" spans="1:17" customFormat="1" ht="15.75">
       <c r="A486" s="2">
         <v>900</v>
       </c>
@@ -27829,7 +28686,7 @@
       <c r="P486" s="38"/>
       <c r="Q486" s="27"/>
     </row>
-    <row r="487" spans="1:17" ht="15.75" hidden="1">
+    <row r="487" spans="1:17" ht="15.75">
       <c r="A487" s="30">
         <v>900</v>
       </c>
@@ -27864,7 +28721,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="488" spans="1:17" ht="15.75" hidden="1">
+    <row r="488" spans="1:17" ht="15.75">
       <c r="A488" s="30">
         <v>900</v>
       </c>
@@ -27899,7 +28756,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="489" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="489" spans="1:17" customFormat="1" ht="15.75">
       <c r="A489" s="2">
         <v>900</v>
       </c>
@@ -27938,7 +28795,7 @@
       <c r="P489" s="38"/>
       <c r="Q489" s="27"/>
     </row>
-    <row r="490" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="490" spans="1:17" customFormat="1" ht="15.75">
       <c r="A490" s="2">
         <v>900</v>
       </c>
@@ -27977,7 +28834,7 @@
       <c r="P490" s="38"/>
       <c r="Q490" s="27"/>
     </row>
-    <row r="491" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="491" spans="1:17" customFormat="1" ht="15.75">
       <c r="A491" s="2">
         <v>900</v>
       </c>
@@ -28009,18 +28866,22 @@
       <c r="J491" s="28">
         <v>1</v>
       </c>
-      <c r="K491" s="10"/>
-      <c r="L491" s="10"/>
+      <c r="K491" s="28">
+        <v>1</v>
+      </c>
+      <c r="L491" s="28">
+        <v>1</v>
+      </c>
       <c r="M491" s="10">
         <f t="shared" si="11"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N491" s="38"/>
       <c r="O491" s="38"/>
       <c r="P491" s="38"/>
       <c r="Q491" s="27"/>
     </row>
-    <row r="492" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="492" spans="1:17" customFormat="1" ht="15.75">
       <c r="A492" s="2">
         <v>900</v>
       </c>
@@ -28052,18 +28913,22 @@
       <c r="J492" s="28">
         <v>1</v>
       </c>
-      <c r="K492" s="10"/>
-      <c r="L492" s="10"/>
+      <c r="K492" s="28">
+        <v>1</v>
+      </c>
+      <c r="L492" s="28">
+        <v>1</v>
+      </c>
       <c r="M492" s="10">
         <f t="shared" si="11"/>
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="N492" s="38"/>
       <c r="O492" s="38"/>
       <c r="P492" s="38"/>
       <c r="Q492" s="27"/>
     </row>
-    <row r="493" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="493" spans="1:17" customFormat="1" ht="15.75">
       <c r="A493" s="2">
         <v>900</v>
       </c>
@@ -28104,7 +28969,7 @@
       <c r="P493" s="38"/>
       <c r="Q493" s="27"/>
     </row>
-    <row r="494" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="494" spans="1:17" customFormat="1" ht="15.75">
       <c r="A494" s="2">
         <v>900</v>
       </c>
@@ -28145,7 +29010,7 @@
       <c r="P494" s="38"/>
       <c r="Q494" s="27"/>
     </row>
-    <row r="495" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="495" spans="1:17" customFormat="1" ht="15.75">
       <c r="A495" s="2">
         <v>1000</v>
       </c>
@@ -28182,7 +29047,7 @@
       <c r="P495" s="38"/>
       <c r="Q495" s="27"/>
     </row>
-    <row r="496" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="496" spans="1:17" customFormat="1" ht="15.75">
       <c r="A496" s="2">
         <v>1000</v>
       </c>
@@ -28219,7 +29084,7 @@
       <c r="P496" s="38"/>
       <c r="Q496" s="27"/>
     </row>
-    <row r="497" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="497" spans="1:17" customFormat="1" ht="15.75">
       <c r="A497" s="2">
         <v>1000</v>
       </c>
@@ -28256,7 +29121,7 @@
       <c r="P497" s="38"/>
       <c r="Q497" s="27"/>
     </row>
-    <row r="498" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="498" spans="1:17" customFormat="1" ht="15.75">
       <c r="A498" s="2">
         <v>1000</v>
       </c>
@@ -28293,7 +29158,7 @@
       <c r="P498" s="38"/>
       <c r="Q498" s="27"/>
     </row>
-    <row r="499" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="499" spans="1:17" customFormat="1" ht="15.75">
       <c r="A499" s="2">
         <v>1000</v>
       </c>
@@ -28330,7 +29195,7 @@
       <c r="P499" s="38"/>
       <c r="Q499" s="27"/>
     </row>
-    <row r="500" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="500" spans="1:17" customFormat="1" ht="15.75">
       <c r="A500" s="2">
         <v>1000</v>
       </c>
@@ -28367,7 +29232,7 @@
       <c r="P500" s="38"/>
       <c r="Q500" s="27"/>
     </row>
-    <row r="501" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="501" spans="1:17" customFormat="1" ht="15.75">
       <c r="A501" s="2">
         <v>1000</v>
       </c>
@@ -28404,7 +29269,7 @@
       <c r="P501" s="38"/>
       <c r="Q501" s="27"/>
     </row>
-    <row r="502" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="502" spans="1:17" customFormat="1" ht="15.75">
       <c r="A502" s="2">
         <v>1000</v>
       </c>
@@ -28441,7 +29306,7 @@
       <c r="P502" s="38"/>
       <c r="Q502" s="27"/>
     </row>
-    <row r="503" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="503" spans="1:17" customFormat="1" ht="15.75">
       <c r="A503" s="2">
         <v>1000</v>
       </c>
@@ -28478,7 +29343,7 @@
       <c r="P503" s="38"/>
       <c r="Q503" s="27"/>
     </row>
-    <row r="504" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="504" spans="1:17" customFormat="1" ht="15.75">
       <c r="A504" s="2">
         <v>1000</v>
       </c>
@@ -28515,7 +29380,7 @@
       <c r="P504" s="38"/>
       <c r="Q504" s="27"/>
     </row>
-    <row r="505" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="505" spans="1:17" customFormat="1" ht="15.75">
       <c r="A505" s="2">
         <v>1000</v>
       </c>
@@ -28552,7 +29417,7 @@
       <c r="P505" s="38"/>
       <c r="Q505" s="27"/>
     </row>
-    <row r="506" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="506" spans="1:17" customFormat="1" ht="15.75">
       <c r="A506" s="2">
         <v>1000</v>
       </c>
@@ -28589,7 +29454,7 @@
       <c r="P506" s="38"/>
       <c r="Q506" s="27"/>
     </row>
-    <row r="507" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="507" spans="1:17" customFormat="1" ht="15.75">
       <c r="A507" s="2">
         <v>1000</v>
       </c>
@@ -28626,7 +29491,7 @@
       <c r="P507" s="38"/>
       <c r="Q507" s="27"/>
     </row>
-    <row r="508" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="508" spans="1:17" customFormat="1" ht="15.75">
       <c r="A508" s="2">
         <v>1000</v>
       </c>
@@ -28663,7 +29528,7 @@
       <c r="P508" s="38"/>
       <c r="Q508" s="27"/>
     </row>
-    <row r="509" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="509" spans="1:17" customFormat="1" ht="15.75">
       <c r="A509" s="2">
         <v>1000</v>
       </c>
@@ -28700,7 +29565,7 @@
       <c r="P509" s="38"/>
       <c r="Q509" s="27"/>
     </row>
-    <row r="510" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="510" spans="1:17" customFormat="1" ht="15.75">
       <c r="A510" s="2">
         <v>1000</v>
       </c>
@@ -28737,7 +29602,7 @@
       <c r="P510" s="38"/>
       <c r="Q510" s="27"/>
     </row>
-    <row r="511" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="511" spans="1:17" customFormat="1" ht="15.75">
       <c r="A511" s="2">
         <v>1000</v>
       </c>
@@ -28774,7 +29639,7 @@
       <c r="P511" s="38"/>
       <c r="Q511" s="27"/>
     </row>
-    <row r="512" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="512" spans="1:17" customFormat="1" ht="15.75">
       <c r="A512" s="2">
         <v>1000</v>
       </c>
@@ -28811,7 +29676,7 @@
       <c r="P512" s="38"/>
       <c r="Q512" s="27"/>
     </row>
-    <row r="513" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="513" spans="1:17" customFormat="1" ht="15.75">
       <c r="A513" s="2">
         <v>1000</v>
       </c>
@@ -28848,7 +29713,7 @@
       <c r="P513" s="38"/>
       <c r="Q513" s="27"/>
     </row>
-    <row r="514" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="514" spans="1:17" customFormat="1" ht="15.75">
       <c r="A514" s="2">
         <v>1000</v>
       </c>
@@ -28885,7 +29750,7 @@
       <c r="P514" s="38"/>
       <c r="Q514" s="27"/>
     </row>
-    <row r="515" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="515" spans="1:17" customFormat="1" ht="15.75">
       <c r="A515" s="2">
         <v>1000</v>
       </c>
@@ -28922,7 +29787,7 @@
       <c r="P515" s="38"/>
       <c r="Q515" s="27"/>
     </row>
-    <row r="516" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="516" spans="1:17" customFormat="1" ht="15.75">
       <c r="A516" s="2">
         <v>1000</v>
       </c>
@@ -28959,7 +29824,7 @@
       <c r="P516" s="38"/>
       <c r="Q516" s="27"/>
     </row>
-    <row r="517" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="517" spans="1:17" customFormat="1" ht="15.75">
       <c r="A517" s="2">
         <v>1000</v>
       </c>
@@ -28996,7 +29861,7 @@
       <c r="P517" s="38"/>
       <c r="Q517" s="27"/>
     </row>
-    <row r="518" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="518" spans="1:17" customFormat="1" ht="15.75">
       <c r="A518" s="4">
         <v>1100</v>
       </c>
@@ -29031,7 +29896,7 @@
       <c r="P518" s="38"/>
       <c r="Q518" s="27"/>
     </row>
-    <row r="519" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="519" spans="1:17" customFormat="1" ht="15.75">
       <c r="A519" s="4">
         <v>1300</v>
       </c>
@@ -29068,7 +29933,7 @@
       <c r="P519" s="38"/>
       <c r="Q519" s="27"/>
     </row>
-    <row r="520" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="520" spans="1:17" customFormat="1" ht="15.75">
       <c r="A520" s="4">
         <v>1300</v>
       </c>
@@ -29109,7 +29974,7 @@
       <c r="P520" s="38"/>
       <c r="Q520" s="27"/>
     </row>
-    <row r="521" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="521" spans="1:17" customFormat="1" ht="15.75">
       <c r="A521" s="4">
         <v>1300</v>
       </c>
@@ -29150,7 +30015,7 @@
       <c r="P521" s="38"/>
       <c r="Q521" s="27"/>
     </row>
-    <row r="522" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="522" spans="1:17" customFormat="1" ht="15.75">
       <c r="A522" s="4">
         <v>1300</v>
       </c>
@@ -29187,7 +30052,7 @@
       <c r="P522" s="38"/>
       <c r="Q522" s="27"/>
     </row>
-    <row r="523" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="523" spans="1:17" customFormat="1" ht="15.75">
       <c r="A523" s="4">
         <v>1300</v>
       </c>
@@ -29224,7 +30089,7 @@
       <c r="P523" s="38"/>
       <c r="Q523" s="27"/>
     </row>
-    <row r="524" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="524" spans="1:17" customFormat="1" ht="15.75">
       <c r="A524" s="4">
         <v>1300</v>
       </c>
@@ -29261,7 +30126,7 @@
       <c r="P524" s="38"/>
       <c r="Q524" s="27"/>
     </row>
-    <row r="525" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="525" spans="1:17" customFormat="1" ht="15.75">
       <c r="A525" s="4">
         <v>1300</v>
       </c>
@@ -29298,7 +30163,7 @@
       <c r="P525" s="38"/>
       <c r="Q525" s="27"/>
     </row>
-    <row r="526" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="526" spans="1:17" customFormat="1" ht="15.75">
       <c r="A526" s="4">
         <v>1300</v>
       </c>
@@ -29335,7 +30200,7 @@
       <c r="P526" s="38"/>
       <c r="Q526" s="27"/>
     </row>
-    <row r="527" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="527" spans="1:17" customFormat="1" ht="15.75">
       <c r="A527" s="4">
         <v>1300</v>
       </c>
@@ -29372,7 +30237,7 @@
       <c r="P527" s="38"/>
       <c r="Q527" s="27"/>
     </row>
-    <row r="528" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="528" spans="1:17" customFormat="1" ht="15.75">
       <c r="A528" s="4">
         <v>1300</v>
       </c>
@@ -29413,7 +30278,7 @@
       <c r="P528" s="38"/>
       <c r="Q528" s="27"/>
     </row>
-    <row r="529" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="529" spans="1:17" customFormat="1" ht="15.75">
       <c r="A529" s="4">
         <v>1300</v>
       </c>
@@ -29454,7 +30319,7 @@
       <c r="P529" s="38"/>
       <c r="Q529" s="27"/>
     </row>
-    <row r="530" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="530" spans="1:17" customFormat="1" ht="15.75">
       <c r="A530" s="4">
         <v>1300</v>
       </c>
@@ -29491,7 +30356,7 @@
       <c r="P530" s="38"/>
       <c r="Q530" s="27"/>
     </row>
-    <row r="531" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="531" spans="1:17" customFormat="1" ht="15.75">
       <c r="A531" s="4">
         <v>1300</v>
       </c>
@@ -29528,7 +30393,7 @@
       <c r="P531" s="38"/>
       <c r="Q531" s="27"/>
     </row>
-    <row r="532" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="532" spans="1:17" customFormat="1" ht="15.75">
       <c r="A532" s="4">
         <v>1300</v>
       </c>
@@ -29569,7 +30434,7 @@
       <c r="P532" s="38"/>
       <c r="Q532" s="27"/>
     </row>
-    <row r="533" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="533" spans="1:17" customFormat="1" ht="15.75">
       <c r="A533" s="4">
         <v>1300</v>
       </c>
@@ -29610,7 +30475,7 @@
       <c r="P533" s="38"/>
       <c r="Q533" s="27"/>
     </row>
-    <row r="534" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="534" spans="1:17" customFormat="1" ht="15.75">
       <c r="A534" s="4">
         <v>1300</v>
       </c>
@@ -29651,7 +30516,7 @@
       <c r="P534" s="38"/>
       <c r="Q534" s="27"/>
     </row>
-    <row r="535" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="535" spans="1:17" customFormat="1" ht="15.75">
       <c r="A535" s="4">
         <v>1300</v>
       </c>
@@ -29692,7 +30557,7 @@
       <c r="P535" s="38"/>
       <c r="Q535" s="27"/>
     </row>
-    <row r="536" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="536" spans="1:17" customFormat="1" ht="15.75">
       <c r="A536" s="4">
         <v>1300</v>
       </c>
@@ -29733,7 +30598,7 @@
       <c r="P536" s="38"/>
       <c r="Q536" s="27"/>
     </row>
-    <row r="537" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="537" spans="1:17" customFormat="1" ht="15.75">
       <c r="A537" s="4">
         <v>1300</v>
       </c>
@@ -29774,7 +30639,7 @@
       <c r="P537" s="38"/>
       <c r="Q537" s="27"/>
     </row>
-    <row r="538" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="538" spans="1:17" customFormat="1" ht="15.75">
       <c r="A538" s="4">
         <v>1300</v>
       </c>
@@ -29815,7 +30680,7 @@
       <c r="P538" s="38"/>
       <c r="Q538" s="27"/>
     </row>
-    <row r="539" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="539" spans="1:17" customFormat="1" ht="15.75">
       <c r="A539" s="4">
         <v>1300</v>
       </c>
@@ -29856,7 +30721,7 @@
       <c r="P539" s="38"/>
       <c r="Q539" s="27"/>
     </row>
-    <row r="540" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="540" spans="1:17" customFormat="1" ht="15.75">
       <c r="A540" s="4">
         <v>1300</v>
       </c>
@@ -29897,7 +30762,7 @@
       <c r="P540" s="38"/>
       <c r="Q540" s="27"/>
     </row>
-    <row r="541" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="541" spans="1:17" customFormat="1" ht="15.75">
       <c r="A541" s="4">
         <v>1300</v>
       </c>
@@ -29938,7 +30803,7 @@
       <c r="P541" s="38"/>
       <c r="Q541" s="27"/>
     </row>
-    <row r="542" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="542" spans="1:17" customFormat="1" ht="15.75">
       <c r="A542" s="4">
         <v>1300</v>
       </c>
@@ -29979,7 +30844,7 @@
       <c r="P542" s="38"/>
       <c r="Q542" s="27"/>
     </row>
-    <row r="543" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="543" spans="1:17" customFormat="1" ht="15.75">
       <c r="A543" s="4">
         <v>1300</v>
       </c>
@@ -30020,7 +30885,7 @@
       <c r="P543" s="38"/>
       <c r="Q543" s="27"/>
     </row>
-    <row r="544" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="544" spans="1:17" customFormat="1" ht="15.75">
       <c r="A544" s="4">
         <v>1300</v>
       </c>
@@ -30061,7 +30926,7 @@
       <c r="P544" s="38"/>
       <c r="Q544" s="27"/>
     </row>
-    <row r="545" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="545" spans="1:17" customFormat="1" ht="15.75">
       <c r="A545" s="4">
         <v>1300</v>
       </c>
@@ -30102,7 +30967,7 @@
       <c r="P545" s="38"/>
       <c r="Q545" s="27"/>
     </row>
-    <row r="546" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="546" spans="1:17" customFormat="1" ht="15.75">
       <c r="A546" s="4">
         <v>1300</v>
       </c>
@@ -30139,7 +31004,7 @@
       <c r="P546" s="38"/>
       <c r="Q546" s="27"/>
     </row>
-    <row r="547" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="547" spans="1:17" customFormat="1" ht="15.75">
       <c r="A547" s="4">
         <v>1300</v>
       </c>
@@ -30176,7 +31041,7 @@
       <c r="P547" s="38"/>
       <c r="Q547" s="27"/>
     </row>
-    <row r="548" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="548" spans="1:17" customFormat="1" ht="15.75">
       <c r="A548" s="4">
         <v>1300</v>
       </c>
@@ -30213,7 +31078,7 @@
       <c r="P548" s="38"/>
       <c r="Q548" s="27"/>
     </row>
-    <row r="549" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="549" spans="1:17" customFormat="1" ht="15.75">
       <c r="A549" s="4">
         <v>1300</v>
       </c>
@@ -30250,7 +31115,7 @@
       <c r="P549" s="38"/>
       <c r="Q549" s="27"/>
     </row>
-    <row r="550" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="550" spans="1:17" customFormat="1" ht="15.75">
       <c r="A550" s="4">
         <v>1300</v>
       </c>
@@ -30291,7 +31156,7 @@
       <c r="P550" s="38"/>
       <c r="Q550" s="27"/>
     </row>
-    <row r="551" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="551" spans="1:17" customFormat="1" ht="15.75">
       <c r="A551" s="4">
         <v>1300</v>
       </c>
@@ -30332,7 +31197,7 @@
       <c r="P551" s="38"/>
       <c r="Q551" s="27"/>
     </row>
-    <row r="552" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="552" spans="1:17" customFormat="1" ht="15.75">
       <c r="A552" s="4">
         <v>1300</v>
       </c>
@@ -30373,7 +31238,7 @@
       <c r="P552" s="38"/>
       <c r="Q552" s="27"/>
     </row>
-    <row r="553" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="553" spans="1:17" customFormat="1" ht="15.75">
       <c r="A553" s="4">
         <v>1300</v>
       </c>
@@ -30414,7 +31279,7 @@
       <c r="P553" s="38"/>
       <c r="Q553" s="27"/>
     </row>
-    <row r="554" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="554" spans="1:17" customFormat="1" ht="15.75">
       <c r="A554" s="4">
         <v>1300</v>
       </c>
@@ -30451,7 +31316,7 @@
       <c r="P554" s="38"/>
       <c r="Q554" s="27"/>
     </row>
-    <row r="555" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="555" spans="1:17" customFormat="1" ht="15.75">
       <c r="A555" s="4">
         <v>1300</v>
       </c>
@@ -30488,7 +31353,7 @@
       <c r="P555" s="38"/>
       <c r="Q555" s="27"/>
     </row>
-    <row r="556" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="556" spans="1:17" customFormat="1" ht="15.75">
       <c r="A556" s="4">
         <v>1300</v>
       </c>
@@ -30525,7 +31390,7 @@
       <c r="P556" s="38"/>
       <c r="Q556" s="27"/>
     </row>
-    <row r="557" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="557" spans="1:17" customFormat="1" ht="15.75">
       <c r="A557" s="4">
         <v>1300</v>
       </c>
@@ -30562,7 +31427,7 @@
       <c r="P557" s="38"/>
       <c r="Q557" s="27"/>
     </row>
-    <row r="558" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="558" spans="1:17" customFormat="1" ht="15.75">
       <c r="A558" s="4">
         <v>1300</v>
       </c>
@@ -30599,7 +31464,7 @@
       <c r="P558" s="38"/>
       <c r="Q558" s="27"/>
     </row>
-    <row r="559" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="559" spans="1:17" customFormat="1" ht="15.75">
       <c r="A559" s="4">
         <v>1300</v>
       </c>
@@ -30636,7 +31501,7 @@
       <c r="P559" s="38"/>
       <c r="Q559" s="27"/>
     </row>
-    <row r="560" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="560" spans="1:17" customFormat="1" ht="15.75">
       <c r="A560" s="4">
         <v>1300</v>
       </c>
@@ -30673,7 +31538,7 @@
       <c r="P560" s="38"/>
       <c r="Q560" s="27"/>
     </row>
-    <row r="561" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="561" spans="1:17" customFormat="1" ht="15.75">
       <c r="A561" s="4">
         <v>1300</v>
       </c>
@@ -30714,7 +31579,7 @@
       <c r="P561" s="38"/>
       <c r="Q561" s="27"/>
     </row>
-    <row r="562" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="562" spans="1:17" customFormat="1" ht="15.75">
       <c r="A562" s="4">
         <v>1300</v>
       </c>
@@ -30755,7 +31620,7 @@
       <c r="P562" s="38"/>
       <c r="Q562" s="27"/>
     </row>
-    <row r="563" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="563" spans="1:17" customFormat="1" ht="15.75">
       <c r="A563" s="4">
         <v>1300</v>
       </c>
@@ -30796,7 +31661,7 @@
       <c r="P563" s="38"/>
       <c r="Q563" s="27"/>
     </row>
-    <row r="564" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="564" spans="1:17" customFormat="1" ht="15.75">
       <c r="A564" s="4">
         <v>1300</v>
       </c>
@@ -30837,7 +31702,7 @@
       <c r="P564" s="38"/>
       <c r="Q564" s="27"/>
     </row>
-    <row r="565" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="565" spans="1:17" customFormat="1" ht="15.75">
       <c r="A565" s="4">
         <v>1300</v>
       </c>
@@ -30874,7 +31739,7 @@
       <c r="P565" s="38"/>
       <c r="Q565" s="27"/>
     </row>
-    <row r="566" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="566" spans="1:17" customFormat="1" ht="15.75">
       <c r="A566" s="4">
         <v>1300</v>
       </c>
@@ -30911,7 +31776,7 @@
       <c r="P566" s="38"/>
       <c r="Q566" s="27"/>
     </row>
-    <row r="567" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="567" spans="1:17" customFormat="1" ht="15.75">
       <c r="A567" s="4">
         <v>1300</v>
       </c>
@@ -30948,7 +31813,7 @@
       <c r="P567" s="38"/>
       <c r="Q567" s="27"/>
     </row>
-    <row r="568" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="568" spans="1:17" customFormat="1" ht="15.75">
       <c r="A568" s="4">
         <v>1300</v>
       </c>
@@ -30985,7 +31850,7 @@
       <c r="P568" s="38"/>
       <c r="Q568" s="27"/>
     </row>
-    <row r="569" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="569" spans="1:17" customFormat="1" ht="15.75">
       <c r="A569" s="4">
         <v>1300</v>
       </c>
@@ -31022,7 +31887,7 @@
       <c r="P569" s="38"/>
       <c r="Q569" s="27"/>
     </row>
-    <row r="570" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="570" spans="1:17" customFormat="1" ht="15.75">
       <c r="A570" s="4">
         <v>1300</v>
       </c>
@@ -31059,7 +31924,7 @@
       <c r="P570" s="38"/>
       <c r="Q570" s="27"/>
     </row>
-    <row r="571" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="571" spans="1:17" customFormat="1" ht="15.75">
       <c r="A571" s="4">
         <v>1300</v>
       </c>
@@ -31096,7 +31961,7 @@
       <c r="P571" s="38"/>
       <c r="Q571" s="27"/>
     </row>
-    <row r="572" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="572" spans="1:17" customFormat="1" ht="15.75">
       <c r="A572" s="4">
         <v>1300</v>
       </c>
@@ -31133,7 +31998,7 @@
       <c r="P572" s="38"/>
       <c r="Q572" s="27"/>
     </row>
-    <row r="573" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="573" spans="1:17" customFormat="1" ht="15.75">
       <c r="A573" s="4">
         <v>1300</v>
       </c>
@@ -31170,7 +32035,7 @@
       <c r="P573" s="38"/>
       <c r="Q573" s="27"/>
     </row>
-    <row r="574" spans="1:17" ht="15.75" hidden="1">
+    <row r="574" spans="1:17" ht="15.75">
       <c r="A574" s="33">
         <v>1300</v>
       </c>
@@ -31207,7 +32072,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="575" spans="1:17" ht="15.75" hidden="1">
+    <row r="575" spans="1:17" ht="15.75">
       <c r="A575" s="33">
         <v>1300</v>
       </c>
@@ -31244,7 +32109,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="576" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="576" spans="1:17" customFormat="1" ht="15.75">
       <c r="A576" s="4">
         <v>1300</v>
       </c>
@@ -31281,7 +32146,7 @@
       <c r="P576" s="38"/>
       <c r="Q576" s="27"/>
     </row>
-    <row r="577" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="577" spans="1:17" customFormat="1" ht="15.75">
       <c r="A577" s="4">
         <v>1300</v>
       </c>
@@ -31318,7 +32183,7 @@
       <c r="P577" s="38"/>
       <c r="Q577" s="27"/>
     </row>
-    <row r="578" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="578" spans="1:17" customFormat="1" ht="15.75">
       <c r="A578" s="4">
         <v>1300</v>
       </c>
@@ -31355,7 +32220,7 @@
       <c r="P578" s="38"/>
       <c r="Q578" s="27"/>
     </row>
-    <row r="579" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="579" spans="1:17" customFormat="1" ht="15.75">
       <c r="A579" s="4">
         <v>1300</v>
       </c>
@@ -31392,7 +32257,7 @@
       <c r="P579" s="38"/>
       <c r="Q579" s="27"/>
     </row>
-    <row r="580" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="580" spans="1:17" customFormat="1" ht="15.75">
       <c r="A580" s="4">
         <v>1300</v>
       </c>
@@ -31429,7 +32294,7 @@
       <c r="P580" s="38"/>
       <c r="Q580" s="27"/>
     </row>
-    <row r="581" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="581" spans="1:17" customFormat="1" ht="15.75">
       <c r="A581" s="4">
         <v>1300</v>
       </c>
@@ -31466,7 +32331,7 @@
       <c r="P581" s="38"/>
       <c r="Q581" s="27"/>
     </row>
-    <row r="582" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="582" spans="1:17" customFormat="1" ht="15.75">
       <c r="A582" s="4">
         <v>1300</v>
       </c>
@@ -31503,7 +32368,7 @@
       <c r="P582" s="38"/>
       <c r="Q582" s="27"/>
     </row>
-    <row r="583" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="583" spans="1:17" customFormat="1" ht="15.75">
       <c r="A583" s="4">
         <v>1300</v>
       </c>
@@ -31540,7 +32405,7 @@
       <c r="P583" s="38"/>
       <c r="Q583" s="27"/>
     </row>
-    <row r="584" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="584" spans="1:17" customFormat="1" ht="15.75">
       <c r="A584" s="4">
         <v>1300</v>
       </c>
@@ -31577,7 +32442,7 @@
       <c r="P584" s="38"/>
       <c r="Q584" s="27"/>
     </row>
-    <row r="585" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="585" spans="1:17" customFormat="1" ht="15.75">
       <c r="A585" s="4">
         <v>1300</v>
       </c>
@@ -31614,7 +32479,7 @@
       <c r="P585" s="38"/>
       <c r="Q585" s="27"/>
     </row>
-    <row r="586" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="586" spans="1:17" customFormat="1" ht="15.75">
       <c r="A586" s="4">
         <v>1300</v>
       </c>
@@ -31649,7 +32514,7 @@
       <c r="P586" s="38"/>
       <c r="Q586" s="27"/>
     </row>
-    <row r="587" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="587" spans="1:17" customFormat="1" ht="15.75">
       <c r="A587" s="4">
         <v>1300</v>
       </c>
@@ -31686,7 +32551,7 @@
       <c r="P587" s="38"/>
       <c r="Q587" s="27"/>
     </row>
-    <row r="588" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="588" spans="1:17" customFormat="1" ht="15.75">
       <c r="A588" s="4">
         <v>1300</v>
       </c>
@@ -31723,7 +32588,7 @@
       <c r="P588" s="38"/>
       <c r="Q588" s="27"/>
     </row>
-    <row r="589" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="589" spans="1:17" customFormat="1" ht="15.75">
       <c r="A589" s="4">
         <v>1300</v>
       </c>
@@ -31760,7 +32625,7 @@
       <c r="P589" s="38"/>
       <c r="Q589" s="27"/>
     </row>
-    <row r="590" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="590" spans="1:17" customFormat="1" ht="15.75">
       <c r="A590" s="4">
         <v>1300</v>
       </c>
@@ -31797,7 +32662,7 @@
       <c r="P590" s="38"/>
       <c r="Q590" s="27"/>
     </row>
-    <row r="591" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="591" spans="1:17" customFormat="1" ht="15.75">
       <c r="A591" s="2">
         <v>1400</v>
       </c>
@@ -31832,7 +32697,7 @@
       <c r="P591" s="38"/>
       <c r="Q591" s="27"/>
     </row>
-    <row r="592" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="592" spans="1:17" customFormat="1" ht="15.75">
       <c r="A592" s="2">
         <v>1400</v>
       </c>
@@ -31869,7 +32734,7 @@
       <c r="P592" s="38"/>
       <c r="Q592" s="27"/>
     </row>
-    <row r="593" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="593" spans="1:17" customFormat="1" ht="15.75">
       <c r="A593" s="2">
         <v>1400</v>
       </c>
@@ -31906,7 +32771,7 @@
       <c r="P593" s="38"/>
       <c r="Q593" s="27"/>
     </row>
-    <row r="594" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="594" spans="1:17" customFormat="1" ht="15.75">
       <c r="A594" s="2">
         <v>1400</v>
       </c>
@@ -31943,7 +32808,7 @@
       <c r="P594" s="38"/>
       <c r="Q594" s="27"/>
     </row>
-    <row r="595" spans="1:17" customFormat="1" ht="15.75" hidden="1">
+    <row r="595" spans="1:17" customFormat="1" ht="15.75">
       <c r="A595" s="2">
         <v>1400</v>
       </c>
@@ -31988,13 +32853,7 @@
     <protectedRange sqref="D8:D94" name="Range1"/>
     <protectedRange sqref="D591" name="Range1_1"/>
   </protectedRanges>
-  <autoFilter ref="A7:AF595">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="کارگر"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A7:AF595"/>
   <mergeCells count="1">
     <mergeCell ref="AA1:AF1"/>
   </mergeCells>

--- a/RCM- پیشرفت کار کارشناسان- تکسونامی تجهیزات گندله سازی.xlsx
+++ b/RCM- پیشرفت کار کارشناسان- تکسونامی تجهیزات گندله سازی.xlsx
@@ -8297,6 +8297,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AF596"/>
   <sheetFormatPr defaultColWidth="12.125" defaultRowHeight="15"/>
   <cols>
@@ -8784,7 +8785,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="15.75">
+    <row r="8" spans="1:32" ht="15.75" hidden="1">
       <c r="A8" s="30">
         <v>100</v>
       </c>
@@ -8827,7 +8828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" customFormat="1" ht="15.75">
+    <row r="9" spans="1:32" customFormat="1" ht="15.75" hidden="1">
       <c r="A9" s="2">
         <v>100</v>
       </c>
@@ -8874,7 +8875,7 @@
       <c r="P9" s="38"/>
       <c r="Q9" s="27"/>
     </row>
-    <row r="10" spans="1:32" customFormat="1" ht="15.75">
+    <row r="10" spans="1:32" customFormat="1" ht="15.75" hidden="1">
       <c r="A10" s="2">
         <v>100</v>
       </c>
@@ -8921,7 +8922,7 @@
       <c r="P10" s="38"/>
       <c r="Q10" s="27"/>
     </row>
-    <row r="11" spans="1:32" ht="15.75">
+    <row r="11" spans="1:32" ht="15.75" hidden="1">
       <c r="A11" s="30">
         <v>100</v>
       </c>
@@ -8964,7 +8965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:32" customFormat="1" ht="15.75">
+    <row r="12" spans="1:32" customFormat="1" ht="15.75" hidden="1">
       <c r="A12" s="2">
         <v>100</v>
       </c>
@@ -9011,7 +9012,7 @@
       <c r="P12" s="38"/>
       <c r="Q12" s="27"/>
     </row>
-    <row r="13" spans="1:32" customFormat="1" ht="15.75">
+    <row r="13" spans="1:32" customFormat="1" ht="15.75" hidden="1">
       <c r="A13" s="2">
         <v>100</v>
       </c>
@@ -9058,7 +9059,7 @@
       <c r="P13" s="38"/>
       <c r="Q13" s="27"/>
     </row>
-    <row r="14" spans="1:32" customFormat="1" ht="15.75">
+    <row r="14" spans="1:32" customFormat="1" ht="15.75" hidden="1">
       <c r="A14" s="2">
         <v>100</v>
       </c>
@@ -9105,7 +9106,7 @@
       <c r="P14" s="38"/>
       <c r="Q14" s="27"/>
     </row>
-    <row r="15" spans="1:32" customFormat="1" ht="15.75">
+    <row r="15" spans="1:32" customFormat="1" ht="15.75" hidden="1">
       <c r="A15" s="2">
         <v>100</v>
       </c>
@@ -9199,7 +9200,7 @@
       <c r="P16" s="38"/>
       <c r="Q16" s="27"/>
     </row>
-    <row r="17" spans="1:17" customFormat="1" ht="15.75">
+    <row r="17" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A17" s="2">
         <v>100</v>
       </c>
@@ -9246,7 +9247,7 @@
       <c r="P17" s="38"/>
       <c r="Q17" s="27"/>
     </row>
-    <row r="18" spans="1:17" customFormat="1" ht="15.75">
+    <row r="18" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A18" s="2">
         <v>100</v>
       </c>
@@ -9293,7 +9294,7 @@
       <c r="P18" s="38"/>
       <c r="Q18" s="27"/>
     </row>
-    <row r="19" spans="1:17" customFormat="1" ht="15.75">
+    <row r="19" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A19" s="2">
         <v>100</v>
       </c>
@@ -9340,7 +9341,7 @@
       <c r="P19" s="38"/>
       <c r="Q19" s="27"/>
     </row>
-    <row r="20" spans="1:17" customFormat="1" ht="15.75">
+    <row r="20" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A20" s="2">
         <v>100</v>
       </c>
@@ -9387,7 +9388,7 @@
       <c r="P20" s="38"/>
       <c r="Q20" s="27"/>
     </row>
-    <row r="21" spans="1:17" customFormat="1" ht="15.75">
+    <row r="21" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A21" s="2">
         <v>100</v>
       </c>
@@ -9434,7 +9435,7 @@
       <c r="P21" s="38"/>
       <c r="Q21" s="27"/>
     </row>
-    <row r="22" spans="1:17" customFormat="1" ht="15.75">
+    <row r="22" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A22" s="2">
         <v>100</v>
       </c>
@@ -9481,7 +9482,7 @@
       <c r="P22" s="38"/>
       <c r="Q22" s="27"/>
     </row>
-    <row r="23" spans="1:17" customFormat="1" ht="15.75">
+    <row r="23" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A23" s="2">
         <v>100</v>
       </c>
@@ -9528,7 +9529,7 @@
       <c r="P23" s="38"/>
       <c r="Q23" s="27"/>
     </row>
-    <row r="24" spans="1:17" customFormat="1" ht="15.75">
+    <row r="24" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A24" s="2">
         <v>100</v>
       </c>
@@ -9575,7 +9576,7 @@
       <c r="P24" s="38"/>
       <c r="Q24" s="27"/>
     </row>
-    <row r="25" spans="1:17" customFormat="1" ht="15.75">
+    <row r="25" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A25" s="2">
         <v>100</v>
       </c>
@@ -9622,7 +9623,7 @@
       <c r="P25" s="38"/>
       <c r="Q25" s="27"/>
     </row>
-    <row r="26" spans="1:17" ht="15.75">
+    <row r="26" spans="1:17" ht="15.75" hidden="1">
       <c r="A26" s="30">
         <v>100</v>
       </c>
@@ -9665,7 +9666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:17" customFormat="1" ht="15.75">
+    <row r="27" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A27" s="2">
         <v>100</v>
       </c>
@@ -9712,7 +9713,7 @@
       <c r="P27" s="38"/>
       <c r="Q27" s="27"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75">
+    <row r="28" spans="1:17" ht="15.75" hidden="1">
       <c r="A28" s="30">
         <v>100</v>
       </c>
@@ -9755,7 +9756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75">
+    <row r="29" spans="1:17" ht="15.75" hidden="1">
       <c r="A29" s="30">
         <v>100</v>
       </c>
@@ -9798,7 +9799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75">
+    <row r="30" spans="1:17" ht="15.75" hidden="1">
       <c r="A30" s="30">
         <v>100</v>
       </c>
@@ -9841,7 +9842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75">
+    <row r="31" spans="1:17" ht="15.75" hidden="1">
       <c r="A31" s="30">
         <v>100</v>
       </c>
@@ -9884,7 +9885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75">
+    <row r="32" spans="1:17" ht="15.75" hidden="1">
       <c r="A32" s="30">
         <v>100</v>
       </c>
@@ -9927,7 +9928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75">
+    <row r="33" spans="1:17" ht="15.75" hidden="1">
       <c r="A33" s="30">
         <v>100</v>
       </c>
@@ -9970,7 +9971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" customFormat="1" ht="15.75">
+    <row r="34" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A34" s="2">
         <v>100</v>
       </c>
@@ -10017,7 +10018,7 @@
       <c r="P34" s="38"/>
       <c r="Q34" s="27"/>
     </row>
-    <row r="35" spans="1:17" customFormat="1" ht="15.75">
+    <row r="35" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A35" s="2">
         <v>100</v>
       </c>
@@ -10064,7 +10065,7 @@
       <c r="P35" s="38"/>
       <c r="Q35" s="27"/>
     </row>
-    <row r="36" spans="1:17" customFormat="1" ht="15.75">
+    <row r="36" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A36" s="2">
         <v>100</v>
       </c>
@@ -10105,7 +10106,7 @@
       <c r="P36" s="38"/>
       <c r="Q36" s="27"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75">
+    <row r="37" spans="1:17" ht="15.75" hidden="1">
       <c r="A37" s="30">
         <v>100</v>
       </c>
@@ -10144,7 +10145,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="38" spans="1:17" customFormat="1" ht="15.75">
+    <row r="38" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A38" s="2">
         <v>100</v>
       </c>
@@ -10191,7 +10192,7 @@
       <c r="P38" s="38"/>
       <c r="Q38" s="27"/>
     </row>
-    <row r="39" spans="1:17" customFormat="1" ht="15.75">
+    <row r="39" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A39" s="2">
         <v>100</v>
       </c>
@@ -10238,7 +10239,7 @@
       <c r="P39" s="38"/>
       <c r="Q39" s="27"/>
     </row>
-    <row r="40" spans="1:17" customFormat="1" ht="15.75">
+    <row r="40" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A40" s="2">
         <v>100</v>
       </c>
@@ -10285,7 +10286,7 @@
       <c r="P40" s="38"/>
       <c r="Q40" s="27"/>
     </row>
-    <row r="41" spans="1:17" customFormat="1" ht="15.75">
+    <row r="41" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A41" s="2">
         <v>100</v>
       </c>
@@ -10332,7 +10333,7 @@
       <c r="P41" s="38"/>
       <c r="Q41" s="27"/>
     </row>
-    <row r="42" spans="1:17" customFormat="1" ht="15.75">
+    <row r="42" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A42" s="2">
         <v>100</v>
       </c>
@@ -10379,7 +10380,7 @@
       <c r="P42" s="38"/>
       <c r="Q42" s="27"/>
     </row>
-    <row r="43" spans="1:17" customFormat="1" ht="15.75">
+    <row r="43" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A43" s="2">
         <v>100</v>
       </c>
@@ -10420,7 +10421,7 @@
       <c r="P43" s="38"/>
       <c r="Q43" s="27"/>
     </row>
-    <row r="44" spans="1:17" customFormat="1" ht="15.75">
+    <row r="44" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A44" s="2">
         <v>100</v>
       </c>
@@ -10461,7 +10462,7 @@
       <c r="P44" s="38"/>
       <c r="Q44" s="27"/>
     </row>
-    <row r="45" spans="1:17" customFormat="1" ht="15.75">
+    <row r="45" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A45" s="2">
         <v>100</v>
       </c>
@@ -10502,7 +10503,7 @@
       <c r="P45" s="38"/>
       <c r="Q45" s="27"/>
     </row>
-    <row r="46" spans="1:17" customFormat="1" ht="15.75">
+    <row r="46" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A46" s="2">
         <v>100</v>
       </c>
@@ -10543,7 +10544,7 @@
       <c r="P46" s="38"/>
       <c r="Q46" s="27"/>
     </row>
-    <row r="47" spans="1:17" customFormat="1" ht="15.75">
+    <row r="47" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A47" s="2">
         <v>100</v>
       </c>
@@ -10584,7 +10585,7 @@
       <c r="P47" s="38"/>
       <c r="Q47" s="27"/>
     </row>
-    <row r="48" spans="1:17" ht="15.75">
+    <row r="48" spans="1:17" ht="15.75" hidden="1">
       <c r="A48" s="30">
         <v>100</v>
       </c>
@@ -10627,7 +10628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75">
+    <row r="49" spans="1:17" ht="15.75" hidden="1">
       <c r="A49" s="30">
         <v>100</v>
       </c>
@@ -10670,7 +10671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75">
+    <row r="50" spans="1:17" ht="15.75" hidden="1">
       <c r="A50" s="30">
         <v>100</v>
       </c>
@@ -10713,7 +10714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" customFormat="1" ht="15.75">
+    <row r="51" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A51" s="2">
         <v>100</v>
       </c>
@@ -10760,7 +10761,7 @@
       <c r="P51" s="38"/>
       <c r="Q51" s="27"/>
     </row>
-    <row r="52" spans="1:17" customFormat="1" ht="15.75">
+    <row r="52" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A52" s="2">
         <v>100</v>
       </c>
@@ -10801,7 +10802,7 @@
       <c r="P52" s="38"/>
       <c r="Q52" s="27"/>
     </row>
-    <row r="53" spans="1:17" customFormat="1" ht="15.75">
+    <row r="53" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A53" s="2">
         <v>100</v>
       </c>
@@ -10848,7 +10849,7 @@
       <c r="P53" s="38"/>
       <c r="Q53" s="27"/>
     </row>
-    <row r="54" spans="1:17" customFormat="1" ht="15.75">
+    <row r="54" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A54" s="2">
         <v>100</v>
       </c>
@@ -10889,7 +10890,7 @@
       <c r="P54" s="38"/>
       <c r="Q54" s="27"/>
     </row>
-    <row r="55" spans="1:17" customFormat="1" ht="15.75">
+    <row r="55" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A55" s="2">
         <v>100</v>
       </c>
@@ -10926,7 +10927,7 @@
       <c r="P55" s="38"/>
       <c r="Q55" s="27"/>
     </row>
-    <row r="56" spans="1:17" ht="15.75">
+    <row r="56" spans="1:17" ht="15.75" hidden="1">
       <c r="A56" s="30">
         <v>100</v>
       </c>
@@ -10969,7 +10970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" customFormat="1" ht="15.75">
+    <row r="57" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A57" s="2">
         <v>100</v>
       </c>
@@ -11016,7 +11017,7 @@
       <c r="P57" s="38"/>
       <c r="Q57" s="27"/>
     </row>
-    <row r="58" spans="1:17" customFormat="1" ht="15.75">
+    <row r="58" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A58" s="2">
         <v>100</v>
       </c>
@@ -11063,7 +11064,7 @@
       <c r="P58" s="38"/>
       <c r="Q58" s="27"/>
     </row>
-    <row r="59" spans="1:17" customFormat="1" ht="15.75">
+    <row r="59" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A59" s="2">
         <v>100</v>
       </c>
@@ -11110,7 +11111,7 @@
       <c r="P59" s="38"/>
       <c r="Q59" s="27"/>
     </row>
-    <row r="60" spans="1:17" customFormat="1" ht="15.75">
+    <row r="60" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A60" s="2">
         <v>100</v>
       </c>
@@ -11157,7 +11158,7 @@
       <c r="P60" s="38"/>
       <c r="Q60" s="27"/>
     </row>
-    <row r="61" spans="1:17" customFormat="1" ht="15.75">
+    <row r="61" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A61" s="2">
         <v>100</v>
       </c>
@@ -11204,7 +11205,7 @@
       <c r="P61" s="38"/>
       <c r="Q61" s="27"/>
     </row>
-    <row r="62" spans="1:17" customFormat="1" ht="15.75">
+    <row r="62" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A62" s="2">
         <v>100</v>
       </c>
@@ -11251,7 +11252,7 @@
       <c r="P62" s="38"/>
       <c r="Q62" s="27"/>
     </row>
-    <row r="63" spans="1:17" customFormat="1" ht="15.75">
+    <row r="63" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A63" s="2">
         <v>100</v>
       </c>
@@ -11298,7 +11299,7 @@
       <c r="P63" s="38"/>
       <c r="Q63" s="27"/>
     </row>
-    <row r="64" spans="1:17" customFormat="1" ht="15.75">
+    <row r="64" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A64" s="2">
         <v>100</v>
       </c>
@@ -11345,7 +11346,7 @@
       <c r="P64" s="38"/>
       <c r="Q64" s="27"/>
     </row>
-    <row r="65" spans="1:17" customFormat="1" ht="15.75">
+    <row r="65" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A65" s="2">
         <v>100</v>
       </c>
@@ -11392,7 +11393,7 @@
       <c r="P65" s="38"/>
       <c r="Q65" s="27"/>
     </row>
-    <row r="66" spans="1:17" customFormat="1" ht="15.75">
+    <row r="66" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A66" s="2">
         <v>100</v>
       </c>
@@ -11439,7 +11440,7 @@
       <c r="P66" s="38"/>
       <c r="Q66" s="27"/>
     </row>
-    <row r="67" spans="1:17" customFormat="1" ht="15.75">
+    <row r="67" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A67" s="2">
         <v>100</v>
       </c>
@@ -11486,7 +11487,7 @@
       <c r="P67" s="38"/>
       <c r="Q67" s="27"/>
     </row>
-    <row r="68" spans="1:17" customFormat="1" ht="15.75">
+    <row r="68" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A68" s="2">
         <v>100</v>
       </c>
@@ -11533,7 +11534,7 @@
       <c r="P68" s="38"/>
       <c r="Q68" s="27"/>
     </row>
-    <row r="69" spans="1:17" customFormat="1" ht="15.75">
+    <row r="69" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A69" s="2">
         <v>100</v>
       </c>
@@ -11570,7 +11571,7 @@
       <c r="P69" s="38"/>
       <c r="Q69" s="27"/>
     </row>
-    <row r="70" spans="1:17" customFormat="1" ht="15.75">
+    <row r="70" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A70" s="2">
         <v>100</v>
       </c>
@@ -11609,7 +11610,7 @@
       <c r="P70" s="38"/>
       <c r="Q70" s="27"/>
     </row>
-    <row r="71" spans="1:17" customFormat="1" ht="15.75">
+    <row r="71" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A71" s="2">
         <v>100</v>
       </c>
@@ -11648,7 +11649,7 @@
       <c r="P71" s="38"/>
       <c r="Q71" s="27"/>
     </row>
-    <row r="72" spans="1:17" customFormat="1" ht="15.75">
+    <row r="72" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A72" s="2">
         <v>100</v>
       </c>
@@ -11689,7 +11690,7 @@
       <c r="P72" s="38"/>
       <c r="Q72" s="27"/>
     </row>
-    <row r="73" spans="1:17" customFormat="1" ht="15.75">
+    <row r="73" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A73" s="2">
         <v>100</v>
       </c>
@@ -11730,7 +11731,7 @@
       <c r="P73" s="38"/>
       <c r="Q73" s="27"/>
     </row>
-    <row r="74" spans="1:17" customFormat="1" ht="15.75">
+    <row r="74" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A74" s="2">
         <v>100</v>
       </c>
@@ -11777,7 +11778,7 @@
       <c r="P74" s="38"/>
       <c r="Q74" s="27"/>
     </row>
-    <row r="75" spans="1:17" customFormat="1" ht="15.75">
+    <row r="75" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A75" s="2">
         <v>200</v>
       </c>
@@ -11814,7 +11815,7 @@
       <c r="P75" s="38"/>
       <c r="Q75" s="27"/>
     </row>
-    <row r="76" spans="1:17" customFormat="1" ht="15.75">
+    <row r="76" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A76" s="2">
         <v>200</v>
       </c>
@@ -11851,7 +11852,7 @@
       <c r="P76" s="38"/>
       <c r="Q76" s="27"/>
     </row>
-    <row r="77" spans="1:17" customFormat="1" ht="15.75">
+    <row r="77" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A77" s="2">
         <v>200</v>
       </c>
@@ -11892,7 +11893,7 @@
       <c r="P77" s="38"/>
       <c r="Q77" s="27"/>
     </row>
-    <row r="78" spans="1:17" customFormat="1" ht="15.75">
+    <row r="78" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A78" s="2">
         <v>200</v>
       </c>
@@ -11929,7 +11930,7 @@
       <c r="P78" s="38"/>
       <c r="Q78" s="27"/>
     </row>
-    <row r="79" spans="1:17" customFormat="1" ht="15.75">
+    <row r="79" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A79" s="2">
         <v>200</v>
       </c>
@@ -11966,7 +11967,7 @@
       <c r="P79" s="38"/>
       <c r="Q79" s="27"/>
     </row>
-    <row r="80" spans="1:17" customFormat="1" ht="15.75">
+    <row r="80" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A80" s="2">
         <v>200</v>
       </c>
@@ -12044,7 +12045,7 @@
       <c r="P81" s="38"/>
       <c r="Q81" s="27"/>
     </row>
-    <row r="82" spans="1:17" customFormat="1" ht="15.75">
+    <row r="82" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A82" s="2">
         <v>200</v>
       </c>
@@ -12286,7 +12287,7 @@
       <c r="P87" s="38"/>
       <c r="Q87" s="27"/>
     </row>
-    <row r="88" spans="1:17" customFormat="1" ht="15.75">
+    <row r="88" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A88" s="2">
         <v>200</v>
       </c>
@@ -12323,7 +12324,7 @@
       <c r="P88" s="38"/>
       <c r="Q88" s="27"/>
     </row>
-    <row r="89" spans="1:17" customFormat="1" ht="15.75">
+    <row r="89" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A89" s="2">
         <v>200</v>
       </c>
@@ -12360,7 +12361,7 @@
       <c r="P89" s="38"/>
       <c r="Q89" s="27"/>
     </row>
-    <row r="90" spans="1:17" customFormat="1" ht="15.75">
+    <row r="90" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A90" s="2">
         <v>200</v>
       </c>
@@ -12397,7 +12398,7 @@
       <c r="P90" s="38"/>
       <c r="Q90" s="27"/>
     </row>
-    <row r="91" spans="1:17" customFormat="1" ht="15.75">
+    <row r="91" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A91" s="2">
         <v>200</v>
       </c>
@@ -12434,7 +12435,7 @@
       <c r="P91" s="38"/>
       <c r="Q91" s="27"/>
     </row>
-    <row r="92" spans="1:17" customFormat="1" ht="15.75">
+    <row r="92" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A92" s="2">
         <v>200</v>
       </c>
@@ -12475,7 +12476,7 @@
       <c r="P92" s="38"/>
       <c r="Q92" s="27"/>
     </row>
-    <row r="93" spans="1:17" customFormat="1" ht="15.75">
+    <row r="93" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A93" s="2">
         <v>300</v>
       </c>
@@ -12514,7 +12515,7 @@
       <c r="P93" s="38"/>
       <c r="Q93" s="27"/>
     </row>
-    <row r="94" spans="1:17" customFormat="1" ht="15.75">
+    <row r="94" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A94" s="2">
         <v>300</v>
       </c>
@@ -12553,7 +12554,7 @@
       <c r="P94" s="38"/>
       <c r="Q94" s="27"/>
     </row>
-    <row r="95" spans="1:17" customFormat="1" ht="15.75">
+    <row r="95" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A95" s="2">
         <v>300</v>
       </c>
@@ -12592,7 +12593,7 @@
       <c r="P95" s="38"/>
       <c r="Q95" s="27"/>
     </row>
-    <row r="96" spans="1:17" customFormat="1" ht="15.75">
+    <row r="96" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A96" s="2">
         <v>300</v>
       </c>
@@ -12631,7 +12632,7 @@
       <c r="P96" s="38"/>
       <c r="Q96" s="27"/>
     </row>
-    <row r="97" spans="1:17" customFormat="1" ht="15.75">
+    <row r="97" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A97" s="2">
         <v>300</v>
       </c>
@@ -12668,7 +12669,7 @@
       <c r="P97" s="38"/>
       <c r="Q97" s="27"/>
     </row>
-    <row r="98" spans="1:17" customFormat="1" ht="15.75">
+    <row r="98" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A98" s="2">
         <v>300</v>
       </c>
@@ -12705,7 +12706,7 @@
       <c r="P98" s="38"/>
       <c r="Q98" s="27"/>
     </row>
-    <row r="99" spans="1:17" customFormat="1" ht="15.75">
+    <row r="99" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A99" s="2">
         <v>300</v>
       </c>
@@ -12744,7 +12745,7 @@
       <c r="P99" s="38"/>
       <c r="Q99" s="27"/>
     </row>
-    <row r="100" spans="1:17" customFormat="1" ht="15.75">
+    <row r="100" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A100" s="2">
         <v>300</v>
       </c>
@@ -12824,7 +12825,7 @@
       <c r="P101" s="38"/>
       <c r="Q101" s="27"/>
     </row>
-    <row r="102" spans="1:17" customFormat="1" ht="15.75">
+    <row r="102" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A102" s="2">
         <v>300</v>
       </c>
@@ -12863,7 +12864,7 @@
       <c r="P102" s="38"/>
       <c r="Q102" s="27"/>
     </row>
-    <row r="103" spans="1:17" customFormat="1" ht="15.75">
+    <row r="103" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A103" s="2">
         <v>300</v>
       </c>
@@ -12902,7 +12903,7 @@
       <c r="P103" s="38"/>
       <c r="Q103" s="27"/>
     </row>
-    <row r="104" spans="1:17" customFormat="1" ht="15.75">
+    <row r="104" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A104" s="2">
         <v>300</v>
       </c>
@@ -12941,7 +12942,7 @@
       <c r="P104" s="38"/>
       <c r="Q104" s="27"/>
     </row>
-    <row r="105" spans="1:17" customFormat="1" ht="15.75">
+    <row r="105" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A105" s="2">
         <v>300</v>
       </c>
@@ -12980,7 +12981,7 @@
       <c r="P105" s="38"/>
       <c r="Q105" s="27"/>
     </row>
-    <row r="106" spans="1:17" customFormat="1" ht="15.75">
+    <row r="106" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A106" s="2">
         <v>300</v>
       </c>
@@ -13017,7 +13018,7 @@
       <c r="P106" s="38"/>
       <c r="Q106" s="27"/>
     </row>
-    <row r="107" spans="1:17" customFormat="1" ht="15.75">
+    <row r="107" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A107" s="2">
         <v>300</v>
       </c>
@@ -13054,7 +13055,7 @@
       <c r="P107" s="38"/>
       <c r="Q107" s="27"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75">
+    <row r="108" spans="1:17" ht="15.75" hidden="1">
       <c r="A108" s="30">
         <v>500</v>
       </c>
@@ -13097,7 +13098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75">
+    <row r="109" spans="1:17" ht="15.75" hidden="1">
       <c r="A109" s="30">
         <v>500</v>
       </c>
@@ -13140,7 +13141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" customFormat="1" ht="15.75">
+    <row r="110" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A110" s="2">
         <v>500</v>
       </c>
@@ -13181,7 +13182,7 @@
       <c r="P110" s="38"/>
       <c r="Q110" s="27"/>
     </row>
-    <row r="111" spans="1:17" customFormat="1" ht="15.75">
+    <row r="111" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A111" s="2">
         <v>500</v>
       </c>
@@ -13222,7 +13223,7 @@
       <c r="P111" s="38"/>
       <c r="Q111" s="27"/>
     </row>
-    <row r="112" spans="1:17" customFormat="1" ht="15.75">
+    <row r="112" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A112" s="2">
         <v>500</v>
       </c>
@@ -13269,7 +13270,7 @@
       <c r="P112" s="38"/>
       <c r="Q112" s="27"/>
     </row>
-    <row r="113" spans="1:17" customFormat="1" ht="15.75">
+    <row r="113" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A113" s="2">
         <v>500</v>
       </c>
@@ -13316,7 +13317,7 @@
       <c r="P113" s="38"/>
       <c r="Q113" s="27"/>
     </row>
-    <row r="114" spans="1:17" customFormat="1" ht="15.75">
+    <row r="114" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A114" s="2">
         <v>500</v>
       </c>
@@ -13363,7 +13364,7 @@
       <c r="P114" s="38"/>
       <c r="Q114" s="27"/>
     </row>
-    <row r="115" spans="1:17" customFormat="1" ht="15.75">
+    <row r="115" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A115" s="2">
         <v>500</v>
       </c>
@@ -13410,7 +13411,7 @@
       <c r="P115" s="38"/>
       <c r="Q115" s="27"/>
     </row>
-    <row r="116" spans="1:17" customFormat="1" ht="15.75">
+    <row r="116" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A116" s="2">
         <v>500</v>
       </c>
@@ -13447,7 +13448,7 @@
       <c r="P116" s="38"/>
       <c r="Q116" s="27"/>
     </row>
-    <row r="117" spans="1:17" customFormat="1" ht="15.75">
+    <row r="117" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A117" s="2">
         <v>500</v>
       </c>
@@ -13484,7 +13485,7 @@
       <c r="P117" s="38"/>
       <c r="Q117" s="27"/>
     </row>
-    <row r="118" spans="1:17" customFormat="1" ht="15.75">
+    <row r="118" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A118" s="2">
         <v>500</v>
       </c>
@@ -13521,7 +13522,7 @@
       <c r="P118" s="38"/>
       <c r="Q118" s="27"/>
     </row>
-    <row r="119" spans="1:17" customFormat="1" ht="15.75">
+    <row r="119" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A119" s="2">
         <v>500</v>
       </c>
@@ -13558,7 +13559,7 @@
       <c r="P119" s="38"/>
       <c r="Q119" s="27"/>
     </row>
-    <row r="120" spans="1:17" customFormat="1" ht="15.75">
+    <row r="120" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A120" s="2">
         <v>500</v>
       </c>
@@ -13595,7 +13596,7 @@
       <c r="P120" s="38"/>
       <c r="Q120" s="27"/>
     </row>
-    <row r="121" spans="1:17" customFormat="1" ht="15.75">
+    <row r="121" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A121" s="2">
         <v>500</v>
       </c>
@@ -13632,7 +13633,7 @@
       <c r="P121" s="38"/>
       <c r="Q121" s="27"/>
     </row>
-    <row r="122" spans="1:17" customFormat="1" ht="15.75">
+    <row r="122" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A122" s="2">
         <v>500</v>
       </c>
@@ -13669,7 +13670,7 @@
       <c r="P122" s="38"/>
       <c r="Q122" s="27"/>
     </row>
-    <row r="123" spans="1:17" customFormat="1" ht="15.75">
+    <row r="123" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A123" s="2">
         <v>500</v>
       </c>
@@ -13706,7 +13707,7 @@
       <c r="P123" s="38"/>
       <c r="Q123" s="27"/>
     </row>
-    <row r="124" spans="1:17" customFormat="1" ht="15.75">
+    <row r="124" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A124" s="2">
         <v>500</v>
       </c>
@@ -13753,7 +13754,7 @@
       <c r="P124" s="38"/>
       <c r="Q124" s="27"/>
     </row>
-    <row r="125" spans="1:17" customFormat="1" ht="15.75">
+    <row r="125" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A125" s="2">
         <v>500</v>
       </c>
@@ -13800,7 +13801,7 @@
       <c r="P125" s="38"/>
       <c r="Q125" s="27"/>
     </row>
-    <row r="126" spans="1:17" customFormat="1" ht="15.75">
+    <row r="126" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A126" s="2">
         <v>500</v>
       </c>
@@ -13847,7 +13848,7 @@
       <c r="P126" s="38"/>
       <c r="Q126" s="27"/>
     </row>
-    <row r="127" spans="1:17" customFormat="1" ht="15.75">
+    <row r="127" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A127" s="2">
         <v>500</v>
       </c>
@@ -13894,7 +13895,7 @@
       <c r="P127" s="38"/>
       <c r="Q127" s="27"/>
     </row>
-    <row r="128" spans="1:17" customFormat="1" ht="15.75">
+    <row r="128" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A128" s="2">
         <v>500</v>
       </c>
@@ -13941,7 +13942,7 @@
       <c r="P128" s="38"/>
       <c r="Q128" s="27"/>
     </row>
-    <row r="129" spans="1:17" customFormat="1" ht="15.75">
+    <row r="129" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A129" s="2">
         <v>500</v>
       </c>
@@ -13988,7 +13989,7 @@
       <c r="P129" s="38"/>
       <c r="Q129" s="27"/>
     </row>
-    <row r="130" spans="1:17" ht="15.75">
+    <row r="130" spans="1:17" ht="15.75" hidden="1">
       <c r="A130" s="30">
         <v>500</v>
       </c>
@@ -14025,7 +14026,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="131" spans="1:17" ht="15.75">
+    <row r="131" spans="1:17" ht="15.75" hidden="1">
       <c r="A131" s="30">
         <v>500</v>
       </c>
@@ -14062,7 +14063,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="132" spans="1:17" customFormat="1" ht="15.75">
+    <row r="132" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A132" s="2">
         <v>500</v>
       </c>
@@ -14099,7 +14100,7 @@
       <c r="P132" s="38"/>
       <c r="Q132" s="27"/>
     </row>
-    <row r="133" spans="1:17" customFormat="1" ht="15.75">
+    <row r="133" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A133" s="2">
         <v>500</v>
       </c>
@@ -14136,7 +14137,7 @@
       <c r="P133" s="38"/>
       <c r="Q133" s="27"/>
     </row>
-    <row r="134" spans="1:17" ht="15.75">
+    <row r="134" spans="1:17" ht="15.75" hidden="1">
       <c r="A134" s="30">
         <v>500</v>
       </c>
@@ -14179,7 +14180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="15.75">
+    <row r="135" spans="1:17" ht="15.75" hidden="1">
       <c r="A135" s="30">
         <v>500</v>
       </c>
@@ -14222,7 +14223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" ht="15.75">
+    <row r="136" spans="1:17" ht="15.75" hidden="1">
       <c r="A136" s="30">
         <v>500</v>
       </c>
@@ -14265,7 +14266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" ht="15.75">
+    <row r="137" spans="1:17" ht="15.75" hidden="1">
       <c r="A137" s="30">
         <v>500</v>
       </c>
@@ -14308,7 +14309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" ht="15.75">
+    <row r="138" spans="1:17" ht="15.75" hidden="1">
       <c r="A138" s="30">
         <v>500</v>
       </c>
@@ -14351,7 +14352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" customFormat="1" ht="15.75">
+    <row r="139" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A139" s="2">
         <v>500</v>
       </c>
@@ -14435,7 +14436,7 @@
       <c r="P140" s="38"/>
       <c r="Q140" s="27"/>
     </row>
-    <row r="141" spans="1:17" ht="15.75">
+    <row r="141" spans="1:17" ht="15.75" hidden="1">
       <c r="A141" s="30">
         <v>500</v>
       </c>
@@ -14478,7 +14479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" ht="15.75">
+    <row r="142" spans="1:17" ht="15.75" hidden="1">
       <c r="A142" s="30">
         <v>500</v>
       </c>
@@ -14521,7 +14522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" customFormat="1" ht="15.75">
+    <row r="143" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A143" s="2">
         <v>500</v>
       </c>
@@ -14558,7 +14559,7 @@
       <c r="P143" s="38"/>
       <c r="Q143" s="27"/>
     </row>
-    <row r="144" spans="1:17" customFormat="1" ht="15.75">
+    <row r="144" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A144" s="2">
         <v>500</v>
       </c>
@@ -14597,7 +14598,7 @@
       <c r="P144" s="38"/>
       <c r="Q144" s="27"/>
     </row>
-    <row r="145" spans="1:17" customFormat="1" ht="15.75">
+    <row r="145" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A145" s="2">
         <v>500</v>
       </c>
@@ -14636,7 +14637,7 @@
       <c r="P145" s="38"/>
       <c r="Q145" s="27"/>
     </row>
-    <row r="146" spans="1:17" customFormat="1" ht="15.75">
+    <row r="146" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A146" s="2">
         <v>500</v>
       </c>
@@ -14675,7 +14676,7 @@
       <c r="P146" s="38"/>
       <c r="Q146" s="27"/>
     </row>
-    <row r="147" spans="1:17" customFormat="1" ht="15.75">
+    <row r="147" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A147" s="2">
         <v>500</v>
       </c>
@@ -14714,7 +14715,7 @@
       <c r="P147" s="38"/>
       <c r="Q147" s="27"/>
     </row>
-    <row r="148" spans="1:17" customFormat="1" ht="15.75">
+    <row r="148" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A148" s="2">
         <v>500</v>
       </c>
@@ -14753,7 +14754,7 @@
       <c r="P148" s="38"/>
       <c r="Q148" s="27"/>
     </row>
-    <row r="149" spans="1:17" customFormat="1" ht="15.75">
+    <row r="149" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A149" s="2">
         <v>500</v>
       </c>
@@ -14829,7 +14830,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="151" spans="1:17" customFormat="1" ht="15.75">
+    <row r="151" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A151" s="2">
         <v>600</v>
       </c>
@@ -14876,7 +14877,7 @@
       <c r="P151" s="38"/>
       <c r="Q151" s="27"/>
     </row>
-    <row r="152" spans="1:17" customFormat="1" ht="15.75">
+    <row r="152" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A152" s="2">
         <v>600</v>
       </c>
@@ -14923,7 +14924,7 @@
       <c r="P152" s="38"/>
       <c r="Q152" s="27"/>
     </row>
-    <row r="153" spans="1:17" customFormat="1" ht="15.75">
+    <row r="153" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A153" s="2">
         <v>600</v>
       </c>
@@ -14970,7 +14971,7 @@
       <c r="P153" s="38"/>
       <c r="Q153" s="27"/>
     </row>
-    <row r="154" spans="1:17" customFormat="1" ht="15.75">
+    <row r="154" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A154" s="2">
         <v>600</v>
       </c>
@@ -15017,7 +15018,7 @@
       <c r="P154" s="38"/>
       <c r="Q154" s="27"/>
     </row>
-    <row r="155" spans="1:17" customFormat="1" ht="15.75">
+    <row r="155" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A155" s="2">
         <v>600</v>
       </c>
@@ -15064,7 +15065,7 @@
       <c r="P155" s="38"/>
       <c r="Q155" s="27"/>
     </row>
-    <row r="156" spans="1:17" customFormat="1" ht="15.75">
+    <row r="156" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A156" s="2">
         <v>600</v>
       </c>
@@ -15111,7 +15112,7 @@
       <c r="P156" s="38"/>
       <c r="Q156" s="27"/>
     </row>
-    <row r="157" spans="1:17" customFormat="1" ht="15.75">
+    <row r="157" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A157" s="2">
         <v>600</v>
       </c>
@@ -15158,7 +15159,7 @@
       <c r="P157" s="38"/>
       <c r="Q157" s="27"/>
     </row>
-    <row r="158" spans="1:17" customFormat="1" ht="15.75">
+    <row r="158" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A158" s="2">
         <v>600</v>
       </c>
@@ -15205,7 +15206,7 @@
       <c r="P158" s="38"/>
       <c r="Q158" s="27"/>
     </row>
-    <row r="159" spans="1:17" customFormat="1" ht="15.75">
+    <row r="159" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A159" s="2">
         <v>600</v>
       </c>
@@ -15252,7 +15253,7 @@
       <c r="P159" s="38"/>
       <c r="Q159" s="27"/>
     </row>
-    <row r="160" spans="1:17" customFormat="1" ht="15.75">
+    <row r="160" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A160" s="2">
         <v>600</v>
       </c>
@@ -15299,7 +15300,7 @@
       <c r="P160" s="38"/>
       <c r="Q160" s="27"/>
     </row>
-    <row r="161" spans="1:17" customFormat="1" ht="15.75">
+    <row r="161" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A161" s="2">
         <v>600</v>
       </c>
@@ -15346,7 +15347,7 @@
       <c r="P161" s="38"/>
       <c r="Q161" s="27"/>
     </row>
-    <row r="162" spans="1:17" customFormat="1" ht="15.75">
+    <row r="162" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A162" s="2">
         <v>600</v>
       </c>
@@ -15393,7 +15394,7 @@
       <c r="P162" s="38"/>
       <c r="Q162" s="27"/>
     </row>
-    <row r="163" spans="1:17" customFormat="1" ht="15.75">
+    <row r="163" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A163" s="2">
         <v>600</v>
       </c>
@@ -15440,7 +15441,7 @@
       <c r="P163" s="38"/>
       <c r="Q163" s="27"/>
     </row>
-    <row r="164" spans="1:17" customFormat="1" ht="15.75">
+    <row r="164" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A164" s="2">
         <v>600</v>
       </c>
@@ -15487,7 +15488,7 @@
       <c r="P164" s="38"/>
       <c r="Q164" s="27"/>
     </row>
-    <row r="165" spans="1:17" customFormat="1" ht="15.75">
+    <row r="165" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A165" s="2">
         <v>600</v>
       </c>
@@ -15528,7 +15529,7 @@
       <c r="P165" s="38"/>
       <c r="Q165" s="27"/>
     </row>
-    <row r="166" spans="1:17" customFormat="1" ht="15.75">
+    <row r="166" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A166" s="2">
         <v>600</v>
       </c>
@@ -15569,7 +15570,7 @@
       <c r="P166" s="38"/>
       <c r="Q166" s="27"/>
     </row>
-    <row r="167" spans="1:17" customFormat="1" ht="15.75">
+    <row r="167" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A167" s="2">
         <v>600</v>
       </c>
@@ -15610,7 +15611,7 @@
       <c r="P167" s="38"/>
       <c r="Q167" s="27"/>
     </row>
-    <row r="168" spans="1:17" customFormat="1" ht="15.75">
+    <row r="168" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A168" s="2">
         <v>600</v>
       </c>
@@ -15651,7 +15652,7 @@
       <c r="P168" s="38"/>
       <c r="Q168" s="27"/>
     </row>
-    <row r="169" spans="1:17" customFormat="1" ht="15.75">
+    <row r="169" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A169" s="2">
         <v>600</v>
       </c>
@@ -15692,7 +15693,7 @@
       <c r="P169" s="38"/>
       <c r="Q169" s="27"/>
     </row>
-    <row r="170" spans="1:17" customFormat="1" ht="15.75">
+    <row r="170" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A170" s="2">
         <v>600</v>
       </c>
@@ -15733,7 +15734,7 @@
       <c r="P170" s="38"/>
       <c r="Q170" s="27"/>
     </row>
-    <row r="171" spans="1:17" customFormat="1" ht="15.75">
+    <row r="171" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A171" s="2">
         <v>600</v>
       </c>
@@ -15780,7 +15781,7 @@
       <c r="P171" s="38"/>
       <c r="Q171" s="27"/>
     </row>
-    <row r="172" spans="1:17" customFormat="1" ht="15.75">
+    <row r="172" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A172" s="2">
         <v>600</v>
       </c>
@@ -15827,7 +15828,7 @@
       <c r="P172" s="38"/>
       <c r="Q172" s="27"/>
     </row>
-    <row r="173" spans="1:17" customFormat="1" ht="15.75">
+    <row r="173" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A173" s="2">
         <v>600</v>
       </c>
@@ -15874,7 +15875,7 @@
       <c r="P173" s="38"/>
       <c r="Q173" s="27"/>
     </row>
-    <row r="174" spans="1:17" customFormat="1" ht="15.75">
+    <row r="174" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A174" s="2">
         <v>600</v>
       </c>
@@ -15921,7 +15922,7 @@
       <c r="P174" s="38"/>
       <c r="Q174" s="27"/>
     </row>
-    <row r="175" spans="1:17" customFormat="1" ht="15.75">
+    <row r="175" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A175" s="2">
         <v>600</v>
       </c>
@@ -15968,7 +15969,7 @@
       <c r="P175" s="38"/>
       <c r="Q175" s="27"/>
     </row>
-    <row r="176" spans="1:17" customFormat="1" ht="15.75">
+    <row r="176" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A176" s="2">
         <v>600</v>
       </c>
@@ -16015,7 +16016,7 @@
       <c r="P176" s="38"/>
       <c r="Q176" s="27"/>
     </row>
-    <row r="177" spans="1:17" customFormat="1" ht="15.75">
+    <row r="177" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A177" s="2">
         <v>600</v>
       </c>
@@ -16062,7 +16063,7 @@
       <c r="P177" s="38"/>
       <c r="Q177" s="27"/>
     </row>
-    <row r="178" spans="1:17" customFormat="1" ht="15.75">
+    <row r="178" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A178" s="2">
         <v>600</v>
       </c>
@@ -16109,7 +16110,7 @@
       <c r="P178" s="38"/>
       <c r="Q178" s="27"/>
     </row>
-    <row r="179" spans="1:17" ht="15.75">
+    <row r="179" spans="1:17" ht="15.75" hidden="1">
       <c r="A179" s="30">
         <v>600</v>
       </c>
@@ -16152,7 +16153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:17" ht="15.75">
+    <row r="180" spans="1:17" ht="15.75" hidden="1">
       <c r="A180" s="30">
         <v>600</v>
       </c>
@@ -16195,7 +16196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:17" ht="15.75">
+    <row r="181" spans="1:17" ht="15.75" hidden="1">
       <c r="A181" s="30">
         <v>600</v>
       </c>
@@ -16238,7 +16239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:17" ht="15.75">
+    <row r="182" spans="1:17" ht="15.75" hidden="1">
       <c r="A182" s="30">
         <v>600</v>
       </c>
@@ -16281,7 +16282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:17" ht="15.75">
+    <row r="183" spans="1:17" ht="15.75" hidden="1">
       <c r="A183" s="30">
         <v>600</v>
       </c>
@@ -16324,7 +16325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:17" ht="15.75">
+    <row r="184" spans="1:17" ht="15.75" hidden="1">
       <c r="A184" s="30">
         <v>600</v>
       </c>
@@ -16367,7 +16368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:17" ht="15.75">
+    <row r="185" spans="1:17" ht="15.75" hidden="1">
       <c r="A185" s="30">
         <v>600</v>
       </c>
@@ -16410,7 +16411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:17" ht="15.75">
+    <row r="186" spans="1:17" ht="15.75" hidden="1">
       <c r="A186" s="30">
         <v>600</v>
       </c>
@@ -16453,7 +16454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:17" ht="15.75">
+    <row r="187" spans="1:17" ht="15.75" hidden="1">
       <c r="A187" s="30">
         <v>600</v>
       </c>
@@ -16496,7 +16497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:17" ht="15.75">
+    <row r="188" spans="1:17" ht="15.75" hidden="1">
       <c r="A188" s="30">
         <v>600</v>
       </c>
@@ -16539,7 +16540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:17" ht="15.75">
+    <row r="189" spans="1:17" ht="15.75" hidden="1">
       <c r="A189" s="30">
         <v>600</v>
       </c>
@@ -16582,7 +16583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:17" ht="15.75">
+    <row r="190" spans="1:17" ht="15.75" hidden="1">
       <c r="A190" s="30">
         <v>600</v>
       </c>
@@ -16625,7 +16626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:17" ht="15.75">
+    <row r="191" spans="1:17" ht="15.75" hidden="1">
       <c r="A191" s="30">
         <v>600</v>
       </c>
@@ -16668,7 +16669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:17" ht="15.75">
+    <row r="192" spans="1:17" ht="15.75" hidden="1">
       <c r="A192" s="30">
         <v>600</v>
       </c>
@@ -16711,7 +16712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:17" ht="15.75">
+    <row r="193" spans="1:17" ht="15.75" hidden="1">
       <c r="A193" s="30">
         <v>600</v>
       </c>
@@ -16754,7 +16755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:17" ht="15.75">
+    <row r="194" spans="1:17" ht="15.75" hidden="1">
       <c r="A194" s="30">
         <v>600</v>
       </c>
@@ -16797,7 +16798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:17" ht="15.75">
+    <row r="195" spans="1:17" ht="15.75" hidden="1">
       <c r="A195" s="30">
         <v>600</v>
       </c>
@@ -16840,7 +16841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:17" ht="15.75">
+    <row r="196" spans="1:17" ht="15.75" hidden="1">
       <c r="A196" s="30">
         <v>600</v>
       </c>
@@ -16883,7 +16884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:17" ht="15.75">
+    <row r="197" spans="1:17" ht="15.75" hidden="1">
       <c r="A197" s="30">
         <v>600</v>
       </c>
@@ -16926,7 +16927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:17" customFormat="1" ht="15.75">
+    <row r="198" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A198" s="2">
         <v>600</v>
       </c>
@@ -16973,7 +16974,7 @@
       <c r="P198" s="38"/>
       <c r="Q198" s="27"/>
     </row>
-    <row r="199" spans="1:17" customFormat="1" ht="15.75">
+    <row r="199" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A199" s="2">
         <v>600</v>
       </c>
@@ -17010,7 +17011,7 @@
       <c r="P199" s="38"/>
       <c r="Q199" s="27"/>
     </row>
-    <row r="200" spans="1:17" ht="15.75">
+    <row r="200" spans="1:17" ht="15.75" hidden="1">
       <c r="A200" s="30">
         <v>700</v>
       </c>
@@ -17053,7 +17054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:17" customFormat="1" ht="15.75">
+    <row r="201" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A201" s="2">
         <v>700</v>
       </c>
@@ -17090,7 +17091,7 @@
       <c r="P201" s="38"/>
       <c r="Q201" s="27"/>
     </row>
-    <row r="202" spans="1:17" ht="15.75">
+    <row r="202" spans="1:17" ht="15.75" hidden="1">
       <c r="A202" s="30">
         <v>700</v>
       </c>
@@ -17133,7 +17134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:17" ht="15.75">
+    <row r="203" spans="1:17" ht="15.75" hidden="1">
       <c r="A203" s="30">
         <v>700</v>
       </c>
@@ -17505,7 +17506,7 @@
       <c r="P210" s="38"/>
       <c r="Q210" s="27"/>
     </row>
-    <row r="211" spans="1:17" customFormat="1" ht="15.75">
+    <row r="211" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A211" s="2">
         <v>700</v>
       </c>
@@ -17552,7 +17553,7 @@
       <c r="P211" s="38"/>
       <c r="Q211" s="27"/>
     </row>
-    <row r="212" spans="1:17" customFormat="1" ht="15.75">
+    <row r="212" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A212" s="2">
         <v>700</v>
       </c>
@@ -18084,7 +18085,7 @@
       <c r="P223" s="38"/>
       <c r="Q223" s="27"/>
     </row>
-    <row r="224" spans="1:17" customFormat="1" ht="15.75">
+    <row r="224" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A224" s="2">
         <v>700</v>
       </c>
@@ -18125,7 +18126,7 @@
       <c r="P224" s="38"/>
       <c r="Q224" s="27"/>
     </row>
-    <row r="225" spans="1:17" ht="15.75">
+    <row r="225" spans="1:17" ht="15.75" hidden="1">
       <c r="A225" s="30">
         <v>700</v>
       </c>
@@ -18168,7 +18169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:17" ht="15.75">
+    <row r="226" spans="1:17" ht="15.75" hidden="1">
       <c r="A226" s="30">
         <v>700</v>
       </c>
@@ -18211,7 +18212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:17" customFormat="1" ht="15.75">
+    <row r="227" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A227" s="2">
         <v>700</v>
       </c>
@@ -18258,7 +18259,7 @@
       <c r="P227" s="38"/>
       <c r="Q227" s="27"/>
     </row>
-    <row r="228" spans="1:17" ht="15.75">
+    <row r="228" spans="1:17" ht="15.75" hidden="1">
       <c r="A228" s="30">
         <v>700</v>
       </c>
@@ -18344,7 +18345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:17" ht="15.75">
+    <row r="230" spans="1:17" ht="15.75" hidden="1">
       <c r="A230" s="30">
         <v>700</v>
       </c>
@@ -18571,7 +18572,7 @@
       <c r="P234" s="38"/>
       <c r="Q234" s="27"/>
     </row>
-    <row r="235" spans="1:17" ht="15.75">
+    <row r="235" spans="1:17" ht="15.75" hidden="1">
       <c r="A235" s="30">
         <v>700</v>
       </c>
@@ -18614,7 +18615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:17" customFormat="1" ht="15.75">
+    <row r="236" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A236" s="2">
         <v>700</v>
       </c>
@@ -18661,7 +18662,7 @@
       <c r="P236" s="38"/>
       <c r="Q236" s="27"/>
     </row>
-    <row r="237" spans="1:17" ht="15.75">
+    <row r="237" spans="1:17" ht="15.75" hidden="1">
       <c r="A237" s="30">
         <v>700</v>
       </c>
@@ -19240,7 +19241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:17" customFormat="1" ht="15.75">
+    <row r="250" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A250" s="2">
         <v>700</v>
       </c>
@@ -19287,7 +19288,7 @@
       <c r="P250" s="38"/>
       <c r="Q250" s="27"/>
     </row>
-    <row r="251" spans="1:17" customFormat="1" ht="15.75">
+    <row r="251" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A251" s="2">
         <v>700</v>
       </c>
@@ -19334,7 +19335,7 @@
       <c r="P251" s="38"/>
       <c r="Q251" s="27"/>
     </row>
-    <row r="252" spans="1:17" customFormat="1" ht="15.75">
+    <row r="252" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A252" s="2">
         <v>700</v>
       </c>
@@ -19418,7 +19419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:17" customFormat="1" ht="15.75">
+    <row r="254" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A254" s="2">
         <v>700</v>
       </c>
@@ -19465,7 +19466,7 @@
       <c r="P254" s="38"/>
       <c r="Q254" s="27"/>
     </row>
-    <row r="255" spans="1:17" customFormat="1" ht="15.75">
+    <row r="255" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A255" s="2">
         <v>700</v>
       </c>
@@ -19512,7 +19513,7 @@
       <c r="P255" s="38"/>
       <c r="Q255" s="27"/>
     </row>
-    <row r="256" spans="1:17" customFormat="1" ht="15.75">
+    <row r="256" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A256" s="13">
         <v>700</v>
       </c>
@@ -19557,7 +19558,7 @@
       <c r="P256" s="38"/>
       <c r="Q256" s="27"/>
     </row>
-    <row r="257" spans="1:17" customFormat="1" ht="15.75">
+    <row r="257" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A257" s="2">
         <v>700</v>
       </c>
@@ -19604,7 +19605,7 @@
       <c r="P257" s="38"/>
       <c r="Q257" s="27"/>
     </row>
-    <row r="258" spans="1:17" customFormat="1" ht="15.75">
+    <row r="258" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A258" s="2">
         <v>700</v>
       </c>
@@ -19688,7 +19689,7 @@
       <c r="P259" s="38"/>
       <c r="Q259" s="27"/>
     </row>
-    <row r="260" spans="1:17" customFormat="1" ht="15.75">
+    <row r="260" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A260" s="2">
         <v>700</v>
       </c>
@@ -19725,7 +19726,7 @@
       <c r="P260" s="38"/>
       <c r="Q260" s="27"/>
     </row>
-    <row r="261" spans="1:17" customFormat="1" ht="15.75">
+    <row r="261" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A261" s="2">
         <v>700</v>
       </c>
@@ -19772,7 +19773,7 @@
       <c r="P261" s="38"/>
       <c r="Q261" s="27"/>
     </row>
-    <row r="262" spans="1:17" ht="15.75">
+    <row r="262" spans="1:17" ht="15.75" hidden="1">
       <c r="A262" s="30">
         <v>700</v>
       </c>
@@ -19815,7 +19816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:17" customFormat="1" ht="15.75">
+    <row r="263" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A263" s="2">
         <v>700</v>
       </c>
@@ -19860,7 +19861,7 @@
       <c r="P263" s="38"/>
       <c r="Q263" s="27"/>
     </row>
-    <row r="264" spans="1:17" customFormat="1" ht="15.75">
+    <row r="264" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A264" s="2">
         <v>700</v>
       </c>
@@ -19905,7 +19906,7 @@
       <c r="P264" s="38"/>
       <c r="Q264" s="27"/>
     </row>
-    <row r="265" spans="1:17" customFormat="1" ht="15.75">
+    <row r="265" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A265" s="2">
         <v>700</v>
       </c>
@@ -19950,7 +19951,7 @@
       <c r="P265" s="38"/>
       <c r="Q265" s="27"/>
     </row>
-    <row r="266" spans="1:17" customFormat="1" ht="15.75">
+    <row r="266" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A266" s="2">
         <v>700</v>
       </c>
@@ -19995,7 +19996,7 @@
       <c r="P266" s="38"/>
       <c r="Q266" s="27"/>
     </row>
-    <row r="267" spans="1:17" customFormat="1" ht="15.75">
+    <row r="267" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A267" s="2">
         <v>700</v>
       </c>
@@ -20042,7 +20043,7 @@
       <c r="P267" s="38"/>
       <c r="Q267" s="27"/>
     </row>
-    <row r="268" spans="1:17" customFormat="1" ht="15.75">
+    <row r="268" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A268" s="2">
         <v>700</v>
       </c>
@@ -20089,7 +20090,7 @@
       <c r="P268" s="38"/>
       <c r="Q268" s="27"/>
     </row>
-    <row r="269" spans="1:17" ht="15.75">
+    <row r="269" spans="1:17" ht="15.75" hidden="1">
       <c r="A269" s="30">
         <v>700</v>
       </c>
@@ -20132,7 +20133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:17" customFormat="1" ht="15.75">
+    <row r="270" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A270" s="2">
         <v>700</v>
       </c>
@@ -20179,7 +20180,7 @@
       <c r="P270" s="38"/>
       <c r="Q270" s="27"/>
     </row>
-    <row r="271" spans="1:17" customFormat="1" ht="15.75">
+    <row r="271" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A271" s="2">
         <v>700</v>
       </c>
@@ -20226,7 +20227,7 @@
       <c r="P271" s="38"/>
       <c r="Q271" s="27"/>
     </row>
-    <row r="272" spans="1:17" ht="15.75">
+    <row r="272" spans="1:17" ht="15.75" hidden="1">
       <c r="A272" s="30">
         <v>700</v>
       </c>
@@ -20312,7 +20313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:17" customFormat="1" ht="15.75">
+    <row r="274" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A274" s="2">
         <v>800</v>
       </c>
@@ -20353,7 +20354,7 @@
       <c r="P274" s="38"/>
       <c r="Q274" s="27"/>
     </row>
-    <row r="275" spans="1:17" customFormat="1" ht="15.75">
+    <row r="275" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A275" s="2">
         <v>800</v>
       </c>
@@ -20394,7 +20395,7 @@
       <c r="P275" s="38"/>
       <c r="Q275" s="27"/>
     </row>
-    <row r="276" spans="1:17" customFormat="1" ht="15.75">
+    <row r="276" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A276" s="2">
         <v>800</v>
       </c>
@@ -20433,7 +20434,7 @@
       <c r="P276" s="38"/>
       <c r="Q276" s="27"/>
     </row>
-    <row r="277" spans="1:17" customFormat="1" ht="15.75">
+    <row r="277" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A277" s="2">
         <v>800</v>
       </c>
@@ -20470,7 +20471,7 @@
       <c r="P277" s="38"/>
       <c r="Q277" s="27"/>
     </row>
-    <row r="278" spans="1:17" customFormat="1" ht="15.75">
+    <row r="278" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A278" s="2">
         <v>800</v>
       </c>
@@ -20509,7 +20510,7 @@
       <c r="P278" s="38"/>
       <c r="Q278" s="27"/>
     </row>
-    <row r="279" spans="1:17" customFormat="1" ht="15.75">
+    <row r="279" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A279" s="2">
         <v>800</v>
       </c>
@@ -20550,7 +20551,7 @@
       <c r="P279" s="38"/>
       <c r="Q279" s="27"/>
     </row>
-    <row r="280" spans="1:17" customFormat="1" ht="15.75">
+    <row r="280" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A280" s="2">
         <v>800</v>
       </c>
@@ -20587,7 +20588,7 @@
       <c r="P280" s="38"/>
       <c r="Q280" s="27"/>
     </row>
-    <row r="281" spans="1:17" customFormat="1" ht="15.75">
+    <row r="281" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A281" s="2">
         <v>800</v>
       </c>
@@ -20624,7 +20625,7 @@
       <c r="P281" s="38"/>
       <c r="Q281" s="27"/>
     </row>
-    <row r="282" spans="1:17" customFormat="1" ht="15.75">
+    <row r="282" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A282" s="2">
         <v>800</v>
       </c>
@@ -20665,7 +20666,7 @@
       <c r="P282" s="38"/>
       <c r="Q282" s="27"/>
     </row>
-    <row r="283" spans="1:17" customFormat="1" ht="15.75">
+    <row r="283" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A283" s="2">
         <v>800</v>
       </c>
@@ -20706,7 +20707,7 @@
       <c r="P283" s="38"/>
       <c r="Q283" s="27"/>
     </row>
-    <row r="284" spans="1:17" customFormat="1" ht="15.75">
+    <row r="284" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A284" s="2">
         <v>800</v>
       </c>
@@ -20747,7 +20748,7 @@
       <c r="P284" s="38"/>
       <c r="Q284" s="27"/>
     </row>
-    <row r="285" spans="1:17" customFormat="1" ht="15.75">
+    <row r="285" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A285" s="2">
         <v>800</v>
       </c>
@@ -20788,7 +20789,7 @@
       <c r="P285" s="38"/>
       <c r="Q285" s="27"/>
     </row>
-    <row r="286" spans="1:17" customFormat="1" ht="15.75">
+    <row r="286" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A286" s="2">
         <v>800</v>
       </c>
@@ -20829,7 +20830,7 @@
       <c r="P286" s="38"/>
       <c r="Q286" s="27"/>
     </row>
-    <row r="287" spans="1:17" customFormat="1" ht="15.75">
+    <row r="287" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A287" s="2">
         <v>800</v>
       </c>
@@ -20870,7 +20871,7 @@
       <c r="P287" s="38"/>
       <c r="Q287" s="27"/>
     </row>
-    <row r="288" spans="1:17" customFormat="1" ht="15.75">
+    <row r="288" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A288" s="2">
         <v>800</v>
       </c>
@@ -20911,7 +20912,7 @@
       <c r="P288" s="38"/>
       <c r="Q288" s="27"/>
     </row>
-    <row r="289" spans="1:17" customFormat="1" ht="15.75">
+    <row r="289" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A289" s="2">
         <v>800</v>
       </c>
@@ -20948,7 +20949,7 @@
       <c r="P289" s="38"/>
       <c r="Q289" s="27"/>
     </row>
-    <row r="290" spans="1:17" customFormat="1" ht="15.75">
+    <row r="290" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A290" s="2">
         <v>800</v>
       </c>
@@ -20985,7 +20986,7 @@
       <c r="P290" s="38"/>
       <c r="Q290" s="27"/>
     </row>
-    <row r="291" spans="1:17" customFormat="1" ht="15.75">
+    <row r="291" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A291" s="2">
         <v>800</v>
       </c>
@@ -21022,7 +21023,7 @@
       <c r="P291" s="38"/>
       <c r="Q291" s="27"/>
     </row>
-    <row r="292" spans="1:17" customFormat="1" ht="15.75">
+    <row r="292" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A292" s="2">
         <v>800</v>
       </c>
@@ -21061,7 +21062,7 @@
       <c r="P292" s="38"/>
       <c r="Q292" s="27"/>
     </row>
-    <row r="293" spans="1:17" customFormat="1" ht="15.75">
+    <row r="293" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A293" s="2">
         <v>800</v>
       </c>
@@ -21100,7 +21101,7 @@
       <c r="P293" s="38"/>
       <c r="Q293" s="27"/>
     </row>
-    <row r="294" spans="1:17" customFormat="1" ht="15.75">
+    <row r="294" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A294" s="2">
         <v>800</v>
       </c>
@@ -21139,7 +21140,7 @@
       <c r="P294" s="38"/>
       <c r="Q294" s="27"/>
     </row>
-    <row r="295" spans="1:17" customFormat="1" ht="15.75">
+    <row r="295" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A295" s="2">
         <v>800</v>
       </c>
@@ -21178,7 +21179,7 @@
       <c r="P295" s="38"/>
       <c r="Q295" s="27"/>
     </row>
-    <row r="296" spans="1:17" customFormat="1" ht="15.75">
+    <row r="296" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A296" s="2">
         <v>800</v>
       </c>
@@ -21217,7 +21218,7 @@
       <c r="P296" s="38"/>
       <c r="Q296" s="27"/>
     </row>
-    <row r="297" spans="1:17" customFormat="1" ht="15.75">
+    <row r="297" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A297" s="2">
         <v>800</v>
       </c>
@@ -21256,7 +21257,7 @@
       <c r="P297" s="38"/>
       <c r="Q297" s="27"/>
     </row>
-    <row r="298" spans="1:17" customFormat="1" ht="15.75">
+    <row r="298" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A298" s="2">
         <v>800</v>
       </c>
@@ -21295,7 +21296,7 @@
       <c r="P298" s="38"/>
       <c r="Q298" s="27"/>
     </row>
-    <row r="299" spans="1:17" customFormat="1" ht="15.75">
+    <row r="299" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A299" s="2">
         <v>800</v>
       </c>
@@ -21334,7 +21335,7 @@
       <c r="P299" s="38"/>
       <c r="Q299" s="27"/>
     </row>
-    <row r="300" spans="1:17" customFormat="1" ht="15.75">
+    <row r="300" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A300" s="2">
         <v>800</v>
       </c>
@@ -21373,7 +21374,7 @@
       <c r="P300" s="38"/>
       <c r="Q300" s="27"/>
     </row>
-    <row r="301" spans="1:17" customFormat="1" ht="15.75">
+    <row r="301" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A301" s="2">
         <v>800</v>
       </c>
@@ -21410,7 +21411,7 @@
       <c r="P301" s="38"/>
       <c r="Q301" s="27"/>
     </row>
-    <row r="302" spans="1:17" customFormat="1" ht="15.75">
+    <row r="302" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A302" s="2">
         <v>800</v>
       </c>
@@ -21447,7 +21448,7 @@
       <c r="P302" s="38"/>
       <c r="Q302" s="27"/>
     </row>
-    <row r="303" spans="1:17" customFormat="1" ht="15.75">
+    <row r="303" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A303" s="2">
         <v>800</v>
       </c>
@@ -21597,7 +21598,7 @@
       <c r="P306" s="38"/>
       <c r="Q306" s="27"/>
     </row>
-    <row r="307" spans="1:17" customFormat="1" ht="15.75">
+    <row r="307" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A307" s="2">
         <v>800</v>
       </c>
@@ -21634,7 +21635,7 @@
       <c r="P307" s="38"/>
       <c r="Q307" s="27"/>
     </row>
-    <row r="308" spans="1:17" customFormat="1" ht="15.75">
+    <row r="308" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A308" s="2">
         <v>800</v>
       </c>
@@ -21671,7 +21672,7 @@
       <c r="P308" s="38"/>
       <c r="Q308" s="27"/>
     </row>
-    <row r="309" spans="1:17" customFormat="1" ht="15.75">
+    <row r="309" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A309" s="2">
         <v>800</v>
       </c>
@@ -21708,7 +21709,7 @@
       <c r="P309" s="38"/>
       <c r="Q309" s="27"/>
     </row>
-    <row r="310" spans="1:17" customFormat="1" ht="15.75">
+    <row r="310" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A310" s="2">
         <v>800</v>
       </c>
@@ -21745,7 +21746,7 @@
       <c r="P310" s="38"/>
       <c r="Q310" s="27"/>
     </row>
-    <row r="311" spans="1:17" customFormat="1" ht="15.75">
+    <row r="311" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A311" s="2">
         <v>800</v>
       </c>
@@ -21782,7 +21783,7 @@
       <c r="P311" s="38"/>
       <c r="Q311" s="27"/>
     </row>
-    <row r="312" spans="1:17" customFormat="1" ht="15.75">
+    <row r="312" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A312" s="2">
         <v>800</v>
       </c>
@@ -21819,7 +21820,7 @@
       <c r="P312" s="38"/>
       <c r="Q312" s="27"/>
     </row>
-    <row r="313" spans="1:17" customFormat="1" ht="15.75">
+    <row r="313" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A313" s="2">
         <v>800</v>
       </c>
@@ -21856,7 +21857,7 @@
       <c r="P313" s="38"/>
       <c r="Q313" s="27"/>
     </row>
-    <row r="314" spans="1:17" customFormat="1" ht="15.75">
+    <row r="314" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A314" s="2">
         <v>800</v>
       </c>
@@ -21893,7 +21894,7 @@
       <c r="P314" s="38"/>
       <c r="Q314" s="27"/>
     </row>
-    <row r="315" spans="1:17" customFormat="1" ht="15.75">
+    <row r="315" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A315" s="2">
         <v>800</v>
       </c>
@@ -21930,7 +21931,7 @@
       <c r="P315" s="38"/>
       <c r="Q315" s="27"/>
     </row>
-    <row r="316" spans="1:17" customFormat="1" ht="15.75">
+    <row r="316" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A316" s="2">
         <v>800</v>
       </c>
@@ -21967,7 +21968,7 @@
       <c r="P316" s="38"/>
       <c r="Q316" s="27"/>
     </row>
-    <row r="317" spans="1:17" customFormat="1" ht="15.75">
+    <row r="317" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A317" s="2">
         <v>800</v>
       </c>
@@ -22004,7 +22005,7 @@
       <c r="P317" s="38"/>
       <c r="Q317" s="27"/>
     </row>
-    <row r="318" spans="1:17" customFormat="1" ht="15.75">
+    <row r="318" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A318" s="2">
         <v>800</v>
       </c>
@@ -22041,7 +22042,7 @@
       <c r="P318" s="38"/>
       <c r="Q318" s="27"/>
     </row>
-    <row r="319" spans="1:17" customFormat="1" ht="15.75">
+    <row r="319" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A319" s="2">
         <v>800</v>
       </c>
@@ -22078,7 +22079,7 @@
       <c r="P319" s="38"/>
       <c r="Q319" s="27"/>
     </row>
-    <row r="320" spans="1:17" customFormat="1" ht="15.75">
+    <row r="320" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A320" s="2">
         <v>800</v>
       </c>
@@ -22115,7 +22116,7 @@
       <c r="P320" s="38"/>
       <c r="Q320" s="27"/>
     </row>
-    <row r="321" spans="1:17" customFormat="1" ht="15.75">
+    <row r="321" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A321" s="2">
         <v>800</v>
       </c>
@@ -22152,7 +22153,7 @@
       <c r="P321" s="38"/>
       <c r="Q321" s="27"/>
     </row>
-    <row r="322" spans="1:17" customFormat="1" ht="15.75">
+    <row r="322" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A322" s="2">
         <v>800</v>
       </c>
@@ -22189,7 +22190,7 @@
       <c r="P322" s="38"/>
       <c r="Q322" s="27"/>
     </row>
-    <row r="323" spans="1:17" customFormat="1" ht="15.75">
+    <row r="323" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A323" s="2">
         <v>800</v>
       </c>
@@ -22226,7 +22227,7 @@
       <c r="P323" s="38"/>
       <c r="Q323" s="27"/>
     </row>
-    <row r="324" spans="1:17" customFormat="1" ht="15.75">
+    <row r="324" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A324" s="2">
         <v>800</v>
       </c>
@@ -22263,7 +22264,7 @@
       <c r="P324" s="38"/>
       <c r="Q324" s="27"/>
     </row>
-    <row r="325" spans="1:17" customFormat="1" ht="15.75">
+    <row r="325" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A325" s="2">
         <v>800</v>
       </c>
@@ -22300,7 +22301,7 @@
       <c r="P325" s="38"/>
       <c r="Q325" s="27"/>
     </row>
-    <row r="326" spans="1:17" customFormat="1" ht="15.75">
+    <row r="326" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A326" s="2">
         <v>800</v>
       </c>
@@ -22337,7 +22338,7 @@
       <c r="P326" s="38"/>
       <c r="Q326" s="27"/>
     </row>
-    <row r="327" spans="1:17" customFormat="1" ht="15.75">
+    <row r="327" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A327" s="2">
         <v>800</v>
       </c>
@@ -22374,7 +22375,7 @@
       <c r="P327" s="38"/>
       <c r="Q327" s="27"/>
     </row>
-    <row r="328" spans="1:17" customFormat="1" ht="15.75">
+    <row r="328" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A328" s="2">
         <v>800</v>
       </c>
@@ -22411,7 +22412,7 @@
       <c r="P328" s="38"/>
       <c r="Q328" s="27"/>
     </row>
-    <row r="329" spans="1:17" customFormat="1" ht="15.75">
+    <row r="329" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A329" s="2">
         <v>800</v>
       </c>
@@ -22448,7 +22449,7 @@
       <c r="P329" s="38"/>
       <c r="Q329" s="27"/>
     </row>
-    <row r="330" spans="1:17" customFormat="1" ht="15.75">
+    <row r="330" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A330" s="2">
         <v>800</v>
       </c>
@@ -22485,7 +22486,7 @@
       <c r="P330" s="38"/>
       <c r="Q330" s="27"/>
     </row>
-    <row r="331" spans="1:17" customFormat="1" ht="15.75">
+    <row r="331" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A331" s="2">
         <v>800</v>
       </c>
@@ -22522,7 +22523,7 @@
       <c r="P331" s="38"/>
       <c r="Q331" s="27"/>
     </row>
-    <row r="332" spans="1:17" customFormat="1" ht="15.75">
+    <row r="332" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A332" s="2">
         <v>800</v>
       </c>
@@ -22559,7 +22560,7 @@
       <c r="P332" s="38"/>
       <c r="Q332" s="27"/>
     </row>
-    <row r="333" spans="1:17" customFormat="1" ht="15.75">
+    <row r="333" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A333" s="2">
         <v>800</v>
       </c>
@@ -22596,7 +22597,7 @@
       <c r="P333" s="38"/>
       <c r="Q333" s="27"/>
     </row>
-    <row r="334" spans="1:17" customFormat="1" ht="15.75">
+    <row r="334" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A334" s="2">
         <v>800</v>
       </c>
@@ -22633,7 +22634,7 @@
       <c r="P334" s="38"/>
       <c r="Q334" s="27"/>
     </row>
-    <row r="335" spans="1:17" customFormat="1" ht="15.75">
+    <row r="335" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A335" s="2">
         <v>800</v>
       </c>
@@ -22670,7 +22671,7 @@
       <c r="P335" s="38"/>
       <c r="Q335" s="27"/>
     </row>
-    <row r="336" spans="1:17" customFormat="1" ht="15.75">
+    <row r="336" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A336" s="2">
         <v>800</v>
       </c>
@@ -22707,7 +22708,7 @@
       <c r="P336" s="38"/>
       <c r="Q336" s="27"/>
     </row>
-    <row r="337" spans="1:17" customFormat="1" ht="15.75">
+    <row r="337" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A337" s="2">
         <v>800</v>
       </c>
@@ -22744,7 +22745,7 @@
       <c r="P337" s="38"/>
       <c r="Q337" s="27"/>
     </row>
-    <row r="338" spans="1:17" customFormat="1" ht="15.75">
+    <row r="338" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A338" s="2">
         <v>800</v>
       </c>
@@ -22781,7 +22782,7 @@
       <c r="P338" s="38"/>
       <c r="Q338" s="27"/>
     </row>
-    <row r="339" spans="1:17" customFormat="1" ht="15.75">
+    <row r="339" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A339" s="2">
         <v>800</v>
       </c>
@@ -22818,7 +22819,7 @@
       <c r="P339" s="38"/>
       <c r="Q339" s="27"/>
     </row>
-    <row r="340" spans="1:17" customFormat="1" ht="15.75">
+    <row r="340" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A340" s="2">
         <v>800</v>
       </c>
@@ -22855,7 +22856,7 @@
       <c r="P340" s="38"/>
       <c r="Q340" s="27"/>
     </row>
-    <row r="341" spans="1:17" customFormat="1" ht="15.75">
+    <row r="341" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A341" s="2">
         <v>800</v>
       </c>
@@ -22892,7 +22893,7 @@
       <c r="P341" s="38"/>
       <c r="Q341" s="27"/>
     </row>
-    <row r="342" spans="1:17" customFormat="1" ht="15.75">
+    <row r="342" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A342" s="2">
         <v>800</v>
       </c>
@@ -22929,7 +22930,7 @@
       <c r="P342" s="38"/>
       <c r="Q342" s="27"/>
     </row>
-    <row r="343" spans="1:17" customFormat="1" ht="15.75">
+    <row r="343" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A343" s="2">
         <v>800</v>
       </c>
@@ -22966,7 +22967,7 @@
       <c r="P343" s="38"/>
       <c r="Q343" s="27"/>
     </row>
-    <row r="344" spans="1:17" customFormat="1" ht="15.75">
+    <row r="344" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A344" s="2">
         <v>800</v>
       </c>
@@ -23003,7 +23004,7 @@
       <c r="P344" s="38"/>
       <c r="Q344" s="27"/>
     </row>
-    <row r="345" spans="1:17" customFormat="1" ht="15.75">
+    <row r="345" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A345" s="2">
         <v>800</v>
       </c>
@@ -23040,7 +23041,7 @@
       <c r="P345" s="38"/>
       <c r="Q345" s="27"/>
     </row>
-    <row r="346" spans="1:17" customFormat="1" ht="15.75">
+    <row r="346" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A346" s="2">
         <v>800</v>
       </c>
@@ -23077,7 +23078,7 @@
       <c r="P346" s="38"/>
       <c r="Q346" s="27"/>
     </row>
-    <row r="347" spans="1:17" customFormat="1" ht="15.75">
+    <row r="347" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A347" s="2">
         <v>800</v>
       </c>
@@ -23114,7 +23115,7 @@
       <c r="P347" s="38"/>
       <c r="Q347" s="27"/>
     </row>
-    <row r="348" spans="1:17" customFormat="1" ht="15.75">
+    <row r="348" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A348" s="2">
         <v>800</v>
       </c>
@@ -23151,7 +23152,7 @@
       <c r="P348" s="38"/>
       <c r="Q348" s="27"/>
     </row>
-    <row r="349" spans="1:17" customFormat="1" ht="15.75">
+    <row r="349" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A349" s="2">
         <v>800</v>
       </c>
@@ -23188,7 +23189,7 @@
       <c r="P349" s="38"/>
       <c r="Q349" s="27"/>
     </row>
-    <row r="350" spans="1:17" customFormat="1" ht="15.75">
+    <row r="350" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A350" s="2">
         <v>800</v>
       </c>
@@ -23225,7 +23226,7 @@
       <c r="P350" s="38"/>
       <c r="Q350" s="27"/>
     </row>
-    <row r="351" spans="1:17" customFormat="1" ht="15.75">
+    <row r="351" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A351" s="2">
         <v>800</v>
       </c>
@@ -23262,7 +23263,7 @@
       <c r="P351" s="38"/>
       <c r="Q351" s="27"/>
     </row>
-    <row r="352" spans="1:17" customFormat="1" ht="15.75">
+    <row r="352" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A352" s="2">
         <v>800</v>
       </c>
@@ -23299,7 +23300,7 @@
       <c r="P352" s="38"/>
       <c r="Q352" s="27"/>
     </row>
-    <row r="353" spans="1:17" customFormat="1" ht="15.75">
+    <row r="353" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A353" s="2">
         <v>800</v>
       </c>
@@ -23336,7 +23337,7 @@
       <c r="P353" s="38"/>
       <c r="Q353" s="27"/>
     </row>
-    <row r="354" spans="1:17" customFormat="1" ht="15.75">
+    <row r="354" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A354" s="2">
         <v>800</v>
       </c>
@@ -23373,7 +23374,7 @@
       <c r="P354" s="38"/>
       <c r="Q354" s="27"/>
     </row>
-    <row r="355" spans="1:17" customFormat="1" ht="15.75">
+    <row r="355" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A355" s="2">
         <v>800</v>
       </c>
@@ -23410,7 +23411,7 @@
       <c r="P355" s="38"/>
       <c r="Q355" s="27"/>
     </row>
-    <row r="356" spans="1:17" customFormat="1" ht="15.75">
+    <row r="356" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A356" s="2">
         <v>800</v>
       </c>
@@ -23447,7 +23448,7 @@
       <c r="P356" s="38"/>
       <c r="Q356" s="27"/>
     </row>
-    <row r="357" spans="1:17" customFormat="1" ht="15.75">
+    <row r="357" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A357" s="2">
         <v>800</v>
       </c>
@@ -23484,7 +23485,7 @@
       <c r="P357" s="38"/>
       <c r="Q357" s="27"/>
     </row>
-    <row r="358" spans="1:17" customFormat="1" ht="15.75">
+    <row r="358" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A358" s="2">
         <v>800</v>
       </c>
@@ -23521,7 +23522,7 @@
       <c r="P358" s="38"/>
       <c r="Q358" s="27"/>
     </row>
-    <row r="359" spans="1:17" customFormat="1" ht="15.75">
+    <row r="359" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A359" s="2">
         <v>800</v>
       </c>
@@ -23558,7 +23559,7 @@
       <c r="P359" s="38"/>
       <c r="Q359" s="27"/>
     </row>
-    <row r="360" spans="1:17" customFormat="1" ht="15.75">
+    <row r="360" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A360" s="2">
         <v>800</v>
       </c>
@@ -23595,7 +23596,7 @@
       <c r="P360" s="38"/>
       <c r="Q360" s="27"/>
     </row>
-    <row r="361" spans="1:17" customFormat="1" ht="15.75">
+    <row r="361" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A361" s="2">
         <v>800</v>
       </c>
@@ -23632,7 +23633,7 @@
       <c r="P361" s="38"/>
       <c r="Q361" s="27"/>
     </row>
-    <row r="362" spans="1:17" customFormat="1" ht="15.75">
+    <row r="362" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A362" s="2">
         <v>800</v>
       </c>
@@ -23669,7 +23670,7 @@
       <c r="P362" s="38"/>
       <c r="Q362" s="27"/>
     </row>
-    <row r="363" spans="1:17" customFormat="1" ht="15.75">
+    <row r="363" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A363" s="2">
         <v>800</v>
       </c>
@@ -23706,7 +23707,7 @@
       <c r="P363" s="38"/>
       <c r="Q363" s="27"/>
     </row>
-    <row r="364" spans="1:17" customFormat="1" ht="15.75">
+    <row r="364" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A364" s="2">
         <v>800</v>
       </c>
@@ -23743,7 +23744,7 @@
       <c r="P364" s="38"/>
       <c r="Q364" s="27"/>
     </row>
-    <row r="365" spans="1:17" customFormat="1" ht="15.75">
+    <row r="365" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A365" s="2">
         <v>800</v>
       </c>
@@ -23780,7 +23781,7 @@
       <c r="P365" s="38"/>
       <c r="Q365" s="27"/>
     </row>
-    <row r="366" spans="1:17" customFormat="1" ht="15.75">
+    <row r="366" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A366" s="2">
         <v>800</v>
       </c>
@@ -23817,7 +23818,7 @@
       <c r="P366" s="38"/>
       <c r="Q366" s="27"/>
     </row>
-    <row r="367" spans="1:17" customFormat="1" ht="15.75">
+    <row r="367" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A367" s="2">
         <v>800</v>
       </c>
@@ -23854,7 +23855,7 @@
       <c r="P367" s="38"/>
       <c r="Q367" s="27"/>
     </row>
-    <row r="368" spans="1:17" customFormat="1" ht="15.75">
+    <row r="368" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A368" s="2">
         <v>800</v>
       </c>
@@ -23891,7 +23892,7 @@
       <c r="P368" s="38"/>
       <c r="Q368" s="27"/>
     </row>
-    <row r="369" spans="1:17" customFormat="1" ht="15.75">
+    <row r="369" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A369" s="2">
         <v>800</v>
       </c>
@@ -23928,7 +23929,7 @@
       <c r="P369" s="38"/>
       <c r="Q369" s="27"/>
     </row>
-    <row r="370" spans="1:17" customFormat="1" ht="15.75">
+    <row r="370" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A370" s="2">
         <v>800</v>
       </c>
@@ -23965,7 +23966,7 @@
       <c r="P370" s="38"/>
       <c r="Q370" s="27"/>
     </row>
-    <row r="371" spans="1:17" customFormat="1" ht="15.75">
+    <row r="371" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A371" s="2">
         <v>800</v>
       </c>
@@ -24002,7 +24003,7 @@
       <c r="P371" s="38"/>
       <c r="Q371" s="27"/>
     </row>
-    <row r="372" spans="1:17" customFormat="1" ht="15.75">
+    <row r="372" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A372" s="2">
         <v>800</v>
       </c>
@@ -24039,7 +24040,7 @@
       <c r="P372" s="38"/>
       <c r="Q372" s="27"/>
     </row>
-    <row r="373" spans="1:17" customFormat="1" ht="15.75">
+    <row r="373" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A373" s="2">
         <v>800</v>
       </c>
@@ -24076,7 +24077,7 @@
       <c r="P373" s="38"/>
       <c r="Q373" s="27"/>
     </row>
-    <row r="374" spans="1:17" customFormat="1" ht="15.75">
+    <row r="374" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A374" s="2">
         <v>800</v>
       </c>
@@ -24113,7 +24114,7 @@
       <c r="P374" s="38"/>
       <c r="Q374" s="27"/>
     </row>
-    <row r="375" spans="1:17" customFormat="1" ht="15.75">
+    <row r="375" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A375" s="2">
         <v>800</v>
       </c>
@@ -24150,7 +24151,7 @@
       <c r="P375" s="38"/>
       <c r="Q375" s="27"/>
     </row>
-    <row r="376" spans="1:17" customFormat="1" ht="15.75">
+    <row r="376" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A376" s="2">
         <v>800</v>
       </c>
@@ -24187,7 +24188,7 @@
       <c r="P376" s="38"/>
       <c r="Q376" s="27"/>
     </row>
-    <row r="377" spans="1:17" customFormat="1" ht="15.75">
+    <row r="377" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A377" s="2">
         <v>800</v>
       </c>
@@ -24224,7 +24225,7 @@
       <c r="P377" s="38"/>
       <c r="Q377" s="27"/>
     </row>
-    <row r="378" spans="1:17" customFormat="1" ht="15.75">
+    <row r="378" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A378" s="2">
         <v>800</v>
       </c>
@@ -24263,7 +24264,7 @@
       <c r="P378" s="38"/>
       <c r="Q378" s="27"/>
     </row>
-    <row r="379" spans="1:17" customFormat="1" ht="15.75">
+    <row r="379" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A379" s="2">
         <v>800</v>
       </c>
@@ -24300,7 +24301,7 @@
       <c r="P379" s="38"/>
       <c r="Q379" s="27"/>
     </row>
-    <row r="380" spans="1:17" customFormat="1" ht="15.75">
+    <row r="380" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A380" s="2">
         <v>800</v>
       </c>
@@ -24337,7 +24338,7 @@
       <c r="P380" s="38"/>
       <c r="Q380" s="27"/>
     </row>
-    <row r="381" spans="1:17" customFormat="1" ht="15.75">
+    <row r="381" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A381" s="2">
         <v>800</v>
       </c>
@@ -24372,7 +24373,7 @@
       <c r="P381" s="38"/>
       <c r="Q381" s="27"/>
     </row>
-    <row r="382" spans="1:17" customFormat="1" ht="15.75">
+    <row r="382" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A382" s="2">
         <v>800</v>
       </c>
@@ -24409,7 +24410,7 @@
       <c r="P382" s="38"/>
       <c r="Q382" s="27"/>
     </row>
-    <row r="383" spans="1:17" customFormat="1" ht="15.75">
+    <row r="383" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A383" s="2">
         <v>800</v>
       </c>
@@ -24450,7 +24451,7 @@
       <c r="P383" s="38"/>
       <c r="Q383" s="27"/>
     </row>
-    <row r="384" spans="1:17" customFormat="1" ht="15.75">
+    <row r="384" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A384" s="2">
         <v>800</v>
       </c>
@@ -24491,7 +24492,7 @@
       <c r="P384" s="38"/>
       <c r="Q384" s="27"/>
     </row>
-    <row r="385" spans="1:17" customFormat="1" ht="15.75">
+    <row r="385" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A385" s="2">
         <v>800</v>
       </c>
@@ -24532,7 +24533,7 @@
       <c r="P385" s="38"/>
       <c r="Q385" s="27"/>
     </row>
-    <row r="386" spans="1:17" customFormat="1" ht="15.75">
+    <row r="386" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A386" s="2">
         <v>800</v>
       </c>
@@ -24573,7 +24574,7 @@
       <c r="P386" s="38"/>
       <c r="Q386" s="27"/>
     </row>
-    <row r="387" spans="1:17" customFormat="1" ht="15.75">
+    <row r="387" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A387" s="2">
         <v>800</v>
       </c>
@@ -24612,7 +24613,7 @@
       <c r="P387" s="38"/>
       <c r="Q387" s="27"/>
     </row>
-    <row r="388" spans="1:17" customFormat="1" ht="15.75">
+    <row r="388" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A388" s="2">
         <v>800</v>
       </c>
@@ -24649,7 +24650,7 @@
       <c r="P388" s="38"/>
       <c r="Q388" s="27"/>
     </row>
-    <row r="389" spans="1:17" customFormat="1" ht="15.75">
+    <row r="389" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A389" s="2">
         <v>800</v>
       </c>
@@ -24686,7 +24687,7 @@
       <c r="P389" s="38"/>
       <c r="Q389" s="27"/>
     </row>
-    <row r="390" spans="1:17" customFormat="1" ht="15.75">
+    <row r="390" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A390" s="2">
         <v>800</v>
       </c>
@@ -24723,7 +24724,7 @@
       <c r="P390" s="38"/>
       <c r="Q390" s="27"/>
     </row>
-    <row r="391" spans="1:17" customFormat="1" ht="15.75">
+    <row r="391" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A391" s="2">
         <v>800</v>
       </c>
@@ -24760,7 +24761,7 @@
       <c r="P391" s="38"/>
       <c r="Q391" s="27"/>
     </row>
-    <row r="392" spans="1:17" customFormat="1" ht="15.75">
+    <row r="392" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A392" s="2">
         <v>800</v>
       </c>
@@ -24799,7 +24800,7 @@
       <c r="P392" s="38"/>
       <c r="Q392" s="27"/>
     </row>
-    <row r="393" spans="1:17" ht="15.75">
+    <row r="393" spans="1:17" ht="15.75" hidden="1">
       <c r="A393" s="30">
         <v>900</v>
       </c>
@@ -24842,7 +24843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:17" customFormat="1" ht="15.75">
+    <row r="394" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A394" s="2">
         <v>900</v>
       </c>
@@ -24889,7 +24890,7 @@
       <c r="P394" s="38"/>
       <c r="Q394" s="27"/>
     </row>
-    <row r="395" spans="1:17" customFormat="1" ht="15.75">
+    <row r="395" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A395" s="2">
         <v>900</v>
       </c>
@@ -24936,7 +24937,7 @@
       <c r="P395" s="38"/>
       <c r="Q395" s="27"/>
     </row>
-    <row r="396" spans="1:17" customFormat="1" ht="15.75">
+    <row r="396" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A396" s="2">
         <v>900</v>
       </c>
@@ -24977,7 +24978,7 @@
       <c r="P396" s="38"/>
       <c r="Q396" s="27"/>
     </row>
-    <row r="397" spans="1:17" customFormat="1" ht="15.75">
+    <row r="397" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A397" s="2">
         <v>900</v>
       </c>
@@ -25018,7 +25019,7 @@
       <c r="P397" s="38"/>
       <c r="Q397" s="27"/>
     </row>
-    <row r="398" spans="1:17" customFormat="1" ht="15.75">
+    <row r="398" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A398" s="2">
         <v>900</v>
       </c>
@@ -25055,7 +25056,7 @@
       <c r="P398" s="38"/>
       <c r="Q398" s="27"/>
     </row>
-    <row r="399" spans="1:17" customFormat="1" ht="15.75">
+    <row r="399" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A399" s="2">
         <v>900</v>
       </c>
@@ -25096,7 +25097,7 @@
       <c r="P399" s="38"/>
       <c r="Q399" s="27"/>
     </row>
-    <row r="400" spans="1:17" customFormat="1" ht="15.75">
+    <row r="400" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A400" s="2">
         <v>900</v>
       </c>
@@ -25143,7 +25144,7 @@
       <c r="P400" s="38"/>
       <c r="Q400" s="27"/>
     </row>
-    <row r="401" spans="1:17" customFormat="1" ht="15.75">
+    <row r="401" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A401" s="2">
         <v>900</v>
       </c>
@@ -25190,7 +25191,7 @@
       <c r="P401" s="38"/>
       <c r="Q401" s="27"/>
     </row>
-    <row r="402" spans="1:17" customFormat="1" ht="15.75">
+    <row r="402" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A402" s="2">
         <v>900</v>
       </c>
@@ -25237,7 +25238,7 @@
       <c r="P402" s="38"/>
       <c r="Q402" s="27"/>
     </row>
-    <row r="403" spans="1:17" customFormat="1" ht="15.75">
+    <row r="403" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A403" s="2">
         <v>900</v>
       </c>
@@ -25278,7 +25279,7 @@
       <c r="P403" s="38"/>
       <c r="Q403" s="27"/>
     </row>
-    <row r="404" spans="1:17" ht="15.75">
+    <row r="404" spans="1:17" ht="15.75" hidden="1">
       <c r="A404" s="30">
         <v>900</v>
       </c>
@@ -25310,7 +25311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:17" customFormat="1" ht="15.75">
+    <row r="405" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A405" s="2">
         <v>900</v>
       </c>
@@ -25347,7 +25348,7 @@
       <c r="P405" s="38"/>
       <c r="Q405" s="27"/>
     </row>
-    <row r="406" spans="1:17" customFormat="1" ht="15.75">
+    <row r="406" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A406" s="2">
         <v>900</v>
       </c>
@@ -25394,7 +25395,7 @@
       <c r="P406" s="38"/>
       <c r="Q406" s="27"/>
     </row>
-    <row r="407" spans="1:17" customFormat="1" ht="15.75">
+    <row r="407" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A407" s="2">
         <v>900</v>
       </c>
@@ -25435,7 +25436,7 @@
       <c r="P407" s="38"/>
       <c r="Q407" s="27"/>
     </row>
-    <row r="408" spans="1:17" ht="15.75">
+    <row r="408" spans="1:17" ht="15.75" hidden="1">
       <c r="A408" s="30">
         <v>900</v>
       </c>
@@ -25478,7 +25479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:17" customFormat="1" ht="15.75">
+    <row r="409" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A409" s="2">
         <v>900</v>
       </c>
@@ -25519,7 +25520,7 @@
       <c r="P409" s="38"/>
       <c r="Q409" s="27"/>
     </row>
-    <row r="410" spans="1:17" customFormat="1" ht="15.75">
+    <row r="410" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A410" s="2">
         <v>900</v>
       </c>
@@ -25556,7 +25557,7 @@
       <c r="P410" s="38"/>
       <c r="Q410" s="27"/>
     </row>
-    <row r="411" spans="1:17" customFormat="1" ht="15.75">
+    <row r="411" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A411" s="2">
         <v>900</v>
       </c>
@@ -25595,7 +25596,7 @@
       <c r="P411" s="38"/>
       <c r="Q411" s="27"/>
     </row>
-    <row r="412" spans="1:17" customFormat="1" ht="15.75">
+    <row r="412" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A412" s="2">
         <v>900</v>
       </c>
@@ -25636,7 +25637,7 @@
       <c r="P412" s="38"/>
       <c r="Q412" s="27"/>
     </row>
-    <row r="413" spans="1:17" customFormat="1" ht="15.75">
+    <row r="413" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A413" s="2">
         <v>900</v>
       </c>
@@ -25683,7 +25684,7 @@
       <c r="P413" s="38"/>
       <c r="Q413" s="27"/>
     </row>
-    <row r="414" spans="1:17" customFormat="1" ht="15.75">
+    <row r="414" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A414" s="2">
         <v>900</v>
       </c>
@@ -25730,7 +25731,7 @@
       <c r="P414" s="38"/>
       <c r="Q414" s="27"/>
     </row>
-    <row r="415" spans="1:17" customFormat="1" ht="15.75">
+    <row r="415" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A415" s="2">
         <v>900</v>
       </c>
@@ -25771,7 +25772,7 @@
       <c r="P415" s="38"/>
       <c r="Q415" s="27"/>
     </row>
-    <row r="416" spans="1:17" customFormat="1" ht="15.75">
+    <row r="416" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A416" s="2">
         <v>900</v>
       </c>
@@ -25818,7 +25819,7 @@
       <c r="P416" s="38"/>
       <c r="Q416" s="27"/>
     </row>
-    <row r="417" spans="1:17" customFormat="1" ht="15.75">
+    <row r="417" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A417" s="2">
         <v>900</v>
       </c>
@@ -25855,7 +25856,7 @@
       <c r="P417" s="38"/>
       <c r="Q417" s="27"/>
     </row>
-    <row r="418" spans="1:17" ht="15.75">
+    <row r="418" spans="1:17" ht="15.75" hidden="1">
       <c r="A418" s="30">
         <v>900</v>
       </c>
@@ -25890,7 +25891,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="419" spans="1:17" customFormat="1" ht="15.75">
+    <row r="419" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A419" s="2">
         <v>900</v>
       </c>
@@ -25929,7 +25930,7 @@
       <c r="P419" s="38"/>
       <c r="Q419" s="27"/>
     </row>
-    <row r="420" spans="1:17" ht="15.75">
+    <row r="420" spans="1:17" ht="15.75" hidden="1">
       <c r="A420" s="30">
         <v>900</v>
       </c>
@@ -25964,7 +25965,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="421" spans="1:17" customFormat="1" ht="15.75">
+    <row r="421" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A421" s="2">
         <v>900</v>
       </c>
@@ -26005,7 +26006,7 @@
       <c r="P421" s="38"/>
       <c r="Q421" s="27"/>
     </row>
-    <row r="422" spans="1:17" customFormat="1" ht="15.75">
+    <row r="422" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A422" s="2">
         <v>900</v>
       </c>
@@ -26046,7 +26047,7 @@
       <c r="P422" s="38"/>
       <c r="Q422" s="27"/>
     </row>
-    <row r="423" spans="1:17" customFormat="1" ht="15.75">
+    <row r="423" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A423" s="2">
         <v>900</v>
       </c>
@@ -26087,7 +26088,7 @@
       <c r="P423" s="38"/>
       <c r="Q423" s="27"/>
     </row>
-    <row r="424" spans="1:17" customFormat="1" ht="15.75">
+    <row r="424" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A424" s="2">
         <v>900</v>
       </c>
@@ -26128,7 +26129,7 @@
       <c r="P424" s="38"/>
       <c r="Q424" s="27"/>
     </row>
-    <row r="425" spans="1:17" customFormat="1" ht="15.75">
+    <row r="425" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A425" s="2">
         <v>900</v>
       </c>
@@ -26169,7 +26170,7 @@
       <c r="P425" s="38"/>
       <c r="Q425" s="27"/>
     </row>
-    <row r="426" spans="1:17" customFormat="1" ht="15.75">
+    <row r="426" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A426" s="2">
         <v>900</v>
       </c>
@@ -26210,7 +26211,7 @@
       <c r="P426" s="38"/>
       <c r="Q426" s="27"/>
     </row>
-    <row r="427" spans="1:17" customFormat="1" ht="15.75">
+    <row r="427" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A427" s="2">
         <v>900</v>
       </c>
@@ -26251,7 +26252,7 @@
       <c r="P427" s="38"/>
       <c r="Q427" s="27"/>
     </row>
-    <row r="428" spans="1:17" customFormat="1" ht="15.75">
+    <row r="428" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A428" s="2">
         <v>900</v>
       </c>
@@ -26292,7 +26293,7 @@
       <c r="P428" s="38"/>
       <c r="Q428" s="27"/>
     </row>
-    <row r="429" spans="1:17" customFormat="1" ht="15.75">
+    <row r="429" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A429" s="2">
         <v>900</v>
       </c>
@@ -26333,7 +26334,7 @@
       <c r="P429" s="38"/>
       <c r="Q429" s="27"/>
     </row>
-    <row r="430" spans="1:17" customFormat="1" ht="15.75">
+    <row r="430" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A430" s="2">
         <v>900</v>
       </c>
@@ -26374,7 +26375,7 @@
       <c r="P430" s="38"/>
       <c r="Q430" s="27"/>
     </row>
-    <row r="431" spans="1:17" customFormat="1" ht="15.75">
+    <row r="431" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A431" s="2">
         <v>900</v>
       </c>
@@ -26411,7 +26412,7 @@
       <c r="P431" s="38"/>
       <c r="Q431" s="27"/>
     </row>
-    <row r="432" spans="1:17" customFormat="1" ht="15.75">
+    <row r="432" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A432" s="2">
         <v>900</v>
       </c>
@@ -26450,7 +26451,7 @@
       <c r="P432" s="38"/>
       <c r="Q432" s="27"/>
     </row>
-    <row r="433" spans="1:17" customFormat="1" ht="15.75">
+    <row r="433" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A433" s="2">
         <v>900</v>
       </c>
@@ -26489,7 +26490,7 @@
       <c r="P433" s="38"/>
       <c r="Q433" s="27"/>
     </row>
-    <row r="434" spans="1:17" customFormat="1" ht="15.75">
+    <row r="434" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A434" s="2">
         <v>900</v>
       </c>
@@ -26528,7 +26529,7 @@
       <c r="P434" s="38"/>
       <c r="Q434" s="27"/>
     </row>
-    <row r="435" spans="1:17" customFormat="1" ht="15.75">
+    <row r="435" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A435" s="2">
         <v>900</v>
       </c>
@@ -26567,7 +26568,7 @@
       <c r="P435" s="38"/>
       <c r="Q435" s="27"/>
     </row>
-    <row r="436" spans="1:17" customFormat="1" ht="15.75">
+    <row r="436" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A436" s="2">
         <v>900</v>
       </c>
@@ -26606,7 +26607,7 @@
       <c r="P436" s="38"/>
       <c r="Q436" s="27"/>
     </row>
-    <row r="437" spans="1:17" customFormat="1" ht="15.75">
+    <row r="437" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A437" s="2">
         <v>900</v>
       </c>
@@ -26643,7 +26644,7 @@
       <c r="P437" s="38"/>
       <c r="Q437" s="27"/>
     </row>
-    <row r="438" spans="1:17" customFormat="1" ht="15.75">
+    <row r="438" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A438" s="2">
         <v>900</v>
       </c>
@@ -26690,7 +26691,7 @@
       <c r="P438" s="38"/>
       <c r="Q438" s="27"/>
     </row>
-    <row r="439" spans="1:17" customFormat="1" ht="15.75">
+    <row r="439" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A439" s="2">
         <v>900</v>
       </c>
@@ -26737,7 +26738,7 @@
       <c r="P439" s="38"/>
       <c r="Q439" s="27"/>
     </row>
-    <row r="440" spans="1:17" customFormat="1" ht="15.75">
+    <row r="440" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A440" s="2">
         <v>900</v>
       </c>
@@ -26784,7 +26785,7 @@
       <c r="P440" s="38"/>
       <c r="Q440" s="27"/>
     </row>
-    <row r="441" spans="1:17" customFormat="1" ht="15.75">
+    <row r="441" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A441" s="2">
         <v>900</v>
       </c>
@@ -26831,7 +26832,7 @@
       <c r="P441" s="38"/>
       <c r="Q441" s="27"/>
     </row>
-    <row r="442" spans="1:17" customFormat="1" ht="15.75">
+    <row r="442" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A442" s="2">
         <v>900</v>
       </c>
@@ -26878,7 +26879,7 @@
       <c r="P442" s="38"/>
       <c r="Q442" s="27"/>
     </row>
-    <row r="443" spans="1:17" customFormat="1" ht="15.75">
+    <row r="443" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A443" s="2">
         <v>900</v>
       </c>
@@ -26925,7 +26926,7 @@
       <c r="P443" s="38"/>
       <c r="Q443" s="27"/>
     </row>
-    <row r="444" spans="1:17" customFormat="1" ht="15.75">
+    <row r="444" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A444" s="2">
         <v>900</v>
       </c>
@@ -26972,7 +26973,7 @@
       <c r="P444" s="38"/>
       <c r="Q444" s="27"/>
     </row>
-    <row r="445" spans="1:17" customFormat="1" ht="15.75">
+    <row r="445" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A445" s="2">
         <v>900</v>
       </c>
@@ -27019,7 +27020,7 @@
       <c r="P445" s="38"/>
       <c r="Q445" s="27"/>
     </row>
-    <row r="446" spans="1:17" customFormat="1" ht="15.75">
+    <row r="446" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A446" s="2">
         <v>900</v>
       </c>
@@ -27066,7 +27067,7 @@
       <c r="P446" s="38"/>
       <c r="Q446" s="27"/>
     </row>
-    <row r="447" spans="1:17" customFormat="1" ht="15.75">
+    <row r="447" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A447" s="2">
         <v>900</v>
       </c>
@@ -27113,7 +27114,7 @@
       <c r="P447" s="38"/>
       <c r="Q447" s="27"/>
     </row>
-    <row r="448" spans="1:17" customFormat="1" ht="15.75">
+    <row r="448" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A448" s="2">
         <v>900</v>
       </c>
@@ -27160,7 +27161,7 @@
       <c r="P448" s="38"/>
       <c r="Q448" s="27"/>
     </row>
-    <row r="449" spans="1:17" customFormat="1" ht="15.75">
+    <row r="449" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A449" s="2">
         <v>900</v>
       </c>
@@ -27207,7 +27208,7 @@
       <c r="P449" s="38"/>
       <c r="Q449" s="27"/>
     </row>
-    <row r="450" spans="1:17" customFormat="1" ht="15.75">
+    <row r="450" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A450" s="2">
         <v>900</v>
       </c>
@@ -27254,7 +27255,7 @@
       <c r="P450" s="38"/>
       <c r="Q450" s="27"/>
     </row>
-    <row r="451" spans="1:17" customFormat="1" ht="15.75">
+    <row r="451" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A451" s="2">
         <v>900</v>
       </c>
@@ -27301,7 +27302,7 @@
       <c r="P451" s="38"/>
       <c r="Q451" s="27"/>
     </row>
-    <row r="452" spans="1:17" customFormat="1" ht="15.75">
+    <row r="452" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A452" s="2">
         <v>900</v>
       </c>
@@ -27338,7 +27339,7 @@
       <c r="P452" s="38"/>
       <c r="Q452" s="27"/>
     </row>
-    <row r="453" spans="1:17" customFormat="1" ht="15.75">
+    <row r="453" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A453" s="2">
         <v>900</v>
       </c>
@@ -27375,7 +27376,7 @@
       <c r="P453" s="38"/>
       <c r="Q453" s="27"/>
     </row>
-    <row r="454" spans="1:17" customFormat="1" ht="15.75">
+    <row r="454" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A454" s="2">
         <v>900</v>
       </c>
@@ -27412,7 +27413,7 @@
       <c r="P454" s="38"/>
       <c r="Q454" s="27"/>
     </row>
-    <row r="455" spans="1:17" customFormat="1" ht="15.75">
+    <row r="455" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A455" s="2">
         <v>900</v>
       </c>
@@ -27449,7 +27450,7 @@
       <c r="P455" s="38"/>
       <c r="Q455" s="27"/>
     </row>
-    <row r="456" spans="1:17" customFormat="1" ht="15.75">
+    <row r="456" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A456" s="2">
         <v>900</v>
       </c>
@@ -27486,7 +27487,7 @@
       <c r="P456" s="38"/>
       <c r="Q456" s="27"/>
     </row>
-    <row r="457" spans="1:17" customFormat="1" ht="15.75">
+    <row r="457" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A457" s="2">
         <v>900</v>
       </c>
@@ -27523,7 +27524,7 @@
       <c r="P457" s="38"/>
       <c r="Q457" s="27"/>
     </row>
-    <row r="458" spans="1:17" customFormat="1" ht="15.75">
+    <row r="458" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A458" s="2">
         <v>900</v>
       </c>
@@ -27562,7 +27563,7 @@
       <c r="P458" s="38"/>
       <c r="Q458" s="27"/>
     </row>
-    <row r="459" spans="1:17" customFormat="1" ht="15.75">
+    <row r="459" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A459" s="2">
         <v>900</v>
       </c>
@@ -27601,7 +27602,7 @@
       <c r="P459" s="38"/>
       <c r="Q459" s="27"/>
     </row>
-    <row r="460" spans="1:17" customFormat="1" ht="15.75">
+    <row r="460" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A460" s="2">
         <v>900</v>
       </c>
@@ -27640,7 +27641,7 @@
       <c r="P460" s="38"/>
       <c r="Q460" s="27"/>
     </row>
-    <row r="461" spans="1:17" customFormat="1" ht="15.75">
+    <row r="461" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A461" s="2">
         <v>900</v>
       </c>
@@ -27679,7 +27680,7 @@
       <c r="P461" s="38"/>
       <c r="Q461" s="27"/>
     </row>
-    <row r="462" spans="1:17" customFormat="1" ht="15.75">
+    <row r="462" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A462" s="2">
         <v>900</v>
       </c>
@@ -27718,7 +27719,7 @@
       <c r="P462" s="38"/>
       <c r="Q462" s="27"/>
     </row>
-    <row r="463" spans="1:17" customFormat="1" ht="15.75">
+    <row r="463" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A463" s="2">
         <v>900</v>
       </c>
@@ -27757,7 +27758,7 @@
       <c r="P463" s="38"/>
       <c r="Q463" s="27"/>
     </row>
-    <row r="464" spans="1:17" ht="15.75">
+    <row r="464" spans="1:17" ht="15.75" hidden="1">
       <c r="A464" s="30">
         <v>900</v>
       </c>
@@ -27800,7 +27801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:17" ht="15.75">
+    <row r="465" spans="1:17" ht="15.75" hidden="1">
       <c r="A465" s="30">
         <v>900</v>
       </c>
@@ -27843,7 +27844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="466" spans="1:17" customFormat="1" ht="15.75">
+    <row r="466" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A466" s="2">
         <v>900</v>
       </c>
@@ -27880,7 +27881,7 @@
       <c r="P466" s="38"/>
       <c r="Q466" s="27"/>
     </row>
-    <row r="467" spans="1:17" customFormat="1" ht="15.75">
+    <row r="467" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A467" s="2">
         <v>900</v>
       </c>
@@ -27917,7 +27918,7 @@
       <c r="P467" s="38"/>
       <c r="Q467" s="27"/>
     </row>
-    <row r="468" spans="1:17" customFormat="1" ht="15.75">
+    <row r="468" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A468" s="2">
         <v>900</v>
       </c>
@@ -27954,7 +27955,7 @@
       <c r="P468" s="38"/>
       <c r="Q468" s="27"/>
     </row>
-    <row r="469" spans="1:17" customFormat="1" ht="15.75">
+    <row r="469" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A469" s="2">
         <v>900</v>
       </c>
@@ -27991,7 +27992,7 @@
       <c r="P469" s="38"/>
       <c r="Q469" s="27"/>
     </row>
-    <row r="470" spans="1:17" customFormat="1" ht="15.75">
+    <row r="470" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A470" s="2">
         <v>900</v>
       </c>
@@ -28028,7 +28029,7 @@
       <c r="P470" s="38"/>
       <c r="Q470" s="27"/>
     </row>
-    <row r="471" spans="1:17" customFormat="1" ht="15.75">
+    <row r="471" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A471" s="2">
         <v>900</v>
       </c>
@@ -28065,7 +28066,7 @@
       <c r="P471" s="38"/>
       <c r="Q471" s="27"/>
     </row>
-    <row r="472" spans="1:17" customFormat="1" ht="15.75">
+    <row r="472" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A472" s="2">
         <v>900</v>
       </c>
@@ -28102,7 +28103,7 @@
       <c r="P472" s="38"/>
       <c r="Q472" s="27"/>
     </row>
-    <row r="473" spans="1:17" customFormat="1" ht="15.75">
+    <row r="473" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A473" s="2">
         <v>900</v>
       </c>
@@ -28139,7 +28140,7 @@
       <c r="P473" s="38"/>
       <c r="Q473" s="27"/>
     </row>
-    <row r="474" spans="1:17" customFormat="1" ht="15.75">
+    <row r="474" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A474" s="2">
         <v>900</v>
       </c>
@@ -28186,7 +28187,7 @@
       <c r="P474" s="38"/>
       <c r="Q474" s="27"/>
     </row>
-    <row r="475" spans="1:17" customFormat="1" ht="15.75">
+    <row r="475" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A475" s="2">
         <v>900</v>
       </c>
@@ -28225,7 +28226,7 @@
       <c r="P475" s="38"/>
       <c r="Q475" s="27"/>
     </row>
-    <row r="476" spans="1:17" customFormat="1" ht="15.75">
+    <row r="476" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A476" s="2">
         <v>900</v>
       </c>
@@ -28266,7 +28267,7 @@
       <c r="P476" s="38"/>
       <c r="Q476" s="27"/>
     </row>
-    <row r="477" spans="1:17" customFormat="1" ht="15.75">
+    <row r="477" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A477" s="2">
         <v>900</v>
       </c>
@@ -28307,7 +28308,7 @@
       <c r="P477" s="38"/>
       <c r="Q477" s="27"/>
     </row>
-    <row r="478" spans="1:17" customFormat="1" ht="15.75">
+    <row r="478" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A478" s="2">
         <v>900</v>
       </c>
@@ -28346,7 +28347,7 @@
       <c r="P478" s="38"/>
       <c r="Q478" s="27"/>
     </row>
-    <row r="479" spans="1:17" customFormat="1" ht="15.75">
+    <row r="479" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A479" s="2">
         <v>900</v>
       </c>
@@ -28385,7 +28386,7 @@
       <c r="P479" s="38"/>
       <c r="Q479" s="27"/>
     </row>
-    <row r="480" spans="1:17" customFormat="1" ht="15.75">
+    <row r="480" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A480" s="2">
         <v>900</v>
       </c>
@@ -28424,7 +28425,7 @@
       <c r="P480" s="38"/>
       <c r="Q480" s="27"/>
     </row>
-    <row r="481" spans="1:17" customFormat="1" ht="15.75">
+    <row r="481" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A481" s="2">
         <v>900</v>
       </c>
@@ -28461,7 +28462,7 @@
       <c r="P481" s="38"/>
       <c r="Q481" s="27"/>
     </row>
-    <row r="482" spans="1:17" customFormat="1" ht="15.75">
+    <row r="482" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A482" s="2">
         <v>900</v>
       </c>
@@ -28508,7 +28509,7 @@
       <c r="P482" s="38"/>
       <c r="Q482" s="27"/>
     </row>
-    <row r="483" spans="1:17" customFormat="1" ht="15.75">
+    <row r="483" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A483" s="2">
         <v>900</v>
       </c>
@@ -28555,7 +28556,7 @@
       <c r="P483" s="38"/>
       <c r="Q483" s="27"/>
     </row>
-    <row r="484" spans="1:17" customFormat="1" ht="15.75">
+    <row r="484" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A484" s="2">
         <v>900</v>
       </c>
@@ -28602,7 +28603,7 @@
       <c r="P484" s="38"/>
       <c r="Q484" s="27"/>
     </row>
-    <row r="485" spans="1:17" customFormat="1" ht="15.75">
+    <row r="485" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A485" s="2">
         <v>900</v>
       </c>
@@ -28649,7 +28650,7 @@
       <c r="P485" s="38"/>
       <c r="Q485" s="27"/>
     </row>
-    <row r="486" spans="1:17" customFormat="1" ht="15.75">
+    <row r="486" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A486" s="2">
         <v>900</v>
       </c>
@@ -28686,7 +28687,7 @@
       <c r="P486" s="38"/>
       <c r="Q486" s="27"/>
     </row>
-    <row r="487" spans="1:17" ht="15.75">
+    <row r="487" spans="1:17" ht="15.75" hidden="1">
       <c r="A487" s="30">
         <v>900</v>
       </c>
@@ -28721,7 +28722,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="488" spans="1:17" ht="15.75">
+    <row r="488" spans="1:17" ht="15.75" hidden="1">
       <c r="A488" s="30">
         <v>900</v>
       </c>
@@ -28756,7 +28757,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="489" spans="1:17" customFormat="1" ht="15.75">
+    <row r="489" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A489" s="2">
         <v>900</v>
       </c>
@@ -28795,7 +28796,7 @@
       <c r="P489" s="38"/>
       <c r="Q489" s="27"/>
     </row>
-    <row r="490" spans="1:17" customFormat="1" ht="15.75">
+    <row r="490" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A490" s="2">
         <v>900</v>
       </c>
@@ -28834,7 +28835,7 @@
       <c r="P490" s="38"/>
       <c r="Q490" s="27"/>
     </row>
-    <row r="491" spans="1:17" customFormat="1" ht="15.75">
+    <row r="491" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A491" s="2">
         <v>900</v>
       </c>
@@ -28881,7 +28882,7 @@
       <c r="P491" s="38"/>
       <c r="Q491" s="27"/>
     </row>
-    <row r="492" spans="1:17" customFormat="1" ht="15.75">
+    <row r="492" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A492" s="2">
         <v>900</v>
       </c>
@@ -28928,7 +28929,7 @@
       <c r="P492" s="38"/>
       <c r="Q492" s="27"/>
     </row>
-    <row r="493" spans="1:17" customFormat="1" ht="15.75">
+    <row r="493" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A493" s="2">
         <v>900</v>
       </c>
@@ -28969,7 +28970,7 @@
       <c r="P493" s="38"/>
       <c r="Q493" s="27"/>
     </row>
-    <row r="494" spans="1:17" customFormat="1" ht="15.75">
+    <row r="494" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A494" s="2">
         <v>900</v>
       </c>
@@ -29010,7 +29011,7 @@
       <c r="P494" s="38"/>
       <c r="Q494" s="27"/>
     </row>
-    <row r="495" spans="1:17" customFormat="1" ht="15.75">
+    <row r="495" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A495" s="2">
         <v>1000</v>
       </c>
@@ -29047,7 +29048,7 @@
       <c r="P495" s="38"/>
       <c r="Q495" s="27"/>
     </row>
-    <row r="496" spans="1:17" customFormat="1" ht="15.75">
+    <row r="496" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A496" s="2">
         <v>1000</v>
       </c>
@@ -29084,7 +29085,7 @@
       <c r="P496" s="38"/>
       <c r="Q496" s="27"/>
     </row>
-    <row r="497" spans="1:17" customFormat="1" ht="15.75">
+    <row r="497" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A497" s="2">
         <v>1000</v>
       </c>
@@ -29121,7 +29122,7 @@
       <c r="P497" s="38"/>
       <c r="Q497" s="27"/>
     </row>
-    <row r="498" spans="1:17" customFormat="1" ht="15.75">
+    <row r="498" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A498" s="2">
         <v>1000</v>
       </c>
@@ -29158,7 +29159,7 @@
       <c r="P498" s="38"/>
       <c r="Q498" s="27"/>
     </row>
-    <row r="499" spans="1:17" customFormat="1" ht="15.75">
+    <row r="499" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A499" s="2">
         <v>1000</v>
       </c>
@@ -29195,7 +29196,7 @@
       <c r="P499" s="38"/>
       <c r="Q499" s="27"/>
     </row>
-    <row r="500" spans="1:17" customFormat="1" ht="15.75">
+    <row r="500" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A500" s="2">
         <v>1000</v>
       </c>
@@ -29232,7 +29233,7 @@
       <c r="P500" s="38"/>
       <c r="Q500" s="27"/>
     </row>
-    <row r="501" spans="1:17" customFormat="1" ht="15.75">
+    <row r="501" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A501" s="2">
         <v>1000</v>
       </c>
@@ -29269,7 +29270,7 @@
       <c r="P501" s="38"/>
       <c r="Q501" s="27"/>
     </row>
-    <row r="502" spans="1:17" customFormat="1" ht="15.75">
+    <row r="502" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A502" s="2">
         <v>1000</v>
       </c>
@@ -29306,7 +29307,7 @@
       <c r="P502" s="38"/>
       <c r="Q502" s="27"/>
     </row>
-    <row r="503" spans="1:17" customFormat="1" ht="15.75">
+    <row r="503" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A503" s="2">
         <v>1000</v>
       </c>
@@ -29343,7 +29344,7 @@
       <c r="P503" s="38"/>
       <c r="Q503" s="27"/>
     </row>
-    <row r="504" spans="1:17" customFormat="1" ht="15.75">
+    <row r="504" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A504" s="2">
         <v>1000</v>
       </c>
@@ -29380,7 +29381,7 @@
       <c r="P504" s="38"/>
       <c r="Q504" s="27"/>
     </row>
-    <row r="505" spans="1:17" customFormat="1" ht="15.75">
+    <row r="505" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A505" s="2">
         <v>1000</v>
       </c>
@@ -29417,7 +29418,7 @@
       <c r="P505" s="38"/>
       <c r="Q505" s="27"/>
     </row>
-    <row r="506" spans="1:17" customFormat="1" ht="15.75">
+    <row r="506" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A506" s="2">
         <v>1000</v>
       </c>
@@ -29454,7 +29455,7 @@
       <c r="P506" s="38"/>
       <c r="Q506" s="27"/>
     </row>
-    <row r="507" spans="1:17" customFormat="1" ht="15.75">
+    <row r="507" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A507" s="2">
         <v>1000</v>
       </c>
@@ -29491,7 +29492,7 @@
       <c r="P507" s="38"/>
       <c r="Q507" s="27"/>
     </row>
-    <row r="508" spans="1:17" customFormat="1" ht="15.75">
+    <row r="508" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A508" s="2">
         <v>1000</v>
       </c>
@@ -29528,7 +29529,7 @@
       <c r="P508" s="38"/>
       <c r="Q508" s="27"/>
     </row>
-    <row r="509" spans="1:17" customFormat="1" ht="15.75">
+    <row r="509" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A509" s="2">
         <v>1000</v>
       </c>
@@ -29565,7 +29566,7 @@
       <c r="P509" s="38"/>
       <c r="Q509" s="27"/>
     </row>
-    <row r="510" spans="1:17" customFormat="1" ht="15.75">
+    <row r="510" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A510" s="2">
         <v>1000</v>
       </c>
@@ -29602,7 +29603,7 @@
       <c r="P510" s="38"/>
       <c r="Q510" s="27"/>
     </row>
-    <row r="511" spans="1:17" customFormat="1" ht="15.75">
+    <row r="511" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A511" s="2">
         <v>1000</v>
       </c>
@@ -29639,7 +29640,7 @@
       <c r="P511" s="38"/>
       <c r="Q511" s="27"/>
     </row>
-    <row r="512" spans="1:17" customFormat="1" ht="15.75">
+    <row r="512" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A512" s="2">
         <v>1000</v>
       </c>
@@ -29676,7 +29677,7 @@
       <c r="P512" s="38"/>
       <c r="Q512" s="27"/>
     </row>
-    <row r="513" spans="1:17" customFormat="1" ht="15.75">
+    <row r="513" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A513" s="2">
         <v>1000</v>
       </c>
@@ -29713,7 +29714,7 @@
       <c r="P513" s="38"/>
       <c r="Q513" s="27"/>
     </row>
-    <row r="514" spans="1:17" customFormat="1" ht="15.75">
+    <row r="514" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A514" s="2">
         <v>1000</v>
       </c>
@@ -29750,7 +29751,7 @@
       <c r="P514" s="38"/>
       <c r="Q514" s="27"/>
     </row>
-    <row r="515" spans="1:17" customFormat="1" ht="15.75">
+    <row r="515" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A515" s="2">
         <v>1000</v>
       </c>
@@ -29787,7 +29788,7 @@
       <c r="P515" s="38"/>
       <c r="Q515" s="27"/>
     </row>
-    <row r="516" spans="1:17" customFormat="1" ht="15.75">
+    <row r="516" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A516" s="2">
         <v>1000</v>
       </c>
@@ -29824,7 +29825,7 @@
       <c r="P516" s="38"/>
       <c r="Q516" s="27"/>
     </row>
-    <row r="517" spans="1:17" customFormat="1" ht="15.75">
+    <row r="517" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A517" s="2">
         <v>1000</v>
       </c>
@@ -29861,7 +29862,7 @@
       <c r="P517" s="38"/>
       <c r="Q517" s="27"/>
     </row>
-    <row r="518" spans="1:17" customFormat="1" ht="15.75">
+    <row r="518" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A518" s="4">
         <v>1100</v>
       </c>
@@ -29896,7 +29897,7 @@
       <c r="P518" s="38"/>
       <c r="Q518" s="27"/>
     </row>
-    <row r="519" spans="1:17" customFormat="1" ht="15.75">
+    <row r="519" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A519" s="4">
         <v>1300</v>
       </c>
@@ -29933,7 +29934,7 @@
       <c r="P519" s="38"/>
       <c r="Q519" s="27"/>
     </row>
-    <row r="520" spans="1:17" customFormat="1" ht="15.75">
+    <row r="520" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A520" s="4">
         <v>1300</v>
       </c>
@@ -29974,7 +29975,7 @@
       <c r="P520" s="38"/>
       <c r="Q520" s="27"/>
     </row>
-    <row r="521" spans="1:17" customFormat="1" ht="15.75">
+    <row r="521" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A521" s="4">
         <v>1300</v>
       </c>
@@ -30015,7 +30016,7 @@
       <c r="P521" s="38"/>
       <c r="Q521" s="27"/>
     </row>
-    <row r="522" spans="1:17" customFormat="1" ht="15.75">
+    <row r="522" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A522" s="4">
         <v>1300</v>
       </c>
@@ -30052,7 +30053,7 @@
       <c r="P522" s="38"/>
       <c r="Q522" s="27"/>
     </row>
-    <row r="523" spans="1:17" customFormat="1" ht="15.75">
+    <row r="523" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A523" s="4">
         <v>1300</v>
       </c>
@@ -30089,7 +30090,7 @@
       <c r="P523" s="38"/>
       <c r="Q523" s="27"/>
     </row>
-    <row r="524" spans="1:17" customFormat="1" ht="15.75">
+    <row r="524" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A524" s="4">
         <v>1300</v>
       </c>
@@ -30126,7 +30127,7 @@
       <c r="P524" s="38"/>
       <c r="Q524" s="27"/>
     </row>
-    <row r="525" spans="1:17" customFormat="1" ht="15.75">
+    <row r="525" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A525" s="4">
         <v>1300</v>
       </c>
@@ -30163,7 +30164,7 @@
       <c r="P525" s="38"/>
       <c r="Q525" s="27"/>
     </row>
-    <row r="526" spans="1:17" customFormat="1" ht="15.75">
+    <row r="526" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A526" s="4">
         <v>1300</v>
       </c>
@@ -30200,7 +30201,7 @@
       <c r="P526" s="38"/>
       <c r="Q526" s="27"/>
     </row>
-    <row r="527" spans="1:17" customFormat="1" ht="15.75">
+    <row r="527" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A527" s="4">
         <v>1300</v>
       </c>
@@ -30237,7 +30238,7 @@
       <c r="P527" s="38"/>
       <c r="Q527" s="27"/>
     </row>
-    <row r="528" spans="1:17" customFormat="1" ht="15.75">
+    <row r="528" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A528" s="4">
         <v>1300</v>
       </c>
@@ -30278,7 +30279,7 @@
       <c r="P528" s="38"/>
       <c r="Q528" s="27"/>
     </row>
-    <row r="529" spans="1:17" customFormat="1" ht="15.75">
+    <row r="529" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A529" s="4">
         <v>1300</v>
       </c>
@@ -30319,7 +30320,7 @@
       <c r="P529" s="38"/>
       <c r="Q529" s="27"/>
     </row>
-    <row r="530" spans="1:17" customFormat="1" ht="15.75">
+    <row r="530" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A530" s="4">
         <v>1300</v>
       </c>
@@ -30356,7 +30357,7 @@
       <c r="P530" s="38"/>
       <c r="Q530" s="27"/>
     </row>
-    <row r="531" spans="1:17" customFormat="1" ht="15.75">
+    <row r="531" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A531" s="4">
         <v>1300</v>
       </c>
@@ -30393,7 +30394,7 @@
       <c r="P531" s="38"/>
       <c r="Q531" s="27"/>
     </row>
-    <row r="532" spans="1:17" customFormat="1" ht="15.75">
+    <row r="532" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A532" s="4">
         <v>1300</v>
       </c>
@@ -30434,7 +30435,7 @@
       <c r="P532" s="38"/>
       <c r="Q532" s="27"/>
     </row>
-    <row r="533" spans="1:17" customFormat="1" ht="15.75">
+    <row r="533" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A533" s="4">
         <v>1300</v>
       </c>
@@ -30475,7 +30476,7 @@
       <c r="P533" s="38"/>
       <c r="Q533" s="27"/>
     </row>
-    <row r="534" spans="1:17" customFormat="1" ht="15.75">
+    <row r="534" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A534" s="4">
         <v>1300</v>
       </c>
@@ -30516,7 +30517,7 @@
       <c r="P534" s="38"/>
       <c r="Q534" s="27"/>
     </row>
-    <row r="535" spans="1:17" customFormat="1" ht="15.75">
+    <row r="535" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A535" s="4">
         <v>1300</v>
       </c>
@@ -30557,7 +30558,7 @@
       <c r="P535" s="38"/>
       <c r="Q535" s="27"/>
     </row>
-    <row r="536" spans="1:17" customFormat="1" ht="15.75">
+    <row r="536" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A536" s="4">
         <v>1300</v>
       </c>
@@ -30598,7 +30599,7 @@
       <c r="P536" s="38"/>
       <c r="Q536" s="27"/>
     </row>
-    <row r="537" spans="1:17" customFormat="1" ht="15.75">
+    <row r="537" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A537" s="4">
         <v>1300</v>
       </c>
@@ -30639,7 +30640,7 @@
       <c r="P537" s="38"/>
       <c r="Q537" s="27"/>
     </row>
-    <row r="538" spans="1:17" customFormat="1" ht="15.75">
+    <row r="538" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A538" s="4">
         <v>1300</v>
       </c>
@@ -30680,7 +30681,7 @@
       <c r="P538" s="38"/>
       <c r="Q538" s="27"/>
     </row>
-    <row r="539" spans="1:17" customFormat="1" ht="15.75">
+    <row r="539" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A539" s="4">
         <v>1300</v>
       </c>
@@ -30721,7 +30722,7 @@
       <c r="P539" s="38"/>
       <c r="Q539" s="27"/>
     </row>
-    <row r="540" spans="1:17" customFormat="1" ht="15.75">
+    <row r="540" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A540" s="4">
         <v>1300</v>
       </c>
@@ -30762,7 +30763,7 @@
       <c r="P540" s="38"/>
       <c r="Q540" s="27"/>
     </row>
-    <row r="541" spans="1:17" customFormat="1" ht="15.75">
+    <row r="541" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A541" s="4">
         <v>1300</v>
       </c>
@@ -30803,7 +30804,7 @@
       <c r="P541" s="38"/>
       <c r="Q541" s="27"/>
     </row>
-    <row r="542" spans="1:17" customFormat="1" ht="15.75">
+    <row r="542" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A542" s="4">
         <v>1300</v>
       </c>
@@ -30844,7 +30845,7 @@
       <c r="P542" s="38"/>
       <c r="Q542" s="27"/>
     </row>
-    <row r="543" spans="1:17" customFormat="1" ht="15.75">
+    <row r="543" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A543" s="4">
         <v>1300</v>
       </c>
@@ -30885,7 +30886,7 @@
       <c r="P543" s="38"/>
       <c r="Q543" s="27"/>
     </row>
-    <row r="544" spans="1:17" customFormat="1" ht="15.75">
+    <row r="544" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A544" s="4">
         <v>1300</v>
       </c>
@@ -30926,7 +30927,7 @@
       <c r="P544" s="38"/>
       <c r="Q544" s="27"/>
     </row>
-    <row r="545" spans="1:17" customFormat="1" ht="15.75">
+    <row r="545" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A545" s="4">
         <v>1300</v>
       </c>
@@ -30967,7 +30968,7 @@
       <c r="P545" s="38"/>
       <c r="Q545" s="27"/>
     </row>
-    <row r="546" spans="1:17" customFormat="1" ht="15.75">
+    <row r="546" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A546" s="4">
         <v>1300</v>
       </c>
@@ -31004,7 +31005,7 @@
       <c r="P546" s="38"/>
       <c r="Q546" s="27"/>
     </row>
-    <row r="547" spans="1:17" customFormat="1" ht="15.75">
+    <row r="547" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A547" s="4">
         <v>1300</v>
       </c>
@@ -31041,7 +31042,7 @@
       <c r="P547" s="38"/>
       <c r="Q547" s="27"/>
     </row>
-    <row r="548" spans="1:17" customFormat="1" ht="15.75">
+    <row r="548" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A548" s="4">
         <v>1300</v>
       </c>
@@ -31078,7 +31079,7 @@
       <c r="P548" s="38"/>
       <c r="Q548" s="27"/>
     </row>
-    <row r="549" spans="1:17" customFormat="1" ht="15.75">
+    <row r="549" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A549" s="4">
         <v>1300</v>
       </c>
@@ -31115,7 +31116,7 @@
       <c r="P549" s="38"/>
       <c r="Q549" s="27"/>
     </row>
-    <row r="550" spans="1:17" customFormat="1" ht="15.75">
+    <row r="550" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A550" s="4">
         <v>1300</v>
       </c>
@@ -31156,7 +31157,7 @@
       <c r="P550" s="38"/>
       <c r="Q550" s="27"/>
     </row>
-    <row r="551" spans="1:17" customFormat="1" ht="15.75">
+    <row r="551" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A551" s="4">
         <v>1300</v>
       </c>
@@ -31197,7 +31198,7 @@
       <c r="P551" s="38"/>
       <c r="Q551" s="27"/>
     </row>
-    <row r="552" spans="1:17" customFormat="1" ht="15.75">
+    <row r="552" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A552" s="4">
         <v>1300</v>
       </c>
@@ -31238,7 +31239,7 @@
       <c r="P552" s="38"/>
       <c r="Q552" s="27"/>
     </row>
-    <row r="553" spans="1:17" customFormat="1" ht="15.75">
+    <row r="553" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A553" s="4">
         <v>1300</v>
       </c>
@@ -31279,7 +31280,7 @@
       <c r="P553" s="38"/>
       <c r="Q553" s="27"/>
     </row>
-    <row r="554" spans="1:17" customFormat="1" ht="15.75">
+    <row r="554" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A554" s="4">
         <v>1300</v>
       </c>
@@ -31316,7 +31317,7 @@
       <c r="P554" s="38"/>
       <c r="Q554" s="27"/>
     </row>
-    <row r="555" spans="1:17" customFormat="1" ht="15.75">
+    <row r="555" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A555" s="4">
         <v>1300</v>
       </c>
@@ -31353,7 +31354,7 @@
       <c r="P555" s="38"/>
       <c r="Q555" s="27"/>
     </row>
-    <row r="556" spans="1:17" customFormat="1" ht="15.75">
+    <row r="556" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A556" s="4">
         <v>1300</v>
       </c>
@@ -31390,7 +31391,7 @@
       <c r="P556" s="38"/>
       <c r="Q556" s="27"/>
     </row>
-    <row r="557" spans="1:17" customFormat="1" ht="15.75">
+    <row r="557" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A557" s="4">
         <v>1300</v>
       </c>
@@ -31427,7 +31428,7 @@
       <c r="P557" s="38"/>
       <c r="Q557" s="27"/>
     </row>
-    <row r="558" spans="1:17" customFormat="1" ht="15.75">
+    <row r="558" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A558" s="4">
         <v>1300</v>
       </c>
@@ -31464,7 +31465,7 @@
       <c r="P558" s="38"/>
       <c r="Q558" s="27"/>
     </row>
-    <row r="559" spans="1:17" customFormat="1" ht="15.75">
+    <row r="559" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A559" s="4">
         <v>1300</v>
       </c>
@@ -31501,7 +31502,7 @@
       <c r="P559" s="38"/>
       <c r="Q559" s="27"/>
     </row>
-    <row r="560" spans="1:17" customFormat="1" ht="15.75">
+    <row r="560" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A560" s="4">
         <v>1300</v>
       </c>
@@ -31538,7 +31539,7 @@
       <c r="P560" s="38"/>
       <c r="Q560" s="27"/>
     </row>
-    <row r="561" spans="1:17" customFormat="1" ht="15.75">
+    <row r="561" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A561" s="4">
         <v>1300</v>
       </c>
@@ -31579,7 +31580,7 @@
       <c r="P561" s="38"/>
       <c r="Q561" s="27"/>
     </row>
-    <row r="562" spans="1:17" customFormat="1" ht="15.75">
+    <row r="562" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A562" s="4">
         <v>1300</v>
       </c>
@@ -31620,7 +31621,7 @@
       <c r="P562" s="38"/>
       <c r="Q562" s="27"/>
     </row>
-    <row r="563" spans="1:17" customFormat="1" ht="15.75">
+    <row r="563" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A563" s="4">
         <v>1300</v>
       </c>
@@ -31661,7 +31662,7 @@
       <c r="P563" s="38"/>
       <c r="Q563" s="27"/>
     </row>
-    <row r="564" spans="1:17" customFormat="1" ht="15.75">
+    <row r="564" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A564" s="4">
         <v>1300</v>
       </c>
@@ -31702,7 +31703,7 @@
       <c r="P564" s="38"/>
       <c r="Q564" s="27"/>
     </row>
-    <row r="565" spans="1:17" customFormat="1" ht="15.75">
+    <row r="565" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A565" s="4">
         <v>1300</v>
       </c>
@@ -31739,7 +31740,7 @@
       <c r="P565" s="38"/>
       <c r="Q565" s="27"/>
     </row>
-    <row r="566" spans="1:17" customFormat="1" ht="15.75">
+    <row r="566" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A566" s="4">
         <v>1300</v>
       </c>
@@ -31776,7 +31777,7 @@
       <c r="P566" s="38"/>
       <c r="Q566" s="27"/>
     </row>
-    <row r="567" spans="1:17" customFormat="1" ht="15.75">
+    <row r="567" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A567" s="4">
         <v>1300</v>
       </c>
@@ -31813,7 +31814,7 @@
       <c r="P567" s="38"/>
       <c r="Q567" s="27"/>
     </row>
-    <row r="568" spans="1:17" customFormat="1" ht="15.75">
+    <row r="568" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A568" s="4">
         <v>1300</v>
       </c>
@@ -31850,7 +31851,7 @@
       <c r="P568" s="38"/>
       <c r="Q568" s="27"/>
     </row>
-    <row r="569" spans="1:17" customFormat="1" ht="15.75">
+    <row r="569" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A569" s="4">
         <v>1300</v>
       </c>
@@ -31887,7 +31888,7 @@
       <c r="P569" s="38"/>
       <c r="Q569" s="27"/>
     </row>
-    <row r="570" spans="1:17" customFormat="1" ht="15.75">
+    <row r="570" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A570" s="4">
         <v>1300</v>
       </c>
@@ -31924,7 +31925,7 @@
       <c r="P570" s="38"/>
       <c r="Q570" s="27"/>
     </row>
-    <row r="571" spans="1:17" customFormat="1" ht="15.75">
+    <row r="571" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A571" s="4">
         <v>1300</v>
       </c>
@@ -31961,7 +31962,7 @@
       <c r="P571" s="38"/>
       <c r="Q571" s="27"/>
     </row>
-    <row r="572" spans="1:17" customFormat="1" ht="15.75">
+    <row r="572" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A572" s="4">
         <v>1300</v>
       </c>
@@ -31998,7 +31999,7 @@
       <c r="P572" s="38"/>
       <c r="Q572" s="27"/>
     </row>
-    <row r="573" spans="1:17" customFormat="1" ht="15.75">
+    <row r="573" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A573" s="4">
         <v>1300</v>
       </c>
@@ -32035,7 +32036,7 @@
       <c r="P573" s="38"/>
       <c r="Q573" s="27"/>
     </row>
-    <row r="574" spans="1:17" ht="15.75">
+    <row r="574" spans="1:17" ht="15.75" hidden="1">
       <c r="A574" s="33">
         <v>1300</v>
       </c>
@@ -32072,7 +32073,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="575" spans="1:17" ht="15.75">
+    <row r="575" spans="1:17" ht="15.75" hidden="1">
       <c r="A575" s="33">
         <v>1300</v>
       </c>
@@ -32109,7 +32110,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="576" spans="1:17" customFormat="1" ht="15.75">
+    <row r="576" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A576" s="4">
         <v>1300</v>
       </c>
@@ -32146,7 +32147,7 @@
       <c r="P576" s="38"/>
       <c r="Q576" s="27"/>
     </row>
-    <row r="577" spans="1:17" customFormat="1" ht="15.75">
+    <row r="577" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A577" s="4">
         <v>1300</v>
       </c>
@@ -32183,7 +32184,7 @@
       <c r="P577" s="38"/>
       <c r="Q577" s="27"/>
     </row>
-    <row r="578" spans="1:17" customFormat="1" ht="15.75">
+    <row r="578" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A578" s="4">
         <v>1300</v>
       </c>
@@ -32220,7 +32221,7 @@
       <c r="P578" s="38"/>
       <c r="Q578" s="27"/>
     </row>
-    <row r="579" spans="1:17" customFormat="1" ht="15.75">
+    <row r="579" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A579" s="4">
         <v>1300</v>
       </c>
@@ -32257,7 +32258,7 @@
       <c r="P579" s="38"/>
       <c r="Q579" s="27"/>
     </row>
-    <row r="580" spans="1:17" customFormat="1" ht="15.75">
+    <row r="580" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A580" s="4">
         <v>1300</v>
       </c>
@@ -32294,7 +32295,7 @@
       <c r="P580" s="38"/>
       <c r="Q580" s="27"/>
     </row>
-    <row r="581" spans="1:17" customFormat="1" ht="15.75">
+    <row r="581" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A581" s="4">
         <v>1300</v>
       </c>
@@ -32331,7 +32332,7 @@
       <c r="P581" s="38"/>
       <c r="Q581" s="27"/>
     </row>
-    <row r="582" spans="1:17" customFormat="1" ht="15.75">
+    <row r="582" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A582" s="4">
         <v>1300</v>
       </c>
@@ -32368,7 +32369,7 @@
       <c r="P582" s="38"/>
       <c r="Q582" s="27"/>
     </row>
-    <row r="583" spans="1:17" customFormat="1" ht="15.75">
+    <row r="583" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A583" s="4">
         <v>1300</v>
       </c>
@@ -32405,7 +32406,7 @@
       <c r="P583" s="38"/>
       <c r="Q583" s="27"/>
     </row>
-    <row r="584" spans="1:17" customFormat="1" ht="15.75">
+    <row r="584" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A584" s="4">
         <v>1300</v>
       </c>
@@ -32442,7 +32443,7 @@
       <c r="P584" s="38"/>
       <c r="Q584" s="27"/>
     </row>
-    <row r="585" spans="1:17" customFormat="1" ht="15.75">
+    <row r="585" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A585" s="4">
         <v>1300</v>
       </c>
@@ -32479,7 +32480,7 @@
       <c r="P585" s="38"/>
       <c r="Q585" s="27"/>
     </row>
-    <row r="586" spans="1:17" customFormat="1" ht="15.75">
+    <row r="586" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A586" s="4">
         <v>1300</v>
       </c>
@@ -32514,7 +32515,7 @@
       <c r="P586" s="38"/>
       <c r="Q586" s="27"/>
     </row>
-    <row r="587" spans="1:17" customFormat="1" ht="15.75">
+    <row r="587" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A587" s="4">
         <v>1300</v>
       </c>
@@ -32551,7 +32552,7 @@
       <c r="P587" s="38"/>
       <c r="Q587" s="27"/>
     </row>
-    <row r="588" spans="1:17" customFormat="1" ht="15.75">
+    <row r="588" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A588" s="4">
         <v>1300</v>
       </c>
@@ -32588,7 +32589,7 @@
       <c r="P588" s="38"/>
       <c r="Q588" s="27"/>
     </row>
-    <row r="589" spans="1:17" customFormat="1" ht="15.75">
+    <row r="589" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A589" s="4">
         <v>1300</v>
       </c>
@@ -32625,7 +32626,7 @@
       <c r="P589" s="38"/>
       <c r="Q589" s="27"/>
     </row>
-    <row r="590" spans="1:17" customFormat="1" ht="15.75">
+    <row r="590" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A590" s="4">
         <v>1300</v>
       </c>
@@ -32662,7 +32663,7 @@
       <c r="P590" s="38"/>
       <c r="Q590" s="27"/>
     </row>
-    <row r="591" spans="1:17" customFormat="1" ht="15.75">
+    <row r="591" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A591" s="2">
         <v>1400</v>
       </c>
@@ -32697,7 +32698,7 @@
       <c r="P591" s="38"/>
       <c r="Q591" s="27"/>
     </row>
-    <row r="592" spans="1:17" customFormat="1" ht="15.75">
+    <row r="592" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A592" s="2">
         <v>1400</v>
       </c>
@@ -32734,7 +32735,7 @@
       <c r="P592" s="38"/>
       <c r="Q592" s="27"/>
     </row>
-    <row r="593" spans="1:17" customFormat="1" ht="15.75">
+    <row r="593" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A593" s="2">
         <v>1400</v>
       </c>
@@ -32771,7 +32772,7 @@
       <c r="P593" s="38"/>
       <c r="Q593" s="27"/>
     </row>
-    <row r="594" spans="1:17" customFormat="1" ht="15.75">
+    <row r="594" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A594" s="2">
         <v>1400</v>
       </c>
@@ -32808,7 +32809,7 @@
       <c r="P594" s="38"/>
       <c r="Q594" s="27"/>
     </row>
-    <row r="595" spans="1:17" customFormat="1" ht="15.75">
+    <row r="595" spans="1:17" customFormat="1" ht="15.75" hidden="1">
       <c r="A595" s="2">
         <v>1400</v>
       </c>
@@ -32853,7 +32854,14 @@
     <protectedRange sqref="D8:D94" name="Range1"/>
     <protectedRange sqref="D591" name="Range1_1"/>
   </protectedRanges>
-  <autoFilter ref="A7:AF595"/>
+  <autoFilter ref="A7:AF595">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="توانا"/>
+        <filter val="توانا/کارگر"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="AA1:AF1"/>
   </mergeCells>
